--- a/Python/ML-DL learning schedule.xlsx
+++ b/Python/ML-DL learning schedule.xlsx
@@ -1,24 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\codes\programming\Python\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\projects\programming\Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC914F09-B3BD-42BD-93DC-75061E2A64DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{170CA0B9-8735-467C-84C1-26B56343B45A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="58050" yWindow="150" windowWidth="27165" windowHeight="15075" tabRatio="577" activeTab="4" xr2:uid="{6907F51F-E0BB-4F68-AA3F-2C472EE0609D}"/>
+    <workbookView xWindow="30375" yWindow="135" windowWidth="25665" windowHeight="15180" tabRatio="709" xr2:uid="{6907F51F-E0BB-4F68-AA3F-2C472EE0609D}"/>
   </bookViews>
   <sheets>
-    <sheet name="D.L" sheetId="1" r:id="rId1"/>
-    <sheet name="M.L" sheetId="5" r:id="rId2"/>
-    <sheet name="TensorFlow 2 for Deep Learning " sheetId="7" r:id="rId3"/>
-    <sheet name="TensorFlow Developer Profession" sheetId="8" r:id="rId4"/>
-    <sheet name="schedule" sheetId="10" r:id="rId5"/>
-    <sheet name="TensorFlow  Advanced Techniques" sheetId="9" r:id="rId6"/>
+    <sheet name="schedule" sheetId="10" r:id="rId1"/>
+    <sheet name="Natural Language Processing Spe" sheetId="11" r:id="rId2"/>
+    <sheet name="Deep Learning Spec" sheetId="12" r:id="rId3"/>
+    <sheet name="D.L" sheetId="1" r:id="rId4"/>
+    <sheet name="M.L" sheetId="5" r:id="rId5"/>
+    <sheet name="TensorFlow 2 for Deep Learning " sheetId="7" r:id="rId6"/>
+    <sheet name="TensorFlow Developer Profession" sheetId="8" r:id="rId7"/>
+    <sheet name="TensorFlow  Advanced Techniques" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1703" uniqueCount="998">
   <si>
     <t>Course 1</t>
   </si>
@@ -1600,6 +1602,1566 @@
   <si>
     <t>C1_W4_Lab_1_image_data_preprocessing_no_validation_s</t>
   </si>
+  <si>
+    <t>Deep Learning Specialization: Course 1 - Neural Networks and Deep Learning</t>
+  </si>
+  <si>
+    <t>Introduction to Deep Learning</t>
+  </si>
+  <si>
+    <t>What is Neural Network?</t>
+  </si>
+  <si>
+    <t>C1W4_Assignment_s.ipynb</t>
+  </si>
+  <si>
+    <t>Supervised Learning with Neural Networks</t>
+  </si>
+  <si>
+    <t>Why is Deep Learning taking off?</t>
+  </si>
+  <si>
+    <t>About this course</t>
+  </si>
+  <si>
+    <t>Logistic Regression as a Neural Network</t>
+  </si>
+  <si>
+    <t>Binary Classification</t>
+  </si>
+  <si>
+    <t>Logistic Regression</t>
+  </si>
+  <si>
+    <t>Logistic Regression Cost Function</t>
+  </si>
+  <si>
+    <t>Gradient Descent</t>
+  </si>
+  <si>
+    <t>Derivatives</t>
+  </si>
+  <si>
+    <t>More Derivatice Examples</t>
+  </si>
+  <si>
+    <t>Computation Graph</t>
+  </si>
+  <si>
+    <t>Derivative with a Computation Graph</t>
+  </si>
+  <si>
+    <t>Logistic Regression Gradient Descent</t>
+  </si>
+  <si>
+    <t>Gradient Descent on m Examples</t>
+  </si>
+  <si>
+    <t>Python and Vectorization</t>
+  </si>
+  <si>
+    <t>Vectorization</t>
+  </si>
+  <si>
+    <t>More Vectorization Examples</t>
+  </si>
+  <si>
+    <t>Vectorizing Logistic Regression</t>
+  </si>
+  <si>
+    <t>Vectorizing Logistic Regression's Gradient Output</t>
+  </si>
+  <si>
+    <t>Broadcasting in Python</t>
+  </si>
+  <si>
+    <t>A Note on Python/Numpy Vectors</t>
+  </si>
+  <si>
+    <t>Neural Networks Overview</t>
+  </si>
+  <si>
+    <t>Shallow Neural Network</t>
+  </si>
+  <si>
+    <t>Neural Network Representation</t>
+  </si>
+  <si>
+    <t>Computing a Neural Network's Output</t>
+  </si>
+  <si>
+    <t>Vectorizing Across Multiple Examples</t>
+  </si>
+  <si>
+    <t>Explanation for Vectorized Implementation</t>
+  </si>
+  <si>
+    <t>Why do you need Non-Linear Activation Functions?</t>
+  </si>
+  <si>
+    <t>Derivative of Activation Functions</t>
+  </si>
+  <si>
+    <t>Gradient Descent for Neural Networks</t>
+  </si>
+  <si>
+    <t>Random initialization</t>
+  </si>
+  <si>
+    <t>Deep Neural Network</t>
+  </si>
+  <si>
+    <t>Deep L-layer Neural Network</t>
+  </si>
+  <si>
+    <t>Forward Propagation in a Deep Network</t>
+  </si>
+  <si>
+    <t>Getting your Matrix Dimensions Right</t>
+  </si>
+  <si>
+    <t>Why deep Representations? ???</t>
+  </si>
+  <si>
+    <t>Building Blocks of Neural Networks</t>
+  </si>
+  <si>
+    <t>Forward and Backward Propagation</t>
+  </si>
+  <si>
+    <t>Parameters vs Hyperparameters</t>
+  </si>
+  <si>
+    <t>What does this have to do with the brain?</t>
+  </si>
+  <si>
+    <t>Deep Learning Specialization: Course 5 - Sequence Models</t>
+  </si>
+  <si>
+    <t>Why Sequence Models?</t>
+  </si>
+  <si>
+    <t>Notation</t>
+  </si>
+  <si>
+    <t>Recurrent Neural Network Model</t>
+  </si>
+  <si>
+    <t>Backpropagation Through Time</t>
+  </si>
+  <si>
+    <t>Different Types of RNNs</t>
+  </si>
+  <si>
+    <t>Language Model and Sequence Generation</t>
+  </si>
+  <si>
+    <t>Sampling Novel Sequences</t>
+  </si>
+  <si>
+    <t>Vanishing Gradients with RNN</t>
+  </si>
+  <si>
+    <t>Gated Recurrenct Unit</t>
+  </si>
+  <si>
+    <t>Long Short Term Menory(LSTM)</t>
+  </si>
+  <si>
+    <t>Bidirectional RNN</t>
+  </si>
+  <si>
+    <t>Deep RNN</t>
+  </si>
+  <si>
+    <t>Natural Language Processing &amp; Word Embeddings</t>
+  </si>
+  <si>
+    <t>Introduction to Word Embeddings</t>
+  </si>
+  <si>
+    <t>Word Representation</t>
+  </si>
+  <si>
+    <t>Lecture: Logistic Regression</t>
+  </si>
+  <si>
+    <t>Video: VideoWelcome to the NLP Specialization</t>
+  </si>
+  <si>
+    <t>Video: VideoWelcome to Course 1</t>
+  </si>
+  <si>
+    <t>Reading: ReadingAcknowledgement - Ken Church</t>
+  </si>
+  <si>
+    <t>Video: VideoWeek Introduction</t>
+  </si>
+  <si>
+    <t>. Duration: 35 seconds35 sec</t>
+  </si>
+  <si>
+    <t>Video: VideoSupervised ML &amp; Sentiment Analysis</t>
+  </si>
+  <si>
+    <t>Reading: ReadingSupervised ML &amp; Sentiment Analysis</t>
+  </si>
+  <si>
+    <t>Video: VideoVocabulary &amp; Feature Extraction</t>
+  </si>
+  <si>
+    <t>Reading: ReadingVocabulary &amp; Feature Extraction</t>
+  </si>
+  <si>
+    <t>Video: VideoNegative and Positive Frequencies</t>
+  </si>
+  <si>
+    <t>Video: VideoFeature Extraction with Frequencies</t>
+  </si>
+  <si>
+    <t>Reading: ReadingFeature Extraction with Frequencies</t>
+  </si>
+  <si>
+    <t>Video: VideoPreprocessing</t>
+  </si>
+  <si>
+    <t>Reading: ReadingPreprocessing</t>
+  </si>
+  <si>
+    <t>Lab: Natural Language preprocessing</t>
+  </si>
+  <si>
+    <t>Video: VideoPutting it All Together</t>
+  </si>
+  <si>
+    <t>Reading: ReadingPutting it all together</t>
+  </si>
+  <si>
+    <t>Lab: Visualizing word frequencies</t>
+  </si>
+  <si>
+    <t>Video: VideoLogistic Regression Overview</t>
+  </si>
+  <si>
+    <t>Reading: ReadingLogistic Regression Overview</t>
+  </si>
+  <si>
+    <t>Video: VideoLogistic Regression: Training</t>
+  </si>
+  <si>
+    <t>Reading: ReadingLogistic Regression: Training</t>
+  </si>
+  <si>
+    <t>Lab: Visualizing tweets and Logistic Regression models</t>
+  </si>
+  <si>
+    <t>Video: VideoLogistic Regression: Testing</t>
+  </si>
+  <si>
+    <t>Reading: ReadingLogistic Regression: Testing</t>
+  </si>
+  <si>
+    <t>Video: VideoLogistic Regression: Cost Function</t>
+  </si>
+  <si>
+    <t>Reading: ReadingOptional Logistic Regression: Cost Function</t>
+  </si>
+  <si>
+    <t>Video: VideoWeek Conclusion</t>
+  </si>
+  <si>
+    <t>. Duration: 30 seconds30 sec</t>
+  </si>
+  <si>
+    <t>Reading: ReadingOptional Logistic Regression: Gradient</t>
+  </si>
+  <si>
+    <t>Reading: ReadingLecture Notes W1</t>
+  </si>
+  <si>
+    <t>Practice Quiz</t>
+  </si>
+  <si>
+    <t>Practice Assignment: Logistic Regression</t>
+  </si>
+  <si>
+    <t>Assignment: Sentiment Analysis with Logistic Regression</t>
+  </si>
+  <si>
+    <t>Reading: Reading(Optional) Downloading your Notebook, Downloading your Workspace and Refreshing your Workspace</t>
+  </si>
+  <si>
+    <t>Programming Assignment: Logistic Regression</t>
+  </si>
+  <si>
+    <t>Heroes of NLP: Chris Manning (Optional)</t>
+  </si>
+  <si>
+    <t>Video: VideoAndrew Ng with Chris Manning</t>
+  </si>
+  <si>
+    <t>. Duration: 46 minutes46 min</t>
+  </si>
+  <si>
+    <t>Using Word Embeddings</t>
+  </si>
+  <si>
+    <t>Properties of Word Embeddings</t>
+  </si>
+  <si>
+    <t>Embedding matrix</t>
+  </si>
+  <si>
+    <t>Learning Word Embeddings: Word2vec &amp; GloVe</t>
+  </si>
+  <si>
+    <t>Learning Word Embedding</t>
+  </si>
+  <si>
+    <t>Word2Vec</t>
+  </si>
+  <si>
+    <t>Negative Sampling</t>
+  </si>
+  <si>
+    <t>GloVe Word Vectors</t>
+  </si>
+  <si>
+    <t>Application using Word Embeddings</t>
+  </si>
+  <si>
+    <t>Sentiment Classification</t>
+  </si>
+  <si>
+    <t>Debiaing Word Embeddings</t>
+  </si>
+  <si>
+    <t>Lecture: Naive Bayes</t>
+  </si>
+  <si>
+    <t>. Duration: 27 seconds27 sec</t>
+  </si>
+  <si>
+    <t>Video: VideoProbability and Bayes’ Rule</t>
+  </si>
+  <si>
+    <t>Reading: ReadingProbability and Bayes’ Rule</t>
+  </si>
+  <si>
+    <t>Video: VideoBayes’ Rule</t>
+  </si>
+  <si>
+    <t>Reading: ReadingBayes' Rule</t>
+  </si>
+  <si>
+    <t>Video: VideoNaïve Bayes Introduction</t>
+  </si>
+  <si>
+    <t>Reading: ReadingNaive Bayes Introduction</t>
+  </si>
+  <si>
+    <t>Video: VideoLaplacian Smoothing</t>
+  </si>
+  <si>
+    <t>Reading: ReadingLaplacian Smoothing</t>
+  </si>
+  <si>
+    <t>Video: VideoLog Likelihood, Part 1</t>
+  </si>
+  <si>
+    <t>Reading: ReadingLog Likelihood, Part 1</t>
+  </si>
+  <si>
+    <t>Video: VideoLog Likelihood, Part 2</t>
+  </si>
+  <si>
+    <t>Reading: ReadingLog Likelihood Part 2</t>
+  </si>
+  <si>
+    <t>Video: VideoTraining Naïve Bayes</t>
+  </si>
+  <si>
+    <t>Reading: ReadingTraining naïve Bayes</t>
+  </si>
+  <si>
+    <t>Lab: Visualizing likelihoods and confidence ellipses</t>
+  </si>
+  <si>
+    <t>Video: VideoTesting Naïve Bayes</t>
+  </si>
+  <si>
+    <t>Reading: ReadingTesting naïve Bayes</t>
+  </si>
+  <si>
+    <t>Video: VideoApplications of Naïve Bayes</t>
+  </si>
+  <si>
+    <t>Reading: ReadingApplications of Naive Bayes</t>
+  </si>
+  <si>
+    <t>Video: VideoNaïve Bayes Assumptions</t>
+  </si>
+  <si>
+    <t>Reading: ReadingNaïve Bayes Assumptions</t>
+  </si>
+  <si>
+    <t>Video: VideoError Analysis</t>
+  </si>
+  <si>
+    <t>Reading: ReadingError Analysis</t>
+  </si>
+  <si>
+    <t>. Duration: 44 seconds44 sec</t>
+  </si>
+  <si>
+    <t>Reading: ReadingLecture Notes W2</t>
+  </si>
+  <si>
+    <t>Practice Assignment: Naive Bayes</t>
+  </si>
+  <si>
+    <t>Assignment: Naive Bayes</t>
+  </si>
+  <si>
+    <t>Programming Assignment: Naive Bayes</t>
+  </si>
+  <si>
+    <t>Lecture: Vector Space Models</t>
+  </si>
+  <si>
+    <t>. Duration: 47 seconds47 sec</t>
+  </si>
+  <si>
+    <t>Video: VideoVector Space Models</t>
+  </si>
+  <si>
+    <t>Reading: ReadingVector Space Models</t>
+  </si>
+  <si>
+    <t>Video: VideoWord by Word and Word by Doc.</t>
+  </si>
+  <si>
+    <t>Reading: ReadingWord by Word and Word by Doc.</t>
+  </si>
+  <si>
+    <t>Lab: Linear algebra in Python with Numpy</t>
+  </si>
+  <si>
+    <t>Video: VideoEuclidean Distance</t>
+  </si>
+  <si>
+    <t>Reading: ReadingEuclidian Distance</t>
+  </si>
+  <si>
+    <t>Video: VideoCosine Similarity: Intuition</t>
+  </si>
+  <si>
+    <t>Reading: ReadingCosine Similarity: Intuition</t>
+  </si>
+  <si>
+    <t>Video: VideoCosine Similarity</t>
+  </si>
+  <si>
+    <t>Reading: ReadingCosine Similarity</t>
+  </si>
+  <si>
+    <t>Video: VideoManipulating Words in Vector Spaces</t>
+  </si>
+  <si>
+    <t>Reading: ReadingManipulating Words in Vector Spaces</t>
+  </si>
+  <si>
+    <t>Lab: Manipulating word embeddings</t>
+  </si>
+  <si>
+    <t>Video: VideoVisualization and PCA</t>
+  </si>
+  <si>
+    <t>Reading: ReadingVisualization and PCA</t>
+  </si>
+  <si>
+    <t>Video: VideoPCA Algorithm</t>
+  </si>
+  <si>
+    <t>Reading: ReadingPCA algorithm</t>
+  </si>
+  <si>
+    <t>Lab: Another explanation about PCA</t>
+  </si>
+  <si>
+    <t>Reading: ReadingThe Rotation Matrix (Optional Reading)</t>
+  </si>
+  <si>
+    <t>. Duration: 46 seconds46 sec</t>
+  </si>
+  <si>
+    <t>Reading: ReadingLecture Notes W3</t>
+  </si>
+  <si>
+    <t>Practice Assignment: Vector Space Models</t>
+  </si>
+  <si>
+    <t>Assignment: Vector Space Models</t>
+  </si>
+  <si>
+    <t>Programming Assignment: Assignment: Vector Space Models</t>
+  </si>
+  <si>
+    <t>Lecture: Machine Translation</t>
+  </si>
+  <si>
+    <t>Video: VideoOverview</t>
+  </si>
+  <si>
+    <t>Video: VideoTransforming word vectors</t>
+  </si>
+  <si>
+    <t>Reading: ReadingTransforming word vectors</t>
+  </si>
+  <si>
+    <t>Lab: Rotation matrices in R2</t>
+  </si>
+  <si>
+    <t>Video: VideoK-nearest neighbors</t>
+  </si>
+  <si>
+    <t>Reading: ReadingK-nearest neighbors</t>
+  </si>
+  <si>
+    <t>Video: VideoHash tables and hash functions</t>
+  </si>
+  <si>
+    <t>Reading: ReadingHash tables and hash functions</t>
+  </si>
+  <si>
+    <t>Video: VideoLocality sensitive hashing</t>
+  </si>
+  <si>
+    <t>Reading: ReadingLocality sensitive hashing</t>
+  </si>
+  <si>
+    <t>Video: VideoMultiple Planes</t>
+  </si>
+  <si>
+    <t>Reading: ReadingMultiple Planes</t>
+  </si>
+  <si>
+    <t>Lab: Hash tables</t>
+  </si>
+  <si>
+    <t>Video: VideoApproximate nearest neighbors</t>
+  </si>
+  <si>
+    <t>Reading: ReadingApproximate nearest neighbors</t>
+  </si>
+  <si>
+    <t>Video: VideoSearching documents</t>
+  </si>
+  <si>
+    <t>Reading: ReadingSearching documents</t>
+  </si>
+  <si>
+    <t>. Duration: 50 seconds50 sec</t>
+  </si>
+  <si>
+    <t>Reading: ReadingLecture Notes W4</t>
+  </si>
+  <si>
+    <t>Practice Assignment: Hashing and Machine Translation</t>
+  </si>
+  <si>
+    <t>End of access to Lab Notebooks</t>
+  </si>
+  <si>
+    <t>Assignment: Machine Translation</t>
+  </si>
+  <si>
+    <t>Programming Assignment: Word Translation</t>
+  </si>
+  <si>
+    <t>Acknowledgments and Bibliography</t>
+  </si>
+  <si>
+    <t>Reading: ReadingAcknowledgements</t>
+  </si>
+  <si>
+    <t>Reading: ReadingBibliography</t>
+  </si>
+  <si>
+    <t>Heroes of NLP: Kathleen McKeown</t>
+  </si>
+  <si>
+    <t>Video: VideoAndrew Ng with Kathleen McKeown</t>
+  </si>
+  <si>
+    <t>. Duration: 35 minutes35 min</t>
+  </si>
+  <si>
+    <t>Lecture: Autocorrect and Minimum Edit Distance</t>
+  </si>
+  <si>
+    <t>Video: VideoIntro to Course 2</t>
+  </si>
+  <si>
+    <t>. Duration: 55 seconds55 sec</t>
+  </si>
+  <si>
+    <t>Reading: ReadingOverview</t>
+  </si>
+  <si>
+    <t>Video: VideoAutocorrect</t>
+  </si>
+  <si>
+    <t>Reading: ReadingAutocorrect</t>
+  </si>
+  <si>
+    <t>Video: VideoBuilding the model</t>
+  </si>
+  <si>
+    <t>Reading: ReadingBuilding the model</t>
+  </si>
+  <si>
+    <t>Lab: Lecture notebook: Building the vocabulary</t>
+  </si>
+  <si>
+    <t>Video: VideoBuilding the model II</t>
+  </si>
+  <si>
+    <t>Reading: ReadingBuilding the model II</t>
+  </si>
+  <si>
+    <t>Lab: Lecture notebook: Candidates from edits</t>
+  </si>
+  <si>
+    <t>Video: VideoMinimum edit distance</t>
+  </si>
+  <si>
+    <t>Reading: ReadingMinimum edit distance</t>
+  </si>
+  <si>
+    <t>Video: VideoMinimum edit distance algorithm</t>
+  </si>
+  <si>
+    <t>Reading: ReadingMinimum edit distance algorithm</t>
+  </si>
+  <si>
+    <t>Video: VideoMinimum edit distance algorithm II</t>
+  </si>
+  <si>
+    <t>Reading: ReadingMinimum edit distance algorithm II</t>
+  </si>
+  <si>
+    <t>Video: VideoMinimum edit distance algorithm III</t>
+  </si>
+  <si>
+    <t>Reading: ReadingMinimum edit distance III</t>
+  </si>
+  <si>
+    <t>Quiz: Auto-correct and Minimum Edit Distance</t>
+  </si>
+  <si>
+    <t>Practice Assignment: Auto-correct and Minimum Edit Distance</t>
+  </si>
+  <si>
+    <t>Assignment: Autocorrect</t>
+  </si>
+  <si>
+    <t>Programming Assignment: Autocorrect</t>
+  </si>
+  <si>
+    <t>Lecture: Part of Speech Tagging</t>
+  </si>
+  <si>
+    <t>Video: VideoPart of Speech Tagging</t>
+  </si>
+  <si>
+    <t>Reading: ReadingPart of Speech Tagging</t>
+  </si>
+  <si>
+    <t>Lab: Lecture Notebook - Working with text files</t>
+  </si>
+  <si>
+    <t>Video: VideoMarkov Chains</t>
+  </si>
+  <si>
+    <t>Reading: ReadingMarkov Chains</t>
+  </si>
+  <si>
+    <t>Video: VideoMarkov Chains and POS Tags</t>
+  </si>
+  <si>
+    <t>Reading: ReadingMarkov Chains and POS Tags</t>
+  </si>
+  <si>
+    <t>Video: VideoHidden Markov Models</t>
+  </si>
+  <si>
+    <t>Reading: ReadingHidden Markov Models</t>
+  </si>
+  <si>
+    <t>Video: VideoCalculating Probabilities</t>
+  </si>
+  <si>
+    <t>Reading: ReadingCalculating Probabilities</t>
+  </si>
+  <si>
+    <t>Video: VideoPopulating the Transition Matrix</t>
+  </si>
+  <si>
+    <t>Reading: ReadingPopulating the Transition Matrix</t>
+  </si>
+  <si>
+    <t>Video: VideoPopulating the Emission Matrix</t>
+  </si>
+  <si>
+    <t>Reading: ReadingPopulating the Emission Matrix</t>
+  </si>
+  <si>
+    <t>Lab: Lecture Notebook - Working with tags and Numpy</t>
+  </si>
+  <si>
+    <t>Video: VideoThe Viterbi Algorithm</t>
+  </si>
+  <si>
+    <t>Reading: ReadingThe Viterbi Algorithm</t>
+  </si>
+  <si>
+    <t>Video: VideoViterbi: Initialization</t>
+  </si>
+  <si>
+    <t>Reading: ReadingViterbi Initialization</t>
+  </si>
+  <si>
+    <t>Video: VideoViterbi: Forward Pass</t>
+  </si>
+  <si>
+    <t>Reading: ReadingViterbi: Forward Pass</t>
+  </si>
+  <si>
+    <t>Video: VideoViterbi: Backward Pass</t>
+  </si>
+  <si>
+    <t>Reading: ReadingViterbi: Backward Pass</t>
+  </si>
+  <si>
+    <t>Practice Assignment: Part of Speech Tagging</t>
+  </si>
+  <si>
+    <t>Assignment: Part of Speech Tagging</t>
+  </si>
+  <si>
+    <t>Programming Assignment: Part of Speech Tagging</t>
+  </si>
+  <si>
+    <t>Video: VideoWeek Introduction</t>
+  </si>
+  <si>
+    <t>. Duration: 1 minute1 min</t>
+  </si>
+  <si>
+    <t>Video: VideoOverview</t>
+  </si>
+  <si>
+    <t>. Duration: 2 minutes2 min</t>
+  </si>
+  <si>
+    <t>Reading: ReadingOverview</t>
+  </si>
+  <si>
+    <t>Video: VideoBasic Word Representations</t>
+  </si>
+  <si>
+    <t>. Duration: 3 minutes3 min</t>
+  </si>
+  <si>
+    <t>Reading: ReadingBasic Word Representations</t>
+  </si>
+  <si>
+    <t>. Duration: 5 minutes5 min</t>
+  </si>
+  <si>
+    <t>Video: VideoWord Embeddings</t>
+  </si>
+  <si>
+    <t>Reading: ReadingWord Embeddings</t>
+  </si>
+  <si>
+    <t>. Duration: 4 minutes4 min</t>
+  </si>
+  <si>
+    <t>Video: VideoHow to Create Word Embeddings</t>
+  </si>
+  <si>
+    <t>Reading: ReadingHow to Create Word Embeddings?</t>
+  </si>
+  <si>
+    <t>Video: VideoWord Embedding Methods</t>
+  </si>
+  <si>
+    <t>Reading: ReadingWord Embedding Methods</t>
+  </si>
+  <si>
+    <t>Video: VideoContinuous Bag-of-Words Model</t>
+  </si>
+  <si>
+    <t>Reading: ReadingContinuous Bag of Words Model</t>
+  </si>
+  <si>
+    <t>Video: VideoCleaning and Tokenization</t>
+  </si>
+  <si>
+    <t>Reading: ReadingCleaning and Tokenization</t>
+  </si>
+  <si>
+    <t>Video: VideoSliding Window of Words in Python</t>
+  </si>
+  <si>
+    <t>Reading: ReadingSliding Window of words in Python</t>
+  </si>
+  <si>
+    <t>. Duration: 10 minutes10 min</t>
+  </si>
+  <si>
+    <t>Video: VideoTransforming Words into Vectors</t>
+  </si>
+  <si>
+    <t>Reading: ReadingTransforming Words into Vectors</t>
+  </si>
+  <si>
+    <t>Lab: Lecture Notebook - Data Preparation</t>
+  </si>
+  <si>
+    <t>. Duration: 30 minutes30 min</t>
+  </si>
+  <si>
+    <t>Video: VideoArchitecture of the CBOW Model</t>
+  </si>
+  <si>
+    <t>Reading: ReadingArchitecture for the CBOW Model</t>
+  </si>
+  <si>
+    <t>Video: VideoArchitecture of the CBOW Model: Dimensions</t>
+  </si>
+  <si>
+    <t>Reading: ReadingArchitecture of the CBOW Model: Dimensions</t>
+  </si>
+  <si>
+    <t>Video: VideoArchitecture of the CBOW Model: Dimensions 2</t>
+  </si>
+  <si>
+    <t>Video: VideoArchitecture of the CBOW Model: Activation Functions</t>
+  </si>
+  <si>
+    <t>Reading: ReadingArchitecture of the CBOW Model: Activation Functions</t>
+  </si>
+  <si>
+    <t>Lab: Lecture Notebook - Intro to CBOW model</t>
+  </si>
+  <si>
+    <t>Video: VideoTraining a CBOW Model: Cost Function</t>
+  </si>
+  <si>
+    <t>Reading: ReadingTraining a CBOW Model: Cost Function</t>
+  </si>
+  <si>
+    <t>Video: VideoTraining a CBOW Model: Forward Propagation</t>
+  </si>
+  <si>
+    <t>Reading: ReadingTraining a CBOW Model: Forward Propagation</t>
+  </si>
+  <si>
+    <t>Video: VideoTraining a CBOW Model: Backpropagation and Gradient Descent</t>
+  </si>
+  <si>
+    <t>Reading: ReadingTraining a CBOW Model: Backpropagation and Gradient Descent</t>
+  </si>
+  <si>
+    <t>Lab: Lecture Notebook - Training the CBOW model</t>
+  </si>
+  <si>
+    <t>. Duration: 40 minutes40 min</t>
+  </si>
+  <si>
+    <t>Video: VideoExtracting Word Embedding Vectors</t>
+  </si>
+  <si>
+    <t>Reading: ReadingExtracting Word Embedding Vectors</t>
+  </si>
+  <si>
+    <t>Lab: Lecture Notebook - Word Embeddings</t>
+  </si>
+  <si>
+    <t>. Duration: 20 minutes20 min</t>
+  </si>
+  <si>
+    <t>Video: VideoEvaluating Word Embeddings: Intrinsic Evaluation</t>
+  </si>
+  <si>
+    <t>Reading: ReadingEvaluating Word Embeddings: Intrinsic Evaluation</t>
+  </si>
+  <si>
+    <t>Video: VideoEvaluating Word Embeddings: Extrinsic Evaluation</t>
+  </si>
+  <si>
+    <t>Reading: ReadingEvaluating Word Embeddings: Extrinsic Evaluation</t>
+  </si>
+  <si>
+    <t>Lab: Lecture notebook: Word embeddings step by step</t>
+  </si>
+  <si>
+    <t>. Duration: 1 hour1h</t>
+  </si>
+  <si>
+    <t>Video: VideoConclusion</t>
+  </si>
+  <si>
+    <t>Reading: ReadingConclusion</t>
+  </si>
+  <si>
+    <t>Video: VideoWeek Conclusion</t>
+  </si>
+  <si>
+    <t>. Duration: 45 seconds45 sec</t>
+  </si>
+  <si>
+    <t>Reading: ReadingLecture Notes W4</t>
+  </si>
+  <si>
+    <t>Practice Assignment: Word Embeddings</t>
+  </si>
+  <si>
+    <t>Reading: Reading[IMPORTANT] Reminder about end of access to Lab Notebooks</t>
+  </si>
+  <si>
+    <t>Programming Assignment: Word Embeddings</t>
+  </si>
+  <si>
+    <t>. Duration: 3 hours3h</t>
+  </si>
+  <si>
+    <t>Reading: ReadingAcknowledgments</t>
+  </si>
+  <si>
+    <t>Lecture: Word Embedding</t>
+  </si>
+  <si>
+    <t>Video: VideoCourse 3 Introduction</t>
+  </si>
+  <si>
+    <t>Video: VideoLesson Introduction</t>
+  </si>
+  <si>
+    <t>. Duration: 44 seconds44 sec</t>
+  </si>
+  <si>
+    <t>Reading: ReadingLesson Introduction Clarification</t>
+  </si>
+  <si>
+    <t>Video: VideoNeural Networks for Sentiment Analysis</t>
+  </si>
+  <si>
+    <t>Reading: ReadingNeural Networks for Sentiment Analysis</t>
+  </si>
+  <si>
+    <t>. Duration: 7 minutes7 min</t>
+  </si>
+  <si>
+    <t>Video: VideoDense Layers and ReLU</t>
+  </si>
+  <si>
+    <t>Reading: ReadingDense Layers and ReLU</t>
+  </si>
+  <si>
+    <t>Video: VideoEmbedding and Mean Layers</t>
+  </si>
+  <si>
+    <t>Reading: ReadingEmbedding and Mean Layers</t>
+  </si>
+  <si>
+    <t>Lab: Introduction to TensorFlow</t>
+  </si>
+  <si>
+    <t>Ungraded App Item: Ungraded App Item[IMPORTANT] Have questions, issues or ideas? Join our community on Discourse!</t>
+  </si>
+  <si>
+    <t>Reading: Reading(Optional) Downloading your Notebook, Downloading your Workspace and Refreshing your Workspace</t>
+  </si>
+  <si>
+    <t>Practice Programming Assignment: Sentiment with Deep Neural Networks</t>
+  </si>
+  <si>
+    <t>. Duration: 49 seconds49 sec</t>
+  </si>
+  <si>
+    <t>Video: VideoTraditional Language models</t>
+  </si>
+  <si>
+    <t>Reading: ReadingTraditional Language models</t>
+  </si>
+  <si>
+    <t>Video: VideoRecurrent Neural Networks</t>
+  </si>
+  <si>
+    <t>Reading: ReadingRecurrent Neural Networks</t>
+  </si>
+  <si>
+    <t>Video: VideoApplications of RNNs</t>
+  </si>
+  <si>
+    <t>Reading: ReadingApplication of RNNs</t>
+  </si>
+  <si>
+    <t>Video: VideoMath in Simple RNNs</t>
+  </si>
+  <si>
+    <t>Reading: ReadingMath in Simple RNNs</t>
+  </si>
+  <si>
+    <t>. Duration: 6 minutes6 min</t>
+  </si>
+  <si>
+    <t>Lab: Hidden State Activation</t>
+  </si>
+  <si>
+    <t>Video: VideoCost Function for RNNs</t>
+  </si>
+  <si>
+    <t>Reading: ReadingCost Function for RNNs</t>
+  </si>
+  <si>
+    <t>Video: VideoImplementation Note</t>
+  </si>
+  <si>
+    <t>Reading: ReadingImplementation Note</t>
+  </si>
+  <si>
+    <t>Video: VideoGated Recurrent Units</t>
+  </si>
+  <si>
+    <t>Reading: ReadingGated Recurrent Units</t>
+  </si>
+  <si>
+    <t>Lab: Vanilla RNNs, GRUs and the scan function</t>
+  </si>
+  <si>
+    <t>Video: VideoDeep and Bi-directional RNNs</t>
+  </si>
+  <si>
+    <t>Reading: ReadingDeep and Bi-directional RNNs</t>
+  </si>
+  <si>
+    <t>Reading: ReadingCalculating Perplexity</t>
+  </si>
+  <si>
+    <t>Lab: Calculating Perplexity</t>
+  </si>
+  <si>
+    <t>. Duration: 57 seconds57 sec</t>
+  </si>
+  <si>
+    <t>Reading: ReadingLecture Notes W1</t>
+  </si>
+  <si>
+    <t>Practice Assignment: RNNs for Language Modelling</t>
+  </si>
+  <si>
+    <t>Programming Assignment: Deep N-grams</t>
+  </si>
+  <si>
+    <t>1. Natural Language Processing with Sequence Models</t>
+  </si>
+  <si>
+    <t>1. Course 3 Introduction</t>
+  </si>
+  <si>
+    <t>0:07 / 3:26</t>
+  </si>
+  <si>
+    <t>Course 3 Introduction</t>
+  </si>
+  <si>
+    <t>Interactive Transcript - Enable basic transcript mode by pressing the escape key</t>
+  </si>
+  <si>
+    <t>You may navigate through the transcript using tab. To save a note for a section of text press CTRL + S. To expand your selection you may use CTRL + arrow key. You may contract your selection using shift + CTRL + arrow key. For screen readers that are incompatible with using arrow keys for shortcuts, you can replace them with the H J K L keys. Some screen readers may require using CTRL in conjunction with the alt key</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Welcome to the third course of this specialization. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">This course is called Natural </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Language Processing with Sequence Models. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">In this course, here are some things you get to build. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">First, you take sentiment analysis </t>
+  </si>
+  <si>
+    <t xml:space="preserve">to the next level with deep neuron networks. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">You also build a language generator </t>
+  </si>
+  <si>
+    <t xml:space="preserve">using RNNs or recurrent neuron networks. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">You apply LSTM units. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LSTM stands for Long Short-Term Memory. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">You apply LSTM units to </t>
+  </si>
+  <si>
+    <t xml:space="preserve">the problem of named entity recognition. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finally, you use </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siamese networks to identify duplicate questions. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Like say if there's an online discussion forum </t>
+  </si>
+  <si>
+    <t xml:space="preserve">and different people are asking questions, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">can you figure out if two different people </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ask essentially the same question, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">but with different wording? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">With the skills you develop in this course, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">you'll be able to build powerful NLP systems to </t>
+  </si>
+  <si>
+    <t xml:space="preserve">solve problems across a wide range of industries. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">It is my pleasure to welcome Lucasz </t>
+  </si>
+  <si>
+    <t xml:space="preserve">and Younes as your instructors for this course, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">and they are thrilled to dive into these topics with you. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Younes, perhaps you could say a bit more about </t>
+  </si>
+  <si>
+    <t xml:space="preserve">the applications that learners will build in this course? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sure thing, thanks Andrew. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Well, I'd like to start by saying </t>
+  </si>
+  <si>
+    <t xml:space="preserve">that in the first two courses of this specialization, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">you built a powerful foundation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">that will provide you with </t>
+  </si>
+  <si>
+    <t xml:space="preserve">both the context and </t>
+  </si>
+  <si>
+    <t xml:space="preserve">the fundamental skills you need to tackle this course. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">For example, you've already </t>
+  </si>
+  <si>
+    <t xml:space="preserve">done sentiment analysis in Course 1, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">with a simple naive bayes classifier. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">But now you, will leverage the power of </t>
+  </si>
+  <si>
+    <t xml:space="preserve">deep neural networks to build </t>
+  </si>
+  <si>
+    <t xml:space="preserve">a much more robust sentiment analysis classifier. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">You've also seen how to do </t>
+  </si>
+  <si>
+    <t xml:space="preserve">things like predict the next word in </t>
+  </si>
+  <si>
+    <t xml:space="preserve">a sequence using </t>
+  </si>
+  <si>
+    <t xml:space="preserve">relatively simple n-gram language models in Course 2. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">In this course, you'll create </t>
+  </si>
+  <si>
+    <t xml:space="preserve">an advanced model using </t>
+  </si>
+  <si>
+    <t xml:space="preserve">recurrent neural networks to generate texts. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">You can think of this course as taking the step from </t>
+  </si>
+  <si>
+    <t xml:space="preserve">foundational skills into building </t>
+  </si>
+  <si>
+    <t xml:space="preserve">real world NLP applications. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Very cool, Younes. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">I think that's a great way to think about it. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lucasz, maybe you could say a bit </t>
+  </si>
+  <si>
+    <t xml:space="preserve">more about the applications learners will get to build? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sure. Thank you, Andrew. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Well, as you saw in the first course, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">the problem of sentiment analysis is a really tricky one. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">But in many applications, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">you want to determine the sentiment of a sentence, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">so it's a really good problem to work on as well. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">With language modeling, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">the problems you can solve are almost infinite. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">From translation to autocomplete, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">to generating text from scratch. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">In Week 2 of this course, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">you'll work on named Entity Recognition, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">which is the problem of separating named entity </t>
+  </si>
+  <si>
+    <t xml:space="preserve">in sentences like people and places. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is a building block of many important NLP systems. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finally, in Week 3 of this course, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">we will tackle the problem of identifying duplicates. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The question of whether two pieces of texts or </t>
+  </si>
+  <si>
+    <t xml:space="preserve">duplicates of each other might </t>
+  </si>
+  <si>
+    <t xml:space="preserve">not sound very interesting at first, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">but as you'll see, it's actually </t>
+  </si>
+  <si>
+    <t xml:space="preserve">core building block of things like </t>
+  </si>
+  <si>
+    <t xml:space="preserve">online forms and search engines, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">and we'll show you how to solve it. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">We're really excited to show you </t>
+  </si>
+  <si>
+    <t xml:space="preserve">these applications and bring </t>
+  </si>
+  <si>
+    <t xml:space="preserve">your skills to the next level. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thank you, Lucasz and thank you, Younes. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is going to be an exciting course. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Let's get started. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good luck. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Have fun. </t>
+  </si>
+  <si>
+    <t>​</t>
+  </si>
+  <si>
+    <t>Share</t>
+  </si>
+  <si>
+    <t>Introduction to Neural Networks and Tensflow</t>
+  </si>
+  <si>
+    <t>LSTMs and Named Entity Recognition</t>
+  </si>
+  <si>
+    <t>Video: VideoRNNs and Vanishing Gradients</t>
+  </si>
+  <si>
+    <t>Reading: ReadingRNNs and Vanishing Gradients</t>
+  </si>
+  <si>
+    <t>Reading: Reading(Optional) Intro to optimization in deep learning: Gradient Descent</t>
+  </si>
+  <si>
+    <t>Lab: Vanishing Gradients</t>
+  </si>
+  <si>
+    <t>Video: VideoIntroduction to LSTMs</t>
+  </si>
+  <si>
+    <t>Reading: ReadingIntroduction to LSTMs</t>
+  </si>
+  <si>
+    <t>Video: VideoLSTM Architecture</t>
+  </si>
+  <si>
+    <t>Reading: ReadingLSTM Architecture</t>
+  </si>
+  <si>
+    <t>Video: VideoIntroduction to Named Entity Recognition</t>
+  </si>
+  <si>
+    <t>Reading: ReadingIntroduction to Named Entity Recognition</t>
+  </si>
+  <si>
+    <t>Video: VideoTraining NERs: Data Processing</t>
+  </si>
+  <si>
+    <t>Reading: ReadingTraining NERs: Data Processing</t>
+  </si>
+  <si>
+    <t>Reading: ReadingLong Short-Term Memory (Deep Learning Specialization C5)</t>
+  </si>
+  <si>
+    <t>Video: VideoComputing Accuracy</t>
+  </si>
+  <si>
+    <t>Reading: ReadingComputing Accuracy</t>
+  </si>
+  <si>
+    <t>Practice Assignment: LSTMs and Named Entity Recognition</t>
+  </si>
+  <si>
+    <t>Assignment: Named Entity Recognition (NER)</t>
+  </si>
+  <si>
+    <t>Programming Assignment: Named Entity Recognition (NER)</t>
+  </si>
+  <si>
+    <t>Siamese Networks</t>
+  </si>
+  <si>
+    <t>Video: VideoSiamese Networks</t>
+  </si>
+  <si>
+    <t>Reading: ReadingSiamese Network</t>
+  </si>
+  <si>
+    <t>Video: VideoArchitecture</t>
+  </si>
+  <si>
+    <t>Reading: ReadingArchitecture</t>
+  </si>
+  <si>
+    <t>Lab: Creating a Siamese Model</t>
+  </si>
+  <si>
+    <t>Video: VideoCost Function</t>
+  </si>
+  <si>
+    <t>Reading: ReadingCost Function</t>
+  </si>
+  <si>
+    <t>Video: VideoTriplets</t>
+  </si>
+  <si>
+    <t>Reading: ReadingTriplets</t>
+  </si>
+  <si>
+    <t>Video: VideoComputing The Cost I</t>
+  </si>
+  <si>
+    <t>Reading: ReadingComputing the Cost I</t>
+  </si>
+  <si>
+    <t>Video: VideoComputing The Cost II</t>
+  </si>
+  <si>
+    <t>Reading: ReadingComputing the Cost II</t>
+  </si>
+  <si>
+    <t>Lab: Implementing the Modified Triplet Loss in TensorFlow</t>
+  </si>
+  <si>
+    <t>Video: VideoOne Shot Learning</t>
+  </si>
+  <si>
+    <t>Reading: ReadingOne Shot Learning</t>
+  </si>
+  <si>
+    <t>Video: VideoTraining / Testing</t>
+  </si>
+  <si>
+    <t>Reading: ReadingTraining / Testing</t>
+  </si>
+  <si>
+    <t>Lab: Evaluate a Siamese Model</t>
+  </si>
+  <si>
+    <t>. Duration: 37 seconds37 sec</t>
+  </si>
+  <si>
+    <t>Practice Assignment: Siamese Networks</t>
+  </si>
+  <si>
+    <t>Assignment: Question Duplicates</t>
+  </si>
+  <si>
+    <t>Programming Assignment: Question Duplicates</t>
+  </si>
+  <si>
+    <t>Neural Machine Translation</t>
+  </si>
+  <si>
+    <t>Video: VideoCourse 4 Introduction</t>
+  </si>
+  <si>
+    <t>Video: VideoSeq2seq</t>
+  </si>
+  <si>
+    <t>Video: VideoSeq2seq Model with Attention</t>
+  </si>
+  <si>
+    <t>Lab: Ungraded Lab: Basic Attention</t>
+  </si>
+  <si>
+    <t>Reading: ReadingBackground on seq2seq</t>
+  </si>
+  <si>
+    <t>Video: VideoQueries, Keys, Values, and Attention</t>
+  </si>
+  <si>
+    <t>Lab: Ungraded Lab: Scaled Dot-Product Attention</t>
+  </si>
+  <si>
+    <t>Video: VideoSetup for Machine Translation</t>
+  </si>
+  <si>
+    <t>Video: VideoTeacher Forcing</t>
+  </si>
+  <si>
+    <t>Video: VideoNMT Model with Attention</t>
+  </si>
+  <si>
+    <t>Video: VideoBLEU Score</t>
+  </si>
+  <si>
+    <t>Lab: Ungraded Lab: BLEU Score</t>
+  </si>
+  <si>
+    <t>Video: VideoROUGE-N Score</t>
+  </si>
+  <si>
+    <t>Video: VideoSampling and Decoding</t>
+  </si>
+  <si>
+    <t>Video: VideoBeam Search</t>
+  </si>
+  <si>
+    <t>Video: VideoMinimum Bayes Risk</t>
+  </si>
+  <si>
+    <t>. Duration: 52 seconds52 sec</t>
+  </si>
+  <si>
+    <t>Reading: ReadingContent Resource</t>
+  </si>
+  <si>
+    <t>Ungraded App Item: Ungraded App Item[IMPORTANT] Have questions, issues or ideas? Join our Community!</t>
+  </si>
+  <si>
+    <t>Lecture Notes (Notes)</t>
+  </si>
+  <si>
+    <t>Practice Assignment: Neural Machine Translation</t>
+  </si>
+  <si>
+    <t>Assignment</t>
+  </si>
+  <si>
+    <t>Programming Assignment: NMT with Attention (Tensorflow)</t>
+  </si>
+  <si>
+    <t>Heroes of NLP: Oren Etzioni</t>
+  </si>
+  <si>
+    <t>Video: VideoAndrew Ng with Oren Etzioni</t>
+  </si>
+  <si>
+    <t>. Duration: 34 minutes34 min</t>
+  </si>
 </sst>
 </file>
 
@@ -1608,7 +3170,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yy;@"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1691,6 +3253,51 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0F1114"/>
+      <name val="Source Sans Pro"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0F1114"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1719,7 +3326,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1776,6 +3383,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1792,6 +3422,65 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/activeX/activeX1.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D11A-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>1465</xdr:colOff>
+          <xdr:row>390</xdr:row>
+          <xdr:rowOff>24179</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>1192090</xdr:colOff>
+          <xdr:row>391</xdr:row>
+          <xdr:rowOff>128954</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1025" name="Control 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1025"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2110,6 +3799,4866 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED28FC12-FCE5-4FD3-B40B-D96785393966}">
+  <dimension ref="A1:I150"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" style="18" customWidth="1"/>
+    <col min="2" max="2" width="8.140625" style="21" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" style="19" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" style="19" customWidth="1"/>
+    <col min="5" max="5" width="69.7109375" style="19" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" style="18" customWidth="1"/>
+    <col min="7" max="7" width="35" style="19" customWidth="1"/>
+    <col min="8" max="8" width="3.5703125" style="19" customWidth="1"/>
+    <col min="9" max="9" width="46.5703125" style="19" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="19"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="15" customFormat="1" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="16" t="s">
+        <v>386</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>387</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>394</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>386</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>388</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="18">
+        <v>45650</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="18">
+        <v>45650</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B7" s="21">
+        <v>2</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>397</v>
+      </c>
+      <c r="I7" s="19" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E8" s="19" t="s">
+        <v>395</v>
+      </c>
+      <c r="I8" s="23" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E9" s="19" t="s">
+        <v>396</v>
+      </c>
+      <c r="I9" s="23" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="18">
+        <v>45650</v>
+      </c>
+      <c r="B12" s="21">
+        <v>3</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D13" s="19" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E14" s="19" t="s">
+        <v>400</v>
+      </c>
+      <c r="I14" s="19" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E15" s="19" t="s">
+        <v>402</v>
+      </c>
+      <c r="I15" s="19" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E16" s="19" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="18">
+        <v>45650</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B20" s="21">
+        <v>2</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E21" s="19" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E22" s="19" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E23" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I23" s="19" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="18">
+        <v>45650</v>
+      </c>
+      <c r="B26" s="21">
+        <v>3</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D27" s="19" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E28" s="19" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E29" s="19" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E30" s="19" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E31" s="19" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="18">
+        <v>45651</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B35" s="21">
+        <v>2</v>
+      </c>
+      <c r="D35" s="19" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E36" s="19" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E37" s="19" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E38" s="19" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="18">
+        <v>45652</v>
+      </c>
+      <c r="C43" s="17" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B44" s="21">
+        <v>1</v>
+      </c>
+      <c r="D44" s="19" t="s">
+        <v>446</v>
+      </c>
+      <c r="F44" s="18">
+        <v>45652</v>
+      </c>
+      <c r="G44" s="19" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E45" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="G45" s="19" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E46" s="19" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E47" s="19" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E48" s="19" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="18">
+        <v>45653</v>
+      </c>
+      <c r="B49" s="21">
+        <v>2</v>
+      </c>
+      <c r="D49" s="19" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E50" s="19" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E51" s="19" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E52" s="19" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E53" s="19" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E54" s="19" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E55" s="19" t="s">
+        <v>458</v>
+      </c>
+      <c r="F55" s="18">
+        <v>45653</v>
+      </c>
+      <c r="G55" s="19" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E56" s="19" t="s">
+        <v>457</v>
+      </c>
+      <c r="F56" s="18">
+        <v>45653</v>
+      </c>
+      <c r="G56" s="19" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="18">
+        <v>45654</v>
+      </c>
+      <c r="B59" s="21">
+        <v>3</v>
+      </c>
+      <c r="D59" s="19" t="s">
+        <v>305</v>
+      </c>
+      <c r="F59" s="18">
+        <v>45656</v>
+      </c>
+      <c r="G59" s="19" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E60" s="19" t="s">
+        <v>461</v>
+      </c>
+      <c r="G60" s="19" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E61" s="19" t="s">
+        <v>462</v>
+      </c>
+      <c r="G61" s="19" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E62" s="19" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E63" s="19" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E64" s="19" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="18">
+        <v>45657</v>
+      </c>
+      <c r="B67" s="21">
+        <v>4</v>
+      </c>
+      <c r="D67" s="19" t="s">
+        <v>347</v>
+      </c>
+      <c r="F67" s="18">
+        <v>45658</v>
+      </c>
+      <c r="G67" s="19" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E68" s="19" t="s">
+        <v>470</v>
+      </c>
+      <c r="F68" s="18">
+        <v>45663</v>
+      </c>
+      <c r="G68" s="19" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E69" s="19" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E70" s="19" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E71" s="19" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E72" s="19" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E73" s="19" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E74" s="19" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="18">
+        <v>45663</v>
+      </c>
+      <c r="C77" s="17" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B78" s="21">
+        <v>1</v>
+      </c>
+      <c r="D78" s="19" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E79" s="19" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E80" s="19" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E81" s="19" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E82" s="19" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="18">
+        <v>45664</v>
+      </c>
+      <c r="B84" s="21">
+        <v>2</v>
+      </c>
+      <c r="D84" s="19" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E85" s="19" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E86" s="19" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E87" s="19" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E88" s="19" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E89" s="19" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E90" s="19" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E91" s="19" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E92" s="19" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E93" s="19" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E94" s="19" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="18">
+        <v>45665</v>
+      </c>
+      <c r="B95" s="21">
+        <v>2</v>
+      </c>
+      <c r="D95" s="19" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E96" s="19" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E97" s="19" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E98" s="19" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E99" s="19" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E100" s="19" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E101" s="19" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="18">
+        <v>45665</v>
+      </c>
+      <c r="B102" s="21">
+        <v>3</v>
+      </c>
+      <c r="D102" s="19" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E103" s="19" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E104" s="19" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E105" s="24" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E106" s="19" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E107" s="19" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E108" s="19" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E109" s="19" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E110" s="19" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E111" s="19" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="18">
+        <v>45666</v>
+      </c>
+      <c r="B112" s="21">
+        <v>4</v>
+      </c>
+      <c r="D112" s="19" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E113" s="19" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E114" s="19" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E115" s="19" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E116" s="19" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E117" s="19" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E118" s="19" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E119" s="19" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E120" s="19" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" s="18">
+        <v>45667</v>
+      </c>
+      <c r="C123" s="17" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B124" s="21">
+        <v>1</v>
+      </c>
+      <c r="D124" s="19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E125" s="19" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E126" s="19" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E127" s="19" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E128" s="19" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E129" s="19" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E130" s="19" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E131" s="19" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E132" s="19" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E133" s="19" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E134" s="19" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E135" s="19" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E136" s="19" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" s="18">
+        <v>45669</v>
+      </c>
+      <c r="B137" s="21">
+        <v>2</v>
+      </c>
+      <c r="D137" s="19" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E138" s="17" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E139" s="19" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E140" s="19" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E141" s="19" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E142" s="19" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" s="18">
+        <v>12</v>
+      </c>
+      <c r="B143" s="21">
+        <v>2</v>
+      </c>
+      <c r="E143" s="17" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E144" s="19" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E145" s="19" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E146" s="19" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E147" s="19" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" s="18">
+        <v>45669</v>
+      </c>
+      <c r="B148" s="21">
+        <v>2</v>
+      </c>
+      <c r="E148" s="17" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E149" s="19" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E150" s="19" t="s">
+        <v>588</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I8" r:id="rId1" display="https://www.coursera.org/learn/convolutional-neural-networks/lecture/4THzO/transfer-learning" xr:uid="{B9121CC7-7813-4873-864A-8369867402F8}"/>
+    <hyperlink ref="I9" r:id="rId2" display="https://www.coursera.org/learn/convolutional-neural-networks/lecture/AYzbX/data-augmentation" xr:uid="{2B7168BD-CD28-4234-9D63-C3228459BEC1}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1BE478C-F386-4978-A4BA-E19A14F77B4C}">
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="B1:H459"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="71" customWidth="1"/>
+    <col min="4" max="4" width="65.7109375" customWidth="1"/>
+    <col min="6" max="6" width="79.7109375" customWidth="1"/>
+    <col min="8" max="8" width="62.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="10" t="s">
+        <v>538</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>589</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>619</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="H2" s="11"/>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B3" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>542</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>542</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>590</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>620</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B5" s="12" t="s">
+        <v>540</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>591</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>621</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B7" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>592</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>622</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B8" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B9" s="12" t="s">
+        <v>542</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>593</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>623</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B10" s="12" t="s">
+        <v>543</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B11" s="12" t="s">
+        <v>544</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>594</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>624</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B12" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B13" s="12" t="s">
+        <v>545</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>595</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>625</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B14" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="12" t="s">
+        <v>546</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>626</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="12" t="s">
+        <v>547</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>597</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>627</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="12" t="s">
+        <v>548</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>598</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>628</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="12" t="s">
+        <v>549</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>599</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>629</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H22" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="12" t="s">
+        <v>550</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>600</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>630</v>
+      </c>
+      <c r="H23" s="12" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="H24" s="12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="12" t="s">
+        <v>551</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>601</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>631</v>
+      </c>
+      <c r="H25" s="12" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H26" s="12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="12" t="s">
+        <v>552</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>602</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>632</v>
+      </c>
+      <c r="H27" s="12" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="H28" s="12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="12" t="s">
+        <v>553</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>603</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>633</v>
+      </c>
+      <c r="H29" s="12" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H30" s="12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="12" t="s">
+        <v>554</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>604</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>634</v>
+      </c>
+      <c r="H31" s="12" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="H32" s="12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="12" t="s">
+        <v>555</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>605</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>635</v>
+      </c>
+      <c r="H33" s="12" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="H34" s="12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="12" t="s">
+        <v>556</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>606</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>636</v>
+      </c>
+      <c r="H35" s="12" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H36" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B37" s="12" t="s">
+        <v>557</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>607</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>637</v>
+      </c>
+      <c r="H37" s="12" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B38" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="H38" s="12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B39" s="12" t="s">
+        <v>558</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>608</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>638</v>
+      </c>
+      <c r="H39" s="12" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H40" s="12" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B41" s="12" t="s">
+        <v>559</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>609</v>
+      </c>
+      <c r="F41" s="12" t="s">
+        <v>639</v>
+      </c>
+      <c r="H41" s="10" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B42" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F42" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="H42" s="11"/>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B43" s="12" t="s">
+        <v>560</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>610</v>
+      </c>
+      <c r="F43" s="12" t="s">
+        <v>640</v>
+      </c>
+      <c r="H43" s="12" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B44" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="F44" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H44" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B45" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="F45" s="12" t="s">
+        <v>566</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B46" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F46" s="12" t="s">
+        <v>641</v>
+      </c>
+      <c r="H46" s="11"/>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B47" s="12" t="s">
+        <v>562</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="H47" s="12" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B48" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="F48" s="11"/>
+      <c r="H48" s="12" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B49" s="12" t="s">
+        <v>563</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>613</v>
+      </c>
+      <c r="F49" s="12" t="s">
+        <v>642</v>
+      </c>
+      <c r="H49" s="10" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B50" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F50" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="H50" s="11"/>
+    </row>
+    <row r="51" spans="2:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="B51" s="12" t="s">
+        <v>564</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>566</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="H51" s="12" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B52" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>614</v>
+      </c>
+      <c r="F52" s="11"/>
+      <c r="H52" s="12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B53" s="12" t="s">
+        <v>565</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="F53" s="12" t="s">
+        <v>643</v>
+      </c>
+      <c r="H53" s="10" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B54" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="D54" s="11"/>
+      <c r="F54" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="H54" s="11"/>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B55" s="12" t="s">
+        <v>566</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>615</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>644</v>
+      </c>
+      <c r="H55" s="12" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B56" s="12" t="s">
+        <v>567</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F56" s="11"/>
+      <c r="H56" s="12" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B57" s="12" t="s">
+        <v>568</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="F57" s="12" t="s">
+        <v>645</v>
+      </c>
+      <c r="H57" s="10" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B58" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="D58" s="11"/>
+      <c r="F58" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="H58" s="11"/>
+    </row>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B59" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>616</v>
+      </c>
+      <c r="H59" s="12" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B60" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="H60" s="12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="B61" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="D61" s="10" t="s">
+        <v>617</v>
+      </c>
+      <c r="H61" s="12" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B62" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D62" s="11"/>
+      <c r="H62" s="12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B63" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>618</v>
+      </c>
+      <c r="H63" s="10" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B64" s="11"/>
+      <c r="D64" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="H64" s="11"/>
+    </row>
+    <row r="65" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B65" s="12" t="s">
+        <v>569</v>
+      </c>
+      <c r="H65" s="12" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="66" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B66" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="H66" s="12" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="67" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B67" s="10" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="68" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B68" s="11"/>
+    </row>
+    <row r="69" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B69" s="12" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="70" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B70" s="12" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="71" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B71" s="10" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="72" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B72" s="11"/>
+    </row>
+    <row r="73" spans="2:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="B73" s="12" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="74" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B74" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="75" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B75" s="12" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="76" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B76" s="12" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="77" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B77" s="10" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="78" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B78" s="11"/>
+    </row>
+    <row r="79" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B79" s="12" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="80" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B80" s="12" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="83" spans="2:6" s="14" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="2:6" s="14" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="2:6" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B87" s="25" t="s">
+        <v>676</v>
+      </c>
+      <c r="D87" s="25" t="s">
+        <v>700</v>
+      </c>
+      <c r="F87" s="27" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="88" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B88" s="26"/>
+      <c r="D88" s="26"/>
+      <c r="F88" s="23" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="89" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B89" s="12" t="s">
+        <v>677</v>
+      </c>
+      <c r="D89" s="12" t="s">
+        <v>542</v>
+      </c>
+      <c r="F89" s="23" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="90" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B90" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D90" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F90" s="23" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="91" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B91" s="12" t="s">
+        <v>542</v>
+      </c>
+      <c r="D91" s="12" t="s">
+        <v>701</v>
+      </c>
+      <c r="F91" s="23" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="92" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B92" s="12" t="s">
+        <v>678</v>
+      </c>
+      <c r="D92" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F92" s="23" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="93" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B93" s="12" t="s">
+        <v>647</v>
+      </c>
+      <c r="D93" s="12" t="s">
+        <v>702</v>
+      </c>
+      <c r="F93" s="23" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="94" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B94" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D94" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F94" s="23" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="95" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B95" s="12" t="s">
+        <v>679</v>
+      </c>
+      <c r="D95" s="12" t="s">
+        <v>703</v>
+      </c>
+      <c r="F95" s="23" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="96" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B96" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D96" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="F96" s="23" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="97" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B97" s="12" t="s">
+        <v>680</v>
+      </c>
+      <c r="D97" s="12" t="s">
+        <v>704</v>
+      </c>
+      <c r="F97" s="23" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B98" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D98" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="F98" s="23" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="99" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B99" s="12" t="s">
+        <v>681</v>
+      </c>
+      <c r="D99" s="12" t="s">
+        <v>705</v>
+      </c>
+      <c r="F99" s="23" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="100" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B100" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D100" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="F100" s="23" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="101" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B101" s="12" t="s">
+        <v>682</v>
+      </c>
+      <c r="D101" s="12" t="s">
+        <v>706</v>
+      </c>
+      <c r="F101" s="23" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="102" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B102" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D102" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F102" s="23" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="103" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B103" s="12" t="s">
+        <v>683</v>
+      </c>
+      <c r="D103" s="12" t="s">
+        <v>707</v>
+      </c>
+      <c r="F103" s="23" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="104" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B104" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D104" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F104" s="23" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B105" s="12" t="s">
+        <v>684</v>
+      </c>
+      <c r="D105" s="12" t="s">
+        <v>708</v>
+      </c>
+      <c r="F105" s="23" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="106" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B106" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D106" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="F106" s="23" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="107" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B107" s="12" t="s">
+        <v>685</v>
+      </c>
+      <c r="D107" s="12" t="s">
+        <v>709</v>
+      </c>
+      <c r="F107" s="23" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B108" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D108" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F108" s="23" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="109" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B109" s="12" t="s">
+        <v>686</v>
+      </c>
+      <c r="D109" s="12" t="s">
+        <v>710</v>
+      </c>
+      <c r="F109" s="23" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="110" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B110" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D110" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="F110" s="23" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="111" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B111" s="12" t="s">
+        <v>687</v>
+      </c>
+      <c r="D111" s="12" t="s">
+        <v>711</v>
+      </c>
+      <c r="F111" s="23" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="112" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B112" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D112" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F112" s="23" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="113" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B113" s="12" t="s">
+        <v>688</v>
+      </c>
+      <c r="D113" s="12" t="s">
+        <v>712</v>
+      </c>
+      <c r="F113" s="23" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="114" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B114" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D114" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F114" s="23" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="115" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B115" s="12" t="s">
+        <v>689</v>
+      </c>
+      <c r="D115" s="12" t="s">
+        <v>713</v>
+      </c>
+      <c r="F115" s="23" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="116" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B116" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D116" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F116" s="23" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="117" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B117" s="12" t="s">
+        <v>690</v>
+      </c>
+      <c r="D117" s="12" t="s">
+        <v>714</v>
+      </c>
+      <c r="F117" s="23" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="118" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B118" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D118" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F118" s="23" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="119" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B119" s="12" t="s">
+        <v>691</v>
+      </c>
+      <c r="D119" s="12" t="s">
+        <v>715</v>
+      </c>
+      <c r="F119" s="23" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="120" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B120" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D120" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F120" s="23" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="121" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B121" s="12" t="s">
+        <v>692</v>
+      </c>
+      <c r="D121" s="12" t="s">
+        <v>716</v>
+      </c>
+      <c r="F121" s="23" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="122" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B122" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D122" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="F122" s="23" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="123" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B123" s="12" t="s">
+        <v>693</v>
+      </c>
+      <c r="D123" s="12" t="s">
+        <v>717</v>
+      </c>
+      <c r="F123" s="23" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="124" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B124" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D124" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F124" s="23" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="125" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B125" s="12" t="s">
+        <v>694</v>
+      </c>
+      <c r="D125" s="12" t="s">
+        <v>718</v>
+      </c>
+      <c r="F125" s="23" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="126" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B126" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D126" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F126" s="23" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="127" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B127" s="12" t="s">
+        <v>695</v>
+      </c>
+      <c r="D127" s="12" t="s">
+        <v>719</v>
+      </c>
+      <c r="F127" s="23" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="128" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B128" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D128" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F128" s="23" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="129" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B129" s="12" t="s">
+        <v>566</v>
+      </c>
+      <c r="D129" s="12" t="s">
+        <v>720</v>
+      </c>
+      <c r="F129" s="23" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="130" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B130" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D130" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F130" s="23" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="131" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="B131" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="D131" s="12" t="s">
+        <v>721</v>
+      </c>
+      <c r="F131" s="23" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="132" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B132" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D132" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F132" s="23" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="133" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B133" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="D133" s="12" t="s">
+        <v>722</v>
+      </c>
+      <c r="F133" s="23" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="134" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B134" s="26"/>
+      <c r="D134" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F134" s="23" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="135" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B135" s="12" t="s">
+        <v>569</v>
+      </c>
+      <c r="D135" s="12" t="s">
+        <v>723</v>
+      </c>
+      <c r="F135" s="23" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="136" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B136" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D136" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F136" s="23" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="137" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B137" s="25" t="s">
+        <v>696</v>
+      </c>
+      <c r="D137" s="12" t="s">
+        <v>724</v>
+      </c>
+      <c r="F137" s="23" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="138" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B138" s="26"/>
+      <c r="D138" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F138" s="23" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="139" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B139" s="12" t="s">
+        <v>697</v>
+      </c>
+      <c r="D139" s="12" t="s">
+        <v>566</v>
+      </c>
+      <c r="F139" s="23" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="140" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B140" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="D140" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F140" s="23" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="141" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B141" s="25" t="s">
+        <v>698</v>
+      </c>
+      <c r="D141" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="F141" s="23" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="142" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B142" s="26"/>
+      <c r="D142" s="26"/>
+      <c r="F142" s="23" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="143" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="B143" s="12" t="s">
+        <v>573</v>
+      </c>
+      <c r="D143" s="12" t="s">
+        <v>615</v>
+      </c>
+      <c r="F143" s="23" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="144" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B144" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D144" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F144" s="23" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="145" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B145" s="12" t="s">
+        <v>699</v>
+      </c>
+      <c r="D145" s="25" t="s">
+        <v>570</v>
+      </c>
+      <c r="F145" s="23" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="146" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B146" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="D146" s="26"/>
+      <c r="F146" s="23" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="147" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D147" s="12" t="s">
+        <v>725</v>
+      </c>
+      <c r="F147" s="23" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="148" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D148" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="F148" s="23" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="149" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D149" s="25" t="s">
+        <v>726</v>
+      </c>
+      <c r="F149" s="23" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="150" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D150" s="26"/>
+      <c r="F150" s="23" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="151" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D151" s="12" t="s">
+        <v>727</v>
+      </c>
+      <c r="F151" s="23" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D152" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="F152" s="23" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="153" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F153" s="23" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="154" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F154" s="23" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="155" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F155" s="23" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="156" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F156" s="23" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="157" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F157" s="23" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="158" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F158" s="23" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="159" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F159" s="23" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="160" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F160" s="23" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="161" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F161" s="23" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="162" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F162" s="23" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="163" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F163" s="23" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="164" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F164" s="23" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="165" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F165" s="23" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="166" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F166" s="23" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="167" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F167" s="23" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="168" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F168" s="23" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="169" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F169" s="23" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="170" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F170" s="23" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="171" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F171" s="23" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="172" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F172" s="23" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="173" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F173" s="23" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="174" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F174" s="23" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="175" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F175" s="23" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="176" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F176" s="23" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="177" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F177" s="23" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="178" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F178" s="23" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="180" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F180" s="23" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="181" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F181" s="23" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="183" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F183" s="23" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="184" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F184" s="23" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="186" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F186" s="23" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="187" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F187" s="23" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="189" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F189" s="23" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="190" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F190" s="23" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="192" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F192" s="23" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="193" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F193" s="23" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="195" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F195" s="23" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="196" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F196" s="23" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="199" spans="2:6" s="14" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="200" spans="2:6" s="14" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="204" spans="2:6" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B204" s="27" t="s">
+        <v>927</v>
+      </c>
+      <c r="D204" s="25" t="s">
+        <v>928</v>
+      </c>
+      <c r="F204" s="25" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="205" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B205" s="23" t="s">
+        <v>792</v>
+      </c>
+      <c r="D205" s="26"/>
+      <c r="F205" s="26"/>
+    </row>
+    <row r="206" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B206" s="23" t="s">
+        <v>734</v>
+      </c>
+      <c r="D206" s="12" t="s">
+        <v>542</v>
+      </c>
+      <c r="F206" s="12" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="207" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B207" s="23" t="s">
+        <v>793</v>
+      </c>
+      <c r="D207" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F207" s="12" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="208" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B208" s="23" t="s">
+        <v>794</v>
+      </c>
+      <c r="D208" s="12" t="s">
+        <v>929</v>
+      </c>
+      <c r="F208" s="12" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="209" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B209" s="23" t="s">
+        <v>795</v>
+      </c>
+      <c r="D209" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F209" s="12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="210" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B210" s="23" t="s">
+        <v>750</v>
+      </c>
+      <c r="D210" s="12" t="s">
+        <v>930</v>
+      </c>
+      <c r="F210" s="12" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="211" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B211" s="23" t="s">
+        <v>796</v>
+      </c>
+      <c r="D211" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F211" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="212" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="B212" s="23" t="s">
+        <v>734</v>
+      </c>
+      <c r="D212" s="12" t="s">
+        <v>931</v>
+      </c>
+      <c r="F212" s="12" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="213" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B213" s="23" t="s">
+        <v>797</v>
+      </c>
+      <c r="D213" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F213" s="12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="214" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B214" s="23" t="s">
+        <v>798</v>
+      </c>
+      <c r="D214" s="12" t="s">
+        <v>932</v>
+      </c>
+      <c r="F214" s="12" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="215" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B215" s="23" t="s">
+        <v>799</v>
+      </c>
+      <c r="D215" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="F215" s="12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="216" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B216" s="23" t="s">
+        <v>731</v>
+      </c>
+      <c r="D216" s="12" t="s">
+        <v>933</v>
+      </c>
+      <c r="F216" s="12" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="217" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B217" s="23" t="s">
+        <v>800</v>
+      </c>
+      <c r="D217" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F217" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="218" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B218" s="23" t="s">
+        <v>736</v>
+      </c>
+      <c r="D218" s="12" t="s">
+        <v>934</v>
+      </c>
+      <c r="F218" s="12" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="219" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B219" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="D219" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="F219" s="12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="220" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B220" s="23" t="s">
+        <v>734</v>
+      </c>
+      <c r="D220" s="12" t="s">
+        <v>935</v>
+      </c>
+      <c r="F220" s="12" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="221" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B221" s="23" t="s">
+        <v>802</v>
+      </c>
+      <c r="D221" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="F221" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="222" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B222" s="23" t="s">
+        <v>734</v>
+      </c>
+      <c r="D222" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F222" s="12" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="223" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B223" s="23" t="s">
+        <v>803</v>
+      </c>
+      <c r="D223" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F223" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="224" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B224" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="D224" s="12" t="s">
+        <v>937</v>
+      </c>
+      <c r="F224" s="12" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="225" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D225" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="F225" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="226" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B226" s="23" t="s">
+        <v>804</v>
+      </c>
+      <c r="D226" s="12" t="s">
+        <v>938</v>
+      </c>
+      <c r="F226" s="12" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="227" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B227" s="23" t="s">
+        <v>750</v>
+      </c>
+      <c r="D227" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F227" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="228" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D228" s="12" t="s">
+        <v>939</v>
+      </c>
+      <c r="F228" s="12" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="229" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B229" s="23" t="s">
+        <v>805</v>
+      </c>
+      <c r="D229" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F229" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="230" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B230" s="23" t="s">
+        <v>736</v>
+      </c>
+      <c r="D230" s="12" t="s">
+        <v>940</v>
+      </c>
+      <c r="F230" s="12" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="231" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D231" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F231" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="232" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="B232" s="23" t="s">
+        <v>806</v>
+      </c>
+      <c r="D232" s="12" t="s">
+        <v>941</v>
+      </c>
+      <c r="F232" s="12" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="233" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B233" s="23" t="s">
+        <v>789</v>
+      </c>
+      <c r="D233" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F233" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="234" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D234" s="12" t="s">
+        <v>942</v>
+      </c>
+      <c r="F234" s="12" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="235" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B235" s="23" t="s">
+        <v>793</v>
+      </c>
+      <c r="D235" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F235" s="12" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="236" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B236" s="23" t="s">
+        <v>807</v>
+      </c>
+      <c r="D236" s="12" t="s">
+        <v>943</v>
+      </c>
+      <c r="F236" s="12" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="237" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B237" s="23" t="s">
+        <v>808</v>
+      </c>
+      <c r="D237" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F237" s="12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="238" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B238" s="23" t="s">
+        <v>734</v>
+      </c>
+      <c r="D238" s="12" t="s">
+        <v>566</v>
+      </c>
+      <c r="F238" s="12" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="239" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B239" s="23" t="s">
+        <v>809</v>
+      </c>
+      <c r="D239" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="F239" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="240" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B240" s="23" t="s">
+        <v>736</v>
+      </c>
+      <c r="D240" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="F240" s="12" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="241" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B241" s="23" t="s">
+        <v>810</v>
+      </c>
+      <c r="D241" s="26"/>
+      <c r="F241" s="12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="242" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B242" s="23" t="s">
+        <v>739</v>
+      </c>
+      <c r="D242" s="12" t="s">
+        <v>615</v>
+      </c>
+      <c r="F242" s="12" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="243" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B243" s="23" t="s">
+        <v>811</v>
+      </c>
+      <c r="D243" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F243" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="244" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B244" s="23" t="s">
+        <v>739</v>
+      </c>
+      <c r="D244" s="25" t="s">
+        <v>570</v>
+      </c>
+      <c r="F244" s="12" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="245" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B245" s="23" t="s">
+        <v>812</v>
+      </c>
+      <c r="D245" s="26"/>
+      <c r="F245" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="246" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B246" s="23" t="s">
+        <v>734</v>
+      </c>
+      <c r="D246" s="12" t="s">
+        <v>944</v>
+      </c>
+      <c r="F246" s="12" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="247" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B247" s="23" t="s">
+        <v>813</v>
+      </c>
+      <c r="D247" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="F247" s="12" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="248" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B248" s="23" t="s">
+        <v>734</v>
+      </c>
+      <c r="D248" s="25" t="s">
+        <v>945</v>
+      </c>
+      <c r="F248" s="25" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="249" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B249" s="23" t="s">
+        <v>814</v>
+      </c>
+      <c r="D249" s="26"/>
+      <c r="F249" s="26"/>
+    </row>
+    <row r="250" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B250" s="23" t="s">
+        <v>734</v>
+      </c>
+      <c r="D250" s="12" t="s">
+        <v>946</v>
+      </c>
+      <c r="F250" s="12" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="251" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B251" s="23" t="s">
+        <v>815</v>
+      </c>
+      <c r="D251" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="F251" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="252" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B252" s="23" t="s">
+        <v>816</v>
+      </c>
+      <c r="F252" s="25" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="253" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B253" s="23" t="s">
+        <v>817</v>
+      </c>
+      <c r="F253" s="26"/>
+    </row>
+    <row r="254" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B254" s="23" t="s">
+        <v>774</v>
+      </c>
+      <c r="F254" s="12" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="255" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B255" s="23" t="s">
+        <v>818</v>
+      </c>
+      <c r="F255" s="12" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="256" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B256" s="23" t="s">
+        <v>731</v>
+      </c>
+      <c r="F256" s="25" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="257" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B257" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="F257" s="26"/>
+    </row>
+    <row r="258" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B258" s="23" t="s">
+        <v>736</v>
+      </c>
+      <c r="F258" s="12" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="259" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B259" s="23" t="s">
+        <v>820</v>
+      </c>
+      <c r="F259" s="12" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="260" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B260" s="23" t="s">
+        <v>729</v>
+      </c>
+      <c r="F260" s="25" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="261" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B261" s="23" t="s">
+        <v>821</v>
+      </c>
+      <c r="F261" s="26"/>
+    </row>
+    <row r="262" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B262" s="23" t="s">
+        <v>734</v>
+      </c>
+      <c r="F262" s="12" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="263" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B263" s="23" t="s">
+        <v>822</v>
+      </c>
+      <c r="F263" s="12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="264" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B264" s="23" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="265" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B265" s="23" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="266" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B266" s="23" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="267" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B267" s="23" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="268" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B268" s="23" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="269" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B269" s="23" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="270" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B270" s="23" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="271" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B271" s="23" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="272" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B272" s="23" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="273" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B273" s="23" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="274" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B274" s="23" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="275" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B275" s="23" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="276" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B276" s="23" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="278" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B278" s="23" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="279" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B279" s="23" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="281" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B281" s="23" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="282" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B282" s="23" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="284" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B284" s="23" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="285" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B285" s="23" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="286" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B286" s="28"/>
+    </row>
+    <row r="287" spans="2:2" ht="24" x14ac:dyDescent="0.4">
+      <c r="B287" s="29"/>
+    </row>
+    <row r="288" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B288" s="23" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="289" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B289" s="23" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="290" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B290" s="28"/>
+    </row>
+    <row r="291" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B291" s="30" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="293" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B293" s="23" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B294" s="28"/>
+    </row>
+    <row r="295" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B295" s="30" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="297" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B297" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="299" spans="2:2" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B299" s="31" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="301" spans="2:2" ht="18" x14ac:dyDescent="0.25">
+      <c r="B301" s="32" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="303" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B303" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="305" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B305" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="306" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B306" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="307" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B307" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="308" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B308" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="309" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B309" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="310" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B310" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="311" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B311" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="312" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B312" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="313" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B313" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="314" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B314" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="315" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B315" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="316" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B316" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="317" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B317" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="318" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B318" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="319" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B319" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="320" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B320" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="321" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B321" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="322" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B322" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="323" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B323" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="324" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B324" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="325" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B325" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="326" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B326" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="327" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B327" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="328" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B328" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="329" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B329" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="330" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B330" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="331" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B331" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="332" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B332" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="333" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B333" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="334" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B334" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="335" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B335" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="336" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B336" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="337" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B337" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="338" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B338" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="339" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B339" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="340" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B340" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="341" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B341" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="342" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B342" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="343" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B343" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="344" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B344" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="345" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B345" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="346" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B346" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="347" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B347" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="348" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B348" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="349" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B349" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="350" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B350" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="351" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B351" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="352" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B352" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="353" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B353" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="354" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B354" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="355" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B355" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="356" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B356" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="357" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B357" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="358" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B358" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="359" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B359" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="360" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B360" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="361" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B361" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="362" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B362" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="363" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B363" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="364" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B364" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="365" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B365" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="366" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B366" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="367" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B367" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="368" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B368" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="369" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B369" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="370" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B370" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="371" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B371" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="372" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B372" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="373" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B373" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="374" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B374" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="375" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B375" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="376" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B376" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="377" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B377" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="378" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B378" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="379" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B379" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="380" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B380" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="381" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B381" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="382" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B382" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="383" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B383" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="384" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B384" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="385" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B385" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="386" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B386" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="387" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B387" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="388" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B388" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="389" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B389" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="390" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B390" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="392" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B392" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="395" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B395" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="397" spans="2:2" s="14" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="398" spans="2:2" s="14" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="400" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B400" s="25" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="401" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B401" s="26"/>
+    </row>
+    <row r="402" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B402" s="12" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="403" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B403" s="12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="404" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B404" s="12" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="405" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B405" s="12" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="406" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B406" s="12" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="407" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B407" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="408" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B408" s="12" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="409" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B409" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="410" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B410" s="12" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="411" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B411" s="12" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="412" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B412" s="12" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="413" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B413" s="12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="414" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B414" s="12" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="415" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B415" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="416" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B416" s="12" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="417" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B417" s="12" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="418" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B418" s="12" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="419" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B419" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="420" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B420" s="12" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="421" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B421" s="12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="422" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B422" s="12" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="423" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B423" s="12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="424" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B424" s="12" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="425" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B425" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="426" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B426" s="12" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="427" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B427" s="12" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="428" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B428" s="12" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="429" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B429" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="430" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B430" s="12" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="431" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B431" s="12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="432" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B432" s="12" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="433" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B433" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="434" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B434" s="12" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="435" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B435" s="12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="436" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B436" s="12" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="437" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B437" s="12" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="438" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B438" s="12" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="439" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B439" s="12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="440" spans="2:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="B440" s="12" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="441" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B441" s="12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="442" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B442" s="25" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="443" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B443" s="26"/>
+    </row>
+    <row r="444" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B444" s="12" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="445" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B445" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="446" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B446" s="25" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="447" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B447" s="26"/>
+    </row>
+    <row r="448" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B448" s="12" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="449" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B449" s="12" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="450" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B450" s="25" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="451" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B451" s="26"/>
+    </row>
+    <row r="452" spans="2:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="B452" s="12" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="453" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B453" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="454" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B454" s="12" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="455" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B455" s="12" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="456" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B456" s="25" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="457" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B457" s="26"/>
+    </row>
+    <row r="458" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B458" s="12" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="459" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B459" s="12" t="s">
+        <v>997</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B3" r:id="rId1" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/dDdRc/welcome-to-the-nlp-specialization" xr:uid="{F40174D0-815D-4D25-87A8-38F10F715AEE}"/>
+    <hyperlink ref="B4" r:id="rId2" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/dDdRc/welcome-to-the-nlp-specialization" xr:uid="{F92F1627-FAF1-498C-B8A7-2E999E61BC39}"/>
+    <hyperlink ref="B5" r:id="rId3" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/DmVDT/welcome-to-course-1" xr:uid="{C864A8C0-36B0-4B4C-9E14-8F78F13F2485}"/>
+    <hyperlink ref="B6" r:id="rId4" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/DmVDT/welcome-to-course-1" xr:uid="{2B80A793-7F2D-4773-8A4A-45FA9DC8B852}"/>
+    <hyperlink ref="B7" r:id="rId5" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/DOeDQ/acknowledgement-ken-church" xr:uid="{430F6541-B5F5-4203-BAFC-80DB1E66003B}"/>
+    <hyperlink ref="B8" r:id="rId6" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/DOeDQ/acknowledgement-ken-church" xr:uid="{020E0B34-50F2-4B0E-9A38-F1ACFDC0F409}"/>
+    <hyperlink ref="B9" r:id="rId7" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/qW1Tp/week-introduction" xr:uid="{0BA7F4C2-77AB-4F06-9F3F-9F5785ADD683}"/>
+    <hyperlink ref="B10" r:id="rId8" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/qW1Tp/week-introduction" xr:uid="{43CB6B12-0029-429F-ACFB-AD6FD9A01FB3}"/>
+    <hyperlink ref="B11" r:id="rId9" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/QYcqq/supervised-ml-sentiment-analysis" xr:uid="{F87B17F3-5A1F-4778-A6BE-E147D8AFA16F}"/>
+    <hyperlink ref="B12" r:id="rId10" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/QYcqq/supervised-ml-sentiment-analysis" xr:uid="{6D41AC04-0FED-4EF3-B8C1-045AFC824405}"/>
+    <hyperlink ref="B13" r:id="rId11" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/J9NR1/supervised-ml-sentiment-analysis" xr:uid="{D2DFE1B8-D119-4056-A374-39A64CF7D5FF}"/>
+    <hyperlink ref="B14" r:id="rId12" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/J9NR1/supervised-ml-sentiment-analysis" xr:uid="{0907AE3F-C340-488E-BE26-D5558C3A1D0D}"/>
+    <hyperlink ref="B15" r:id="rId13" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/gNXI3/vocabulary-feature-extraction" xr:uid="{D960FCE8-17CF-4183-BED1-1B2C48A20273}"/>
+    <hyperlink ref="B16" r:id="rId14" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/gNXI3/vocabulary-feature-extraction" xr:uid="{7016E0CC-0971-4583-881B-0EFB57DAB6D5}"/>
+    <hyperlink ref="B17" r:id="rId15" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/m7UdZ/vocabulary-feature-extraction" xr:uid="{76537B12-AD46-41B8-8436-50C68A4E5E75}"/>
+    <hyperlink ref="B18" r:id="rId16" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/m7UdZ/vocabulary-feature-extraction" xr:uid="{A7C1D34E-C37A-46FB-846A-58A822111E6B}"/>
+    <hyperlink ref="B19" r:id="rId17" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/cITmZ/negative-and-positive-frequencies" xr:uid="{20934E75-DFC6-4FAF-A5BE-3D5DB6DA8E50}"/>
+    <hyperlink ref="B20" r:id="rId18" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/cITmZ/negative-and-positive-frequencies" xr:uid="{AB9E32FA-2574-465F-B90F-C0933F399924}"/>
+    <hyperlink ref="B21" r:id="rId19" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/j92dt/feature-extraction-with-frequencies" xr:uid="{56C79CCB-7EDE-4016-ACCF-F68B51ED7847}"/>
+    <hyperlink ref="B22" r:id="rId20" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/j92dt/feature-extraction-with-frequencies" xr:uid="{32EDCAE3-627A-4CDE-BACF-48A557767AAC}"/>
+    <hyperlink ref="B23" r:id="rId21" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/sfhGt/feature-extraction-with-frequencies" xr:uid="{A9DD1849-C9E3-4145-845C-D115D0817851}"/>
+    <hyperlink ref="B24" r:id="rId22" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/sfhGt/feature-extraction-with-frequencies" xr:uid="{759B453B-F216-4346-AAA6-8383C3EE6E72}"/>
+    <hyperlink ref="B25" r:id="rId23" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/nbPdT/preprocessing" xr:uid="{8E9337EE-F4B5-4A49-8A34-D93CBAEA9FAD}"/>
+    <hyperlink ref="B26" r:id="rId24" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/nbPdT/preprocessing" xr:uid="{53BAC3AC-0B97-40E1-8C4E-AA432F642F2A}"/>
+    <hyperlink ref="B27" r:id="rId25" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/SLqys/preprocessing" xr:uid="{5613D580-4F74-4EDE-8F3A-68E4DCD18BA2}"/>
+    <hyperlink ref="B28" r:id="rId26" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/SLqys/preprocessing" xr:uid="{DA7A69C1-BE08-4496-9A9D-D91A46DE4BAB}"/>
+    <hyperlink ref="B29" r:id="rId27" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/ungradedLab/TXtyC/natural-language-preprocessing" xr:uid="{D349D54A-9B5D-451C-BAFE-6DE3F5EA77E9}"/>
+    <hyperlink ref="B30" r:id="rId28" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/ungradedLab/TXtyC/natural-language-preprocessing" xr:uid="{822EAD24-7A15-4C35-AFBF-54B454CC72DD}"/>
+    <hyperlink ref="B31" r:id="rId29" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/r139b/putting-it-all-together" xr:uid="{BB35722A-871E-4F25-93B3-8D9DC2EA752A}"/>
+    <hyperlink ref="B32" r:id="rId30" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/r139b/putting-it-all-together" xr:uid="{07985116-7DA8-4B83-B288-66224AE90ADC}"/>
+    <hyperlink ref="B33" r:id="rId31" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/HjiGd/putting-it-all-together" xr:uid="{CD97F101-A961-4630-AD95-B252BA0A77E2}"/>
+    <hyperlink ref="B34" r:id="rId32" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/HjiGd/putting-it-all-together" xr:uid="{FD1D5256-1DDB-4975-BD62-21AEEBA276B6}"/>
+    <hyperlink ref="B35" r:id="rId33" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/ungradedLab/13HKM/visualizing-word-frequencies" xr:uid="{AE5755DB-4489-470E-8FCB-9569AC667115}"/>
+    <hyperlink ref="B36" r:id="rId34" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/ungradedLab/13HKM/visualizing-word-frequencies" xr:uid="{0C7F7571-0E88-4714-98F9-19CB77081ABE}"/>
+    <hyperlink ref="B37" r:id="rId35" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/N26QT/logistic-regression-overview" xr:uid="{9580CB42-6F33-451B-9F08-F73900F9EAE5}"/>
+    <hyperlink ref="B38" r:id="rId36" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/N26QT/logistic-regression-overview" xr:uid="{727B0558-C742-413A-8925-15394E59F83B}"/>
+    <hyperlink ref="B39" r:id="rId37" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/4GuN0/logistic-regression-overview" xr:uid="{9284A0AA-823F-455D-B11B-AE087390F776}"/>
+    <hyperlink ref="B40" r:id="rId38" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/4GuN0/logistic-regression-overview" xr:uid="{DDC97D82-0353-4FB2-A5CA-FFE7D8380239}"/>
+    <hyperlink ref="B41" r:id="rId39" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/LCtiZ/logistic-regression-training" xr:uid="{F0F57E87-813F-4566-8AD3-F5919C1972B9}"/>
+    <hyperlink ref="B42" r:id="rId40" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/LCtiZ/logistic-regression-training" xr:uid="{3717455A-C2A6-42CE-B029-DB1A73908FAA}"/>
+    <hyperlink ref="B43" r:id="rId41" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/AJSvB/logistic-regression-training" xr:uid="{058F312F-034C-4D38-AC26-8B237BBA24CB}"/>
+    <hyperlink ref="B44" r:id="rId42" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/AJSvB/logistic-regression-training" xr:uid="{32750B98-230A-420C-A1B4-703B071427AC}"/>
+    <hyperlink ref="B45" r:id="rId43" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/ungradedLab/GeAyH/visualizing-tweets-and-logistic-regression-models" xr:uid="{1D65B359-1FDD-4665-88A9-49B35AD4FCD8}"/>
+    <hyperlink ref="B46" r:id="rId44" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/ungradedLab/GeAyH/visualizing-tweets-and-logistic-regression-models" xr:uid="{5D620486-519E-471A-B48D-07EF05232F16}"/>
+    <hyperlink ref="B47" r:id="rId45" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/HZQ26/logistic-regression-testing" xr:uid="{B6814E03-7B78-42C9-A5BE-95C55FDFF9C8}"/>
+    <hyperlink ref="B48" r:id="rId46" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/HZQ26/logistic-regression-testing" xr:uid="{D3C29D59-58F2-4329-9345-65D506F892E5}"/>
+    <hyperlink ref="B49" r:id="rId47" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/AmwJi/logistic-regression-testing" xr:uid="{A6F94D90-08AD-431B-AF27-97CE8A451951}"/>
+    <hyperlink ref="B50" r:id="rId48" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/AmwJi/logistic-regression-testing" xr:uid="{276AC901-5E9E-4F82-8E9F-CCBD6F3B4096}"/>
+    <hyperlink ref="B51" r:id="rId49" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/GVxHo/logistic-regression-cost-function" xr:uid="{696F006B-B3F6-4941-9CA0-40287B5B016B}"/>
+    <hyperlink ref="B52" r:id="rId50" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/GVxHo/logistic-regression-cost-function" xr:uid="{F9A6A01C-ADE1-445D-AEDD-7EC41D882EE9}"/>
+    <hyperlink ref="B53" r:id="rId51" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/b3fHH/optional-logistic-regression-cost-function" xr:uid="{60674E28-6A17-4F4E-BDDA-054CB4334A18}"/>
+    <hyperlink ref="B54" r:id="rId52" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/b3fHH/optional-logistic-regression-cost-function" xr:uid="{26CF8E0C-58F5-47A5-B4C4-C43D45E1DDF4}"/>
+    <hyperlink ref="B55" r:id="rId53" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/Isrkv/week-conclusion" xr:uid="{6EBFC445-598A-4228-A994-D5639AFCED66}"/>
+    <hyperlink ref="B56" r:id="rId54" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/Isrkv/week-conclusion" xr:uid="{86FB3974-B5B0-48BA-AAF3-12A881C493A2}"/>
+    <hyperlink ref="B57" r:id="rId55" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/afcaR/optional-logistic-regression-gradient" xr:uid="{304C39B5-D72E-482C-BB67-89053732A9E7}"/>
+    <hyperlink ref="B58" r:id="rId56" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/afcaR/optional-logistic-regression-gradient" xr:uid="{27439DA3-AA3A-450E-A7D9-6F5507954963}"/>
+    <hyperlink ref="B59" r:id="rId57" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/ungradedLti/iFfxj/intake-survey" xr:uid="{0F339A27-4F1B-4FAE-836D-74F9018F9B5C}"/>
+    <hyperlink ref="B60" r:id="rId58" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/ungradedLti/iFfxj/intake-survey" xr:uid="{2C5D091C-F63D-4A74-856D-9BE9B856FCD8}"/>
+    <hyperlink ref="B61" r:id="rId59" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/ythWu/important-have-questions-issues-or-ideas-join-our-forum" xr:uid="{44971645-F487-4D65-9E5D-CDD13816BF19}"/>
+    <hyperlink ref="B62" r:id="rId60" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/ythWu/important-have-questions-issues-or-ideas-join-our-forum" xr:uid="{0D263498-4793-4157-8E11-112ACE9A9912}"/>
+    <hyperlink ref="B65" r:id="rId61" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/JPwGC/lecture-notes-w1" xr:uid="{801423EC-AF7C-49C3-8CAA-29F2D97642FA}"/>
+    <hyperlink ref="B66" r:id="rId62" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/JPwGC/lecture-notes-w1" xr:uid="{83FCA905-5191-4F46-9EFD-EA12291C7D73}"/>
+    <hyperlink ref="B69" r:id="rId63" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/assignment-submission/RCzSX/logistic-regression" xr:uid="{65E2CABC-548F-4F45-9AE9-76B555E23ACA}"/>
+    <hyperlink ref="B70" r:id="rId64" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/assignment-submission/RCzSX/logistic-regression" xr:uid="{38DCDC99-49C6-43B5-AD67-6D47A0DF6424}"/>
+    <hyperlink ref="B73" r:id="rId65" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/cTCiZ/optional-downloading-your-notebook-downloading-your-workspace-and-refreshing" xr:uid="{77410A52-F95A-4758-B48C-C7EE2462B32A}"/>
+    <hyperlink ref="B74" r:id="rId66" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/cTCiZ/optional-downloading-your-notebook-downloading-your-workspace-and-refreshing" xr:uid="{785D21E0-D3A2-46E7-8D77-35D22ACD0ED8}"/>
+    <hyperlink ref="B75" r:id="rId67" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/programming/P4CTb/logistic-regression" xr:uid="{6C99F032-132F-4049-9DF2-E32C9B99A9A7}"/>
+    <hyperlink ref="B76" r:id="rId68" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/programming/P4CTb/logistic-regression" xr:uid="{59D3E5FA-387F-434A-B892-7535D889C7AA}"/>
+    <hyperlink ref="B79" r:id="rId69" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/sA35B/andrew-ng-with-chris-manning" xr:uid="{E7EE64E4-134A-454C-82EA-C86426961BF4}"/>
+    <hyperlink ref="B80" r:id="rId70" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/sA35B/andrew-ng-with-chris-manning" xr:uid="{2094BDAE-5EE9-40A9-B54A-4AFA570103E4}"/>
+    <hyperlink ref="D3" r:id="rId71" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/iyIWf/week-introduction" xr:uid="{7B0CCDF1-34EC-4A1D-875D-38B4E2DA9492}"/>
+    <hyperlink ref="D4" r:id="rId72" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/iyIWf/week-introduction" xr:uid="{8194E327-3B2D-4BFA-8541-E59D7B93ED73}"/>
+    <hyperlink ref="D5" r:id="rId73" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/QYeQu/probability-and-bayes-rule" xr:uid="{986D8033-985F-4500-BA2A-C0ABF948E1A0}"/>
+    <hyperlink ref="D6" r:id="rId74" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/QYeQu/probability-and-bayes-rule" xr:uid="{D5280182-7556-49D8-B6B0-12D76E1B2FB0}"/>
+    <hyperlink ref="D7" r:id="rId75" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/gK4BU/probability-and-bayes-rule" xr:uid="{DC2F957E-4DC3-4046-8F00-DFB9840B0093}"/>
+    <hyperlink ref="D8" r:id="rId76" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/gK4BU/probability-and-bayes-rule" xr:uid="{7EEE1200-4EE6-4CBF-81E1-87AAF84C6CB9}"/>
+    <hyperlink ref="D9" r:id="rId77" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/2tm1M/bayes-rule" xr:uid="{FEA691FD-3491-465A-A85B-8665302800BD}"/>
+    <hyperlink ref="D10" r:id="rId78" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/2tm1M/bayes-rule" xr:uid="{CADBB0F4-535C-4DB1-9A8D-7382EE679AEC}"/>
+    <hyperlink ref="D11" r:id="rId79" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/1I1q1/bayes-rule" xr:uid="{9DDD5965-4653-4CB5-BFC0-042FD1976801}"/>
+    <hyperlink ref="D12" r:id="rId80" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/1I1q1/bayes-rule" xr:uid="{A46695DB-D43B-44E1-8E12-D8AE57CAF56F}"/>
+    <hyperlink ref="D13" r:id="rId81" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/MtRRO/naive-bayes-introduction" xr:uid="{370C9988-8783-44D6-91BE-93D59ABD2FCA}"/>
+    <hyperlink ref="D14" r:id="rId82" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/MtRRO/naive-bayes-introduction" xr:uid="{EC5B4828-2403-4A5D-A6E0-408343B4D5F6}"/>
+    <hyperlink ref="D15" r:id="rId83" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/boKAa/naive-bayes-introduction" xr:uid="{467A34FA-E094-41E2-8703-6A663180F9D6}"/>
+    <hyperlink ref="D16" r:id="rId84" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/boKAa/naive-bayes-introduction" xr:uid="{6D06E8EE-1499-4178-B835-9E96A117E1F9}"/>
+    <hyperlink ref="D17" r:id="rId85" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/2jMPy/laplacian-smoothing" xr:uid="{5CD52A82-F581-46EE-91B2-301EAFA7B75C}"/>
+    <hyperlink ref="D18" r:id="rId86" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/2jMPy/laplacian-smoothing" xr:uid="{6563B438-FD6E-4A70-905C-6C97ECD44025}"/>
+    <hyperlink ref="D19" r:id="rId87" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/IbV5W/laplacian-smoothing" xr:uid="{272E411F-3524-49D6-9F7F-7CA515326D52}"/>
+    <hyperlink ref="D20" r:id="rId88" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/IbV5W/laplacian-smoothing" xr:uid="{013B24CF-0034-4944-9689-D06B7D5C0F5D}"/>
+    <hyperlink ref="D21" r:id="rId89" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/rJ4A7/log-likelihood-part-1" xr:uid="{0D7E68F4-7183-4D32-AC1E-A9EF930E52EC}"/>
+    <hyperlink ref="D22" r:id="rId90" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/rJ4A7/log-likelihood-part-1" xr:uid="{B6CD1C24-EEE3-44B8-B92E-F47B037DB930}"/>
+    <hyperlink ref="D23" r:id="rId91" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/lNljj/log-likelihood-part-1" xr:uid="{5536A653-A40A-4A68-AA50-8325C5A713F6}"/>
+    <hyperlink ref="D24" r:id="rId92" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/lNljj/log-likelihood-part-1" xr:uid="{CAF87C73-4586-47A5-A11E-E7150E0EC714}"/>
+    <hyperlink ref="D25" r:id="rId93" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/cIVmu/log-likelihood-part-2" xr:uid="{9F875B33-8CEB-4F14-897E-B690EBD2B53C}"/>
+    <hyperlink ref="D26" r:id="rId94" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/cIVmu/log-likelihood-part-2" xr:uid="{C5640221-86CE-4A59-BCEF-B2300CFC07A2}"/>
+    <hyperlink ref="D27" r:id="rId95" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/oYXpy/log-likelihood-part-2" xr:uid="{57C7EF22-1BE0-491E-BE66-24E278E87843}"/>
+    <hyperlink ref="D28" r:id="rId96" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/oYXpy/log-likelihood-part-2" xr:uid="{5C33DA26-493C-4E68-9A04-ED4CAA7B8E02}"/>
+    <hyperlink ref="D29" r:id="rId97" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/uQXpl/training-naive-bayes" xr:uid="{B2A40E07-7C7E-4179-A501-579177D67BB0}"/>
+    <hyperlink ref="D30" r:id="rId98" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/uQXpl/training-naive-bayes" xr:uid="{45FAB38B-6135-4619-8A3A-8DFD94CF0C2A}"/>
+    <hyperlink ref="D31" r:id="rId99" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/0imfM/training-naive-bayes" xr:uid="{D9D58DE7-DB08-4B53-AD83-70B102538622}"/>
+    <hyperlink ref="D32" r:id="rId100" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/0imfM/training-naive-bayes" xr:uid="{20B3A879-E0F6-48A0-898E-EBB1B300A3B2}"/>
+    <hyperlink ref="D33" r:id="rId101" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/ungradedLab/NuNV6/visualizing-likelihoods-and-confidence-ellipses" xr:uid="{A547C95E-92FA-4F8A-8A4C-E20395E25455}"/>
+    <hyperlink ref="D34" r:id="rId102" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/ungradedLab/NuNV6/visualizing-likelihoods-and-confidence-ellipses" xr:uid="{AA5AF9A4-3A83-48AC-AC04-047C18705D24}"/>
+    <hyperlink ref="D35" r:id="rId103" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/1ODdZ/testing-naive-bayes" xr:uid="{C63E523F-891B-4EA5-94A3-3303593E93F4}"/>
+    <hyperlink ref="D36" r:id="rId104" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/1ODdZ/testing-naive-bayes" xr:uid="{E8D2B257-B816-447A-BF01-1A50742821AB}"/>
+    <hyperlink ref="D37" r:id="rId105" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/nquvt/testing-naive-bayes" xr:uid="{6178DD62-658D-4BC6-AB52-A26B8F220EB5}"/>
+    <hyperlink ref="D38" r:id="rId106" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/nquvt/testing-naive-bayes" xr:uid="{FCC521EE-DAC0-4FA3-9037-CDAF72D753DC}"/>
+    <hyperlink ref="D39" r:id="rId107" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/bJXYZ/applications-of-naive-bayes" xr:uid="{AD10F518-46BD-4497-8D30-BC8924C67116}"/>
+    <hyperlink ref="D40" r:id="rId108" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/bJXYZ/applications-of-naive-bayes" xr:uid="{AE60BB0D-6EF4-486A-857C-EF7534EF254F}"/>
+    <hyperlink ref="D41" r:id="rId109" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/aQTbY/applications-of-naive-bayes" xr:uid="{40C4CFD5-C791-47AE-8D13-960D0100AFDE}"/>
+    <hyperlink ref="D42" r:id="rId110" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/aQTbY/applications-of-naive-bayes" xr:uid="{2EA48E08-9A5B-42FF-B28F-DD2B647A469A}"/>
+    <hyperlink ref="D43" r:id="rId111" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/ctBij/naive-bayes-assumptions" xr:uid="{495649F7-6A74-4509-AFDE-14575791C787}"/>
+    <hyperlink ref="D44" r:id="rId112" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/ctBij/naive-bayes-assumptions" xr:uid="{87352162-71ED-4AEF-B75E-1EAC7F501448}"/>
+    <hyperlink ref="D45" r:id="rId113" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/xoi1w/naive-bayes-assumptions" xr:uid="{9D3DC9D0-AF7D-468E-AAE9-F1EF66624F21}"/>
+    <hyperlink ref="D46" r:id="rId114" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/xoi1w/naive-bayes-assumptions" xr:uid="{2D7E0C12-DD56-44E1-A0FF-EFDC87D4570E}"/>
+    <hyperlink ref="D47" r:id="rId115" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/9FZWb/error-analysis" xr:uid="{62A6E761-33F3-4360-9212-A35A2381AD64}"/>
+    <hyperlink ref="D48" r:id="rId116" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/9FZWb/error-analysis" xr:uid="{D1DDDB42-FA7F-4E44-9A4B-35DC0CC16F71}"/>
+    <hyperlink ref="D49" r:id="rId117" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/clcHR/error-analysis" xr:uid="{9ACDBC20-2C1E-4860-AC76-9813DE747052}"/>
+    <hyperlink ref="D50" r:id="rId118" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/clcHR/error-analysis" xr:uid="{4FB902CF-C2B1-4815-82C2-D767414107F6}"/>
+    <hyperlink ref="D51" r:id="rId119" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/mdefR/week-conclusion" xr:uid="{73E63B0A-A189-4DB0-8DC4-30464FD139AE}"/>
+    <hyperlink ref="D52" r:id="rId120" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/mdefR/week-conclusion" xr:uid="{FEE9717F-6F69-48ED-872C-D053529F77FC}"/>
+    <hyperlink ref="D55" r:id="rId121" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/WYcSb/lecture-notes-w2" xr:uid="{20C8418A-0311-4FB7-89FD-F93CDAC5E2A5}"/>
+    <hyperlink ref="D56" r:id="rId122" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/WYcSb/lecture-notes-w2" xr:uid="{79C2DD1E-3291-48F9-8811-45C69B550857}"/>
+    <hyperlink ref="D59" r:id="rId123" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/assignment-submission/x9g6u/naive-bayes" xr:uid="{DF2496BE-5D18-4189-8E47-AF2A97685028}"/>
+    <hyperlink ref="D60" r:id="rId124" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/assignment-submission/x9g6u/naive-bayes" xr:uid="{CCA3E346-739C-450C-AF69-998493127A00}"/>
+    <hyperlink ref="D63" r:id="rId125" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/programming/xDch8/naive-bayes" xr:uid="{F4F1CD2D-DD16-43A3-9047-BBF29783E720}"/>
+    <hyperlink ref="D64" r:id="rId126" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/programming/xDch8/naive-bayes" xr:uid="{BF421E9B-E29F-4152-9158-0A6C4DD3B5FF}"/>
+    <hyperlink ref="F3" r:id="rId127" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/yOsh6/week-introduction" xr:uid="{80514D99-9FD8-4D7C-AF4C-B6F34C897CF6}"/>
+    <hyperlink ref="F4" r:id="rId128" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/yOsh6/week-introduction" xr:uid="{B09DA25A-C0A4-4472-A53E-AE67334B3D75}"/>
+    <hyperlink ref="F5" r:id="rId129" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/ODpV0/vector-space-models" xr:uid="{1E900109-C48E-4EFE-9506-0813F33DDA7E}"/>
+    <hyperlink ref="F6" r:id="rId130" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/ODpV0/vector-space-models" xr:uid="{1FAAA25F-E8F3-4BA8-906F-ACE69E4E77BB}"/>
+    <hyperlink ref="F7" r:id="rId131" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/yYagJ/vector-space-models" xr:uid="{82BC7AD3-8019-4CE8-9CB5-5477287DA0D4}"/>
+    <hyperlink ref="F8" r:id="rId132" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/yYagJ/vector-space-models" xr:uid="{0E04E7C3-C2B4-4A0A-AD97-2B5743CC2E64}"/>
+    <hyperlink ref="F9" r:id="rId133" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/uFYj6/word-by-word-and-word-by-doc" xr:uid="{CD01318F-61F0-4C8E-84A8-862EA58D0448}"/>
+    <hyperlink ref="F10" r:id="rId134" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/uFYj6/word-by-word-and-word-by-doc" xr:uid="{0BF27430-5427-41E3-9A4E-229FB9E4463E}"/>
+    <hyperlink ref="F11" r:id="rId135" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/XAYg4/word-by-word-and-word-by-doc" xr:uid="{1D63490E-A6BA-447C-9507-14DCFDD1B42E}"/>
+    <hyperlink ref="F12" r:id="rId136" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/XAYg4/word-by-word-and-word-by-doc" xr:uid="{180415B8-39AF-43A5-BE4E-71E51CD2503D}"/>
+    <hyperlink ref="F13" r:id="rId137" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/ungradedLab/Ijghw/linear-algebra-in-python-with-numpy" xr:uid="{EAF7EA49-AA29-41C6-9774-D80C3FDE2AA7}"/>
+    <hyperlink ref="F14" r:id="rId138" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/ungradedLab/Ijghw/linear-algebra-in-python-with-numpy" xr:uid="{C0B942A7-A5D4-48E1-85AC-E5561924DBD0}"/>
+    <hyperlink ref="F15" r:id="rId139" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/rkbLw/euclidean-distance" xr:uid="{0009D0B5-448B-4BE4-8BBA-2437816EB30D}"/>
+    <hyperlink ref="F16" r:id="rId140" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/rkbLw/euclidean-distance" xr:uid="{EC8417D4-EC7D-43A8-8F77-6DECA66A510B}"/>
+    <hyperlink ref="F17" r:id="rId141" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/uqakE/euclidian-distance" xr:uid="{F6EFB1EA-695E-45A5-934E-94132661AB6D}"/>
+    <hyperlink ref="F18" r:id="rId142" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/uqakE/euclidian-distance" xr:uid="{DFC76F5D-4452-4EF5-8CC2-F399D6415F75}"/>
+    <hyperlink ref="F19" r:id="rId143" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/C5EoL/cosine-similarity-intuition" xr:uid="{0E238085-58B8-4563-BD8B-CCADBA0C5EF0}"/>
+    <hyperlink ref="F20" r:id="rId144" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/C5EoL/cosine-similarity-intuition" xr:uid="{34B69B5A-1751-4D11-9D95-EA45B163B609}"/>
+    <hyperlink ref="F21" r:id="rId145" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/xW4vy/cosine-similarity-intuition" xr:uid="{5184FE2D-D749-47AE-97A5-8559EE8ECF13}"/>
+    <hyperlink ref="F22" r:id="rId146" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/xW4vy/cosine-similarity-intuition" xr:uid="{3125B2DA-DE96-4106-9813-C5B8130030E1}"/>
+    <hyperlink ref="F23" r:id="rId147" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/M70Sm/cosine-similarity" xr:uid="{8C94E59B-89AB-46BF-8F65-13B9C12DBAAE}"/>
+    <hyperlink ref="F24" r:id="rId148" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/M70Sm/cosine-similarity" xr:uid="{2083561B-D764-4F06-B30E-5EFC56C92A3C}"/>
+    <hyperlink ref="F25" r:id="rId149" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/yasAe/cosine-similarity" xr:uid="{52372806-6D37-4643-9D2C-FA341E591125}"/>
+    <hyperlink ref="F26" r:id="rId150" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/yasAe/cosine-similarity" xr:uid="{ABDBC409-3BAA-4384-8546-2C222AEA715D}"/>
+    <hyperlink ref="F27" r:id="rId151" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/g6fge/manipulating-words-in-vector-spaces" xr:uid="{BE64C858-446F-4F4B-8762-F73CEE2DD3DC}"/>
+    <hyperlink ref="F28" r:id="rId152" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/g6fge/manipulating-words-in-vector-spaces" xr:uid="{C688EEF4-FCEA-4B8A-BAFF-7FB4190FA98D}"/>
+    <hyperlink ref="F29" r:id="rId153" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/G99oo/manipulating-words-in-vector-spaces" xr:uid="{E21D9C59-04BE-4D7E-9D8E-D39C6724D565}"/>
+    <hyperlink ref="F30" r:id="rId154" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/G99oo/manipulating-words-in-vector-spaces" xr:uid="{745A47D4-8B5C-481B-B34B-29FF6D885E9E}"/>
+    <hyperlink ref="F31" r:id="rId155" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/ungradedLab/oq8uf/manipulating-word-embeddings" xr:uid="{EAA3167A-CE2D-4313-BFD6-DFD9980DA128}"/>
+    <hyperlink ref="F32" r:id="rId156" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/ungradedLab/oq8uf/manipulating-word-embeddings" xr:uid="{3EC7DC0A-E5DC-4375-BDDC-8191D65E0EB6}"/>
+    <hyperlink ref="F33" r:id="rId157" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/hjJgT/visualization-and-pca" xr:uid="{066124EF-0EC9-4A2B-993C-C3618CA1F48A}"/>
+    <hyperlink ref="F34" r:id="rId158" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/hjJgT/visualization-and-pca" xr:uid="{8B44D90D-D231-4CA1-A28C-010CCF0A508C}"/>
+    <hyperlink ref="F35" r:id="rId159" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/7FUaZ/visualization-and-pca" xr:uid="{6BE69399-EA94-4287-8689-38FA4BE2532C}"/>
+    <hyperlink ref="F36" r:id="rId160" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/7FUaZ/visualization-and-pca" xr:uid="{FC5DB04C-8316-4966-AAE8-8C83B28FCBC4}"/>
+    <hyperlink ref="F37" r:id="rId161" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/evvvb/pca-algorithm" xr:uid="{26767D1F-6B8D-4018-B0CE-CC7C2EE75989}"/>
+    <hyperlink ref="F38" r:id="rId162" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/evvvb/pca-algorithm" xr:uid="{AFE3FBF8-FE8F-4C9A-A530-0E9BD3D79349}"/>
+    <hyperlink ref="F39" r:id="rId163" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/Xd2w5/pca-algorithm" xr:uid="{4689E5C5-8E45-4A61-91A5-94B808F5A0AB}"/>
+    <hyperlink ref="F40" r:id="rId164" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/Xd2w5/pca-algorithm" xr:uid="{D93D75FB-7240-4493-98F0-5CC22DCF2307}"/>
+    <hyperlink ref="F41" r:id="rId165" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/ungradedLab/n1iZS/another-explanation-about-pca" xr:uid="{D26D1BB1-2EFB-44E7-A109-548A8FBED5F2}"/>
+    <hyperlink ref="F42" r:id="rId166" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/ungradedLab/n1iZS/another-explanation-about-pca" xr:uid="{D2086465-BE4D-4752-9FBA-1F543259FFE7}"/>
+    <hyperlink ref="F43" r:id="rId167" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/fwEUM/the-rotation-matrix-optional-reading" xr:uid="{0556E5C0-CAFA-43E4-9D22-D3438B391D54}"/>
+    <hyperlink ref="F44" r:id="rId168" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/fwEUM/the-rotation-matrix-optional-reading" xr:uid="{89B55654-27B9-4EDF-99AB-D72D8088C41E}"/>
+    <hyperlink ref="F45" r:id="rId169" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/XRo6R/week-conclusion" xr:uid="{9FE3C475-2006-4869-B073-B4155AEA505E}"/>
+    <hyperlink ref="F46" r:id="rId170" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/XRo6R/week-conclusion" xr:uid="{61F20068-0DFC-4FAE-9A0C-18088EEE09CA}"/>
+    <hyperlink ref="F49" r:id="rId171" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/qJyE6/lecture-notes-w3" xr:uid="{17B8DAE0-8A3E-4410-B5F9-FE0D87152B08}"/>
+    <hyperlink ref="F50" r:id="rId172" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/qJyE6/lecture-notes-w3" xr:uid="{D0CE2072-CB7A-45C7-BD90-1AA220E12251}"/>
+    <hyperlink ref="F53" r:id="rId173" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/assignment-submission/rTqMw/vector-space-models" xr:uid="{C761C3F5-6606-4042-B571-5249BAF31D12}"/>
+    <hyperlink ref="F54" r:id="rId174" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/assignment-submission/rTqMw/vector-space-models" xr:uid="{99DEFAA9-E809-4E08-A76B-7FFED1411D5F}"/>
+    <hyperlink ref="F57" r:id="rId175" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/programming/vbHXo/assignment-vector-space-models" xr:uid="{747B0C40-2ADC-4BA3-91A6-77BA93A37BA6}"/>
+    <hyperlink ref="F58" r:id="rId176" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/programming/vbHXo/assignment-vector-space-models" xr:uid="{A9B9FDCE-FE88-49D4-A25B-3E7158364B1A}"/>
+    <hyperlink ref="H3" r:id="rId177" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/88uZJ/week-introduction" xr:uid="{65865A86-271D-47DC-AA69-38DB889851E7}"/>
+    <hyperlink ref="H4" r:id="rId178" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/88uZJ/week-introduction" xr:uid="{B0C62CA3-8822-4D39-8797-EF2D44BEF4B8}"/>
+    <hyperlink ref="H5" r:id="rId179" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/3s44D/overview" xr:uid="{33B7322A-CC90-4A36-9394-099CE3E230A9}"/>
+    <hyperlink ref="H6" r:id="rId180" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/3s44D/overview" xr:uid="{11BE1C04-BE1C-4E26-839D-5E63D6B51BB8}"/>
+    <hyperlink ref="H7" r:id="rId181" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/dsx37/transforming-word-vectors" xr:uid="{603A8B8D-C9A5-4BFA-88AF-6AAA95031A2B}"/>
+    <hyperlink ref="H8" r:id="rId182" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/dsx37/transforming-word-vectors" xr:uid="{8187267A-91AF-410E-B075-FB4D2A78E8D6}"/>
+    <hyperlink ref="H9" r:id="rId183" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/SwK3F/transforming-word-vectors" xr:uid="{DA5C5F2A-50BB-4E38-B611-EF724CBD570D}"/>
+    <hyperlink ref="H10" r:id="rId184" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/SwK3F/transforming-word-vectors" xr:uid="{074BE44A-06A4-4489-9A58-196B01FDFA71}"/>
+    <hyperlink ref="H11" r:id="rId185" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/ungradedLab/qPdZ9/rotation-matrices-in-r2" xr:uid="{F3C69C8A-C2CC-403A-926C-AEE33C7B8870}"/>
+    <hyperlink ref="H12" r:id="rId186" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/ungradedLab/qPdZ9/rotation-matrices-in-r2" xr:uid="{F1DFDED5-CA6D-4B2B-B0D1-7D363E87149B}"/>
+    <hyperlink ref="H13" r:id="rId187" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/d13tm/k-nearest-neighbors" xr:uid="{E650EBF7-6811-4024-8E55-B0CB779DD8B2}"/>
+    <hyperlink ref="H14" r:id="rId188" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/d13tm/k-nearest-neighbors" xr:uid="{6E9217FB-D50B-42F9-BA5D-928D7809C82A}"/>
+    <hyperlink ref="H15" r:id="rId189" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/avTgO/k-nearest-neighbors" xr:uid="{06A7EFBE-DC3C-4535-8613-FDF464BCEA12}"/>
+    <hyperlink ref="H16" r:id="rId190" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/avTgO/k-nearest-neighbors" xr:uid="{F8D0E107-BE34-4A2A-9399-F96E9A3328AE}"/>
+    <hyperlink ref="H17" r:id="rId191" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/OpheJ/hash-tables-and-hash-functions" xr:uid="{D7C1552B-6FB4-48DA-91C7-E357C48EFD34}"/>
+    <hyperlink ref="H18" r:id="rId192" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/OpheJ/hash-tables-and-hash-functions" xr:uid="{EF385C47-D3CD-4F04-8093-052EC082C309}"/>
+    <hyperlink ref="H19" r:id="rId193" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/UFnGD/hash-tables-and-hash-functions" xr:uid="{AEC83AC2-9C64-4E64-BFD3-4AA1824DF5F5}"/>
+    <hyperlink ref="H20" r:id="rId194" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/UFnGD/hash-tables-and-hash-functions" xr:uid="{79898A9B-FD84-44E1-A8BE-DB8AFA4F6D79}"/>
+    <hyperlink ref="H21" r:id="rId195" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/HhTQF/locality-sensitive-hashing" xr:uid="{C65D7347-4009-41B5-85AA-4ADE3344F238}"/>
+    <hyperlink ref="H22" r:id="rId196" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/HhTQF/locality-sensitive-hashing" xr:uid="{1ED9D416-BB63-43DF-9E73-6D19E3A6B26F}"/>
+    <hyperlink ref="H23" r:id="rId197" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/ieYM6/locality-sensitive-hashing" xr:uid="{D1B86CBA-5351-4A3F-AB42-D384F6F50083}"/>
+    <hyperlink ref="H24" r:id="rId198" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/ieYM6/locality-sensitive-hashing" xr:uid="{BFF67695-438A-4DD1-8AA7-22F35E4C14DA}"/>
+    <hyperlink ref="H25" r:id="rId199" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/wdPgw/multiple-planes" xr:uid="{67EC7024-41DA-49D1-86A4-FA2851D7CAA5}"/>
+    <hyperlink ref="H26" r:id="rId200" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/wdPgw/multiple-planes" xr:uid="{891B112A-0C44-454B-9BDF-44B747D5C04D}"/>
+    <hyperlink ref="H27" r:id="rId201" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/oZLAR/multiple-planes" xr:uid="{A3A8267B-95AE-43E8-B727-76688E46929D}"/>
+    <hyperlink ref="H28" r:id="rId202" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/oZLAR/multiple-planes" xr:uid="{6B20ED10-BE07-4508-B22C-B86CEAC88496}"/>
+    <hyperlink ref="H29" r:id="rId203" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/ungradedLab/J6leY/hash-tables" xr:uid="{4A84621B-79E9-4798-970B-09AE124BB54C}"/>
+    <hyperlink ref="H30" r:id="rId204" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/ungradedLab/J6leY/hash-tables" xr:uid="{33055D89-1FD2-4222-AC13-B3D20D37C28A}"/>
+    <hyperlink ref="H31" r:id="rId205" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/ZmRFC/approximate-nearest-neighbors" xr:uid="{6F8EA44D-B058-42F9-BEEE-39EF14592A0C}"/>
+    <hyperlink ref="H32" r:id="rId206" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/ZmRFC/approximate-nearest-neighbors" xr:uid="{FFF015DE-DABD-41F1-8568-A0E1A5DB5D78}"/>
+    <hyperlink ref="H33" r:id="rId207" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/Rnp5U/approximate-nearest-neighbors" xr:uid="{CCC0972F-F595-4150-9AC7-D73C4ED48BE0}"/>
+    <hyperlink ref="H34" r:id="rId208" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/Rnp5U/approximate-nearest-neighbors" xr:uid="{6BD89C4E-C1D6-4590-B44A-4D79B75460FE}"/>
+    <hyperlink ref="H35" r:id="rId209" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/ATIYL/searching-documents" xr:uid="{FACEAFD8-07F3-4C3B-A0E6-EA215364374C}"/>
+    <hyperlink ref="H36" r:id="rId210" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/ATIYL/searching-documents" xr:uid="{FE0E2F30-A708-42FA-9290-6ADC3E5680A7}"/>
+    <hyperlink ref="H37" r:id="rId211" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/x6aJN/searching-documents" xr:uid="{EB9AFED2-8B9B-4E8A-8D6D-095BBC029D89}"/>
+    <hyperlink ref="H38" r:id="rId212" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/x6aJN/searching-documents" xr:uid="{7709B2C5-5F8E-4E0C-B070-232C4959A328}"/>
+    <hyperlink ref="H39" r:id="rId213" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/RGNFD/week-conclusion" xr:uid="{178FC47C-2FA5-40CC-9130-7270E768B321}"/>
+    <hyperlink ref="H40" r:id="rId214" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/RGNFD/week-conclusion" xr:uid="{0951E471-6213-434F-AB60-653DB7157B5E}"/>
+    <hyperlink ref="H43" r:id="rId215" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/EwPOc/lecture-notes-w4" xr:uid="{4CEE6976-6D5A-4A29-92B8-62FCDF6A4D5E}"/>
+    <hyperlink ref="H44" r:id="rId216" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/EwPOc/lecture-notes-w4" xr:uid="{476A48B8-D757-4B97-8500-189F8B3D87E3}"/>
+    <hyperlink ref="H47" r:id="rId217" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/assignment-submission/AUnU8/hashing-and-machine-translation" xr:uid="{66FFB3F3-2F8C-4B88-AC16-A9884CE6EE34}"/>
+    <hyperlink ref="H48" r:id="rId218" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/assignment-submission/AUnU8/hashing-and-machine-translation" xr:uid="{16DD0D84-F447-43FD-851C-FE2D4580BB04}"/>
+    <hyperlink ref="H51" r:id="rId219" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/614C4/important-reminder-about-end-of-access-to-lab-notebooks" xr:uid="{74085683-9AB1-418C-9C52-9A271B760DC9}"/>
+    <hyperlink ref="H52" r:id="rId220" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/614C4/important-reminder-about-end-of-access-to-lab-notebooks" xr:uid="{CAFE33BC-3296-4515-BC84-2C318EC31445}"/>
+    <hyperlink ref="H55" r:id="rId221" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/programming/qFU3R/word-translation" xr:uid="{B4467ACC-15ED-472F-8733-4D1E2B38E363}"/>
+    <hyperlink ref="H56" r:id="rId222" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/programming/qFU3R/word-translation" xr:uid="{85C7D53D-7ADB-43C0-A074-ED1FCD57E073}"/>
+    <hyperlink ref="H59" r:id="rId223" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/kahOv/acknowledgements" xr:uid="{EBECBC5E-5B8A-4D21-B823-7A55EB0984AE}"/>
+    <hyperlink ref="H60" r:id="rId224" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/kahOv/acknowledgements" xr:uid="{310F0A18-AC92-4E1E-B5F0-338186774F4C}"/>
+    <hyperlink ref="H61" r:id="rId225" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/qRRNN/bibliography" xr:uid="{81C0F8A7-DCD9-4237-A369-84303A7F4C89}"/>
+    <hyperlink ref="H62" r:id="rId226" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/supplement/qRRNN/bibliography" xr:uid="{5F92A797-F749-4249-9E93-0697A07DB1EB}"/>
+    <hyperlink ref="H65" r:id="rId227" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/Te5Z7/andrew-ng-with-kathleen-mckeown" xr:uid="{BE09B995-BFDD-4FAA-8A30-BA16FFB4E319}"/>
+    <hyperlink ref="H66" r:id="rId228" display="https://www.coursera.org/learn/classification-vector-spaces-in-nlp/lecture/Te5Z7/andrew-ng-with-kathleen-mckeown" xr:uid="{F1EA828E-BE4A-45F1-8B1E-0B7D224B4686}"/>
+    <hyperlink ref="B89" r:id="rId229" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/Z7TZ9/intro-to-course-2" xr:uid="{EDAF572F-DEB1-4AFD-A794-F73F8142E988}"/>
+    <hyperlink ref="B90" r:id="rId230" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/Z7TZ9/intro-to-course-2" xr:uid="{995CF3AF-A4CC-489F-8057-2056EE577C0E}"/>
+    <hyperlink ref="B91" r:id="rId231" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/pjjA1/week-introduction" xr:uid="{F3B9F2FB-16FB-450B-830A-9DC8E8A49FE0}"/>
+    <hyperlink ref="B92" r:id="rId232" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/pjjA1/week-introduction" xr:uid="{1C8F7A36-5639-4B6E-95A9-058B9AEF559A}"/>
+    <hyperlink ref="B93" r:id="rId233" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/ZTOqC/overview" xr:uid="{7F559450-CF66-442E-9DB0-70AB2CB103A2}"/>
+    <hyperlink ref="B94" r:id="rId234" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/ZTOqC/overview" xr:uid="{E7B408E4-1D2E-4D9E-8C9B-FC3494E55DF5}"/>
+    <hyperlink ref="B95" r:id="rId235" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/ap1cF/overview" xr:uid="{0EBADA09-A9A3-473D-9922-46B7FE80EDF1}"/>
+    <hyperlink ref="B96" r:id="rId236" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/ap1cF/overview" xr:uid="{8A2175A2-9DCE-4238-A852-24757905880B}"/>
+    <hyperlink ref="B97" r:id="rId237" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/alIBT/autocorrect" xr:uid="{C1A90062-9AAF-4ACB-BD08-A056F9642F95}"/>
+    <hyperlink ref="B98" r:id="rId238" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/alIBT/autocorrect" xr:uid="{A8E93B11-FA44-4DB9-847C-E625D360E9BF}"/>
+    <hyperlink ref="B99" r:id="rId239" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/zCyLo/autocorrect" xr:uid="{7FAD7C6E-93B2-444D-ACFF-047711402CF2}"/>
+    <hyperlink ref="B100" r:id="rId240" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/zCyLo/autocorrect" xr:uid="{6AFEC431-A3E1-462E-96C8-0C6958F095B2}"/>
+    <hyperlink ref="B101" r:id="rId241" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/2X33p/building-the-model" xr:uid="{44BA7FFA-E92C-4381-9B24-DC2BD6E93F69}"/>
+    <hyperlink ref="B102" r:id="rId242" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/2X33p/building-the-model" xr:uid="{13261687-3DE4-47A5-AFF0-8CFF64F859FA}"/>
+    <hyperlink ref="B103" r:id="rId243" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/SB0aq/building-the-model" xr:uid="{B7B16305-D996-4991-B656-15F0E83B20CA}"/>
+    <hyperlink ref="B104" r:id="rId244" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/SB0aq/building-the-model" xr:uid="{F0F5C680-A7D2-4CEB-97B5-7C7FD7F13CEB}"/>
+    <hyperlink ref="B105" r:id="rId245" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/ungradedLab/s5bsO/lecture-notebook-building-the-vocabulary" xr:uid="{DF25AB83-2E56-44AB-AAEA-B884D857ED86}"/>
+    <hyperlink ref="B106" r:id="rId246" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/ungradedLab/s5bsO/lecture-notebook-building-the-vocabulary" xr:uid="{005C4A71-0EFF-4A5E-9B57-BDA8BDA50912}"/>
+    <hyperlink ref="B107" r:id="rId247" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/HcuzT/building-the-model-ii" xr:uid="{288A6193-9D96-4B39-A302-2AC2174B06B4}"/>
+    <hyperlink ref="B108" r:id="rId248" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/HcuzT/building-the-model-ii" xr:uid="{960FA19F-13FA-4C97-A611-2B5CF905B2D9}"/>
+    <hyperlink ref="B109" r:id="rId249" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/NaSrM/building-the-model-ii" xr:uid="{A9348900-236B-4F16-A6E6-19D1BABA9457}"/>
+    <hyperlink ref="B110" r:id="rId250" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/NaSrM/building-the-model-ii" xr:uid="{3CFF3BDF-BFF4-45D0-8F63-7DB1CBEF6348}"/>
+    <hyperlink ref="B111" r:id="rId251" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/ungradedLab/bU1bz/lecture-notebook-candidates-from-edits" xr:uid="{FE419B0A-DE5A-46A6-BF1A-78B50B4D0E95}"/>
+    <hyperlink ref="B112" r:id="rId252" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/ungradedLab/bU1bz/lecture-notebook-candidates-from-edits" xr:uid="{3241241C-0656-462F-A69C-6D4C612943C6}"/>
+    <hyperlink ref="B113" r:id="rId253" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/mbrxw/minimum-edit-distance" xr:uid="{31A0EE62-C8F1-4E4A-9831-331EF458A906}"/>
+    <hyperlink ref="B114" r:id="rId254" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/mbrxw/minimum-edit-distance" xr:uid="{B993AA43-ECA8-4AC1-9074-F76AFF36CB44}"/>
+    <hyperlink ref="B115" r:id="rId255" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/sYxbc/minimum-edit-distance" xr:uid="{4E04E919-00E1-4DFB-8C34-F59014C2E956}"/>
+    <hyperlink ref="B116" r:id="rId256" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/sYxbc/minimum-edit-distance" xr:uid="{26BCE041-576C-4CFE-A7E0-5184D75B86D3}"/>
+    <hyperlink ref="B117" r:id="rId257" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/NHRZQ/minimum-edit-distance-algorithm" xr:uid="{18682609-3B93-4FA1-B6DF-51EBD241D35E}"/>
+    <hyperlink ref="B118" r:id="rId258" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/NHRZQ/minimum-edit-distance-algorithm" xr:uid="{04688E9C-47E3-441B-B1CD-52F58DA8A186}"/>
+    <hyperlink ref="B119" r:id="rId259" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/7IeNU/minimum-edit-distance-algorithm" xr:uid="{0FD64CC7-60BB-44A0-BF49-2D3E963D8F72}"/>
+    <hyperlink ref="B120" r:id="rId260" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/7IeNU/minimum-edit-distance-algorithm" xr:uid="{9E749954-E35F-431F-9414-6C472EA38182}"/>
+    <hyperlink ref="B121" r:id="rId261" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/bvYJa/minimum-edit-distance-algorithm-ii" xr:uid="{D83E3967-B26D-4874-BBAB-370F59DD3761}"/>
+    <hyperlink ref="B122" r:id="rId262" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/bvYJa/minimum-edit-distance-algorithm-ii" xr:uid="{79119CA5-E13B-4612-AA79-A62EDF644025}"/>
+    <hyperlink ref="B123" r:id="rId263" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/3EvOV/minimum-edit-distance-algorithm-ii" xr:uid="{9C3C8D06-BC91-4817-B84B-A7017ABC7B2D}"/>
+    <hyperlink ref="B124" r:id="rId264" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/3EvOV/minimum-edit-distance-algorithm-ii" xr:uid="{8E748835-DB0F-48A7-A331-3D7639AAF6FB}"/>
+    <hyperlink ref="B125" r:id="rId265" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/dCLWU/minimum-edit-distance-algorithm-iii" xr:uid="{A8FC3C36-7A66-4F97-9E02-C60D49F95644}"/>
+    <hyperlink ref="B126" r:id="rId266" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/dCLWU/minimum-edit-distance-algorithm-iii" xr:uid="{FC8F6433-1966-44BF-8E37-FEE08CC8881B}"/>
+    <hyperlink ref="B127" r:id="rId267" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/Fi4mT/minimum-edit-distance-iii" xr:uid="{3B4A5570-3194-4AA5-B52D-42745FB71A10}"/>
+    <hyperlink ref="B128" r:id="rId268" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/Fi4mT/minimum-edit-distance-iii" xr:uid="{B08532D1-5D1C-4074-AF26-3DD37DCA7F7A}"/>
+    <hyperlink ref="B129" r:id="rId269" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/hEEbo/week-conclusion" xr:uid="{24D24561-383E-4184-B5A1-86C5BB805B02}"/>
+    <hyperlink ref="B130" r:id="rId270" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/hEEbo/week-conclusion" xr:uid="{CEBAC0E6-C64C-47D5-AFD3-4A7960C53C9D}"/>
+    <hyperlink ref="B131" r:id="rId271" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/q4SK7/important-have-questions-issues-or-ideas-join-our-forum" xr:uid="{D00083D9-EF6A-4706-88FC-F50B099CEAC6}"/>
+    <hyperlink ref="B132" r:id="rId272" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/q4SK7/important-have-questions-issues-or-ideas-join-our-forum" xr:uid="{904B5738-2544-4646-B95F-708AAD2776F6}"/>
+    <hyperlink ref="B135" r:id="rId273" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/7AMzB/lecture-notes-w1" xr:uid="{AEC9447A-F80A-4D01-89A2-634B20B6D85A}"/>
+    <hyperlink ref="B136" r:id="rId274" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/7AMzB/lecture-notes-w1" xr:uid="{72C901DE-5E88-459F-BF7A-FDFFE0F471C8}"/>
+    <hyperlink ref="B139" r:id="rId275" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/assignment-submission/cHWZt/auto-correct-and-minimum-edit-distance" xr:uid="{D165656E-4593-428C-BC1B-F715303EE7A9}"/>
+    <hyperlink ref="B140" r:id="rId276" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/assignment-submission/cHWZt/auto-correct-and-minimum-edit-distance" xr:uid="{C273F248-9A41-4B3A-939E-4B341BF8633D}"/>
+    <hyperlink ref="B143" r:id="rId277" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/NdPJd/optional-downloading-your-notebook-downloading-your-workspace-and-refreshing" xr:uid="{B8F4DAF6-510F-4EE2-BFA0-58B15111B4B0}"/>
+    <hyperlink ref="B144" r:id="rId278" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/NdPJd/optional-downloading-your-notebook-downloading-your-workspace-and-refreshing" xr:uid="{67394707-CE89-4925-96EA-E13F9F845885}"/>
+    <hyperlink ref="B145" r:id="rId279" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/programming/x6KCC/autocorrect" xr:uid="{F07ADD5D-D7C6-4151-B900-42DF3E5838E3}"/>
+    <hyperlink ref="B146" r:id="rId280" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/programming/x6KCC/autocorrect" xr:uid="{21CFD838-0F79-4828-B68B-8DD82D792573}"/>
+    <hyperlink ref="D89" r:id="rId281" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/ne5fw/week-introduction" xr:uid="{1BB2EAEC-9FEE-47F8-8C90-80B91ED18BAA}"/>
+    <hyperlink ref="D90" r:id="rId282" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/ne5fw/week-introduction" xr:uid="{DE72CCD6-1E9A-456A-8288-78DDFCF5CF8B}"/>
+    <hyperlink ref="D91" r:id="rId283" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/VbnrA/part-of-speech-tagging" xr:uid="{A762BD52-017D-4A8B-BA5E-05E5E8F017AE}"/>
+    <hyperlink ref="D92" r:id="rId284" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/VbnrA/part-of-speech-tagging" xr:uid="{076EF56B-E4A3-401E-B81F-4E0D0667CCBF}"/>
+    <hyperlink ref="D93" r:id="rId285" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/ZRFD9/part-of-speech-tagging" xr:uid="{EFA35D14-302D-44F7-A653-CC1B2AF16ACE}"/>
+    <hyperlink ref="D94" r:id="rId286" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/ZRFD9/part-of-speech-tagging" xr:uid="{9866FAA9-9B41-466E-9945-177AC69AFE81}"/>
+    <hyperlink ref="D95" r:id="rId287" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/ungradedLab/NuFGV/lecture-notebook-working-with-text-files" xr:uid="{F424E8CB-A7F5-411B-8362-CC3C94F9D3E2}"/>
+    <hyperlink ref="D96" r:id="rId288" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/ungradedLab/NuFGV/lecture-notebook-working-with-text-files" xr:uid="{F18C18D6-C81B-4FA6-BF85-7D18658ACFB7}"/>
+    <hyperlink ref="D97" r:id="rId289" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/mFeRe/markov-chains" xr:uid="{E9FAB69C-ACD4-416E-BDC4-38BAC29C83AC}"/>
+    <hyperlink ref="D98" r:id="rId290" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/mFeRe/markov-chains" xr:uid="{1F1A236F-CD7E-46E7-9AD6-67A077F3D509}"/>
+    <hyperlink ref="D99" r:id="rId291" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/X18i6/markov-chains" xr:uid="{28BB104C-E45F-40D0-9D9A-E51FF6EFAA3B}"/>
+    <hyperlink ref="D100" r:id="rId292" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/X18i6/markov-chains" xr:uid="{09F58B80-8C13-4AAF-BF9C-7D63C8F86B7D}"/>
+    <hyperlink ref="D101" r:id="rId293" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/6KUim/markov-chains-and-pos-tags" xr:uid="{B8E5A580-C678-4C9C-AA02-FEE70B95D89C}"/>
+    <hyperlink ref="D102" r:id="rId294" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/6KUim/markov-chains-and-pos-tags" xr:uid="{FF11364D-5BF2-4128-A51A-C31A984D880B}"/>
+    <hyperlink ref="D103" r:id="rId295" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/XXA01/markov-chains-and-pos-tags" xr:uid="{F90A8A8C-164B-4784-A162-B39A888D1CE4}"/>
+    <hyperlink ref="D104" r:id="rId296" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/XXA01/markov-chains-and-pos-tags" xr:uid="{8092959C-7DF7-4322-9EF6-C42745A8C964}"/>
+    <hyperlink ref="D105" r:id="rId297" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/oG2yu/hidden-markov-models" xr:uid="{4F8CE64C-AF08-4208-8523-54AD42D39CA8}"/>
+    <hyperlink ref="D106" r:id="rId298" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/oG2yu/hidden-markov-models" xr:uid="{CF914973-C94A-4E94-87E1-004A3D9AB110}"/>
+    <hyperlink ref="D107" r:id="rId299" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/guW1m/hidden-markov-models" xr:uid="{CCFE90FC-3B37-4677-AD7A-56B15CFD5CD2}"/>
+    <hyperlink ref="D108" r:id="rId300" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/guW1m/hidden-markov-models" xr:uid="{A0ACD153-4349-465D-9C0D-0C9FDF69DAA7}"/>
+    <hyperlink ref="D109" r:id="rId301" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/c2tmp/calculating-probabilities" xr:uid="{BDA2AB99-0AB3-4FCA-A1E5-937F80430FF1}"/>
+    <hyperlink ref="D110" r:id="rId302" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/c2tmp/calculating-probabilities" xr:uid="{41E4E599-1207-460B-8332-E62AF40C5073}"/>
+    <hyperlink ref="D111" r:id="rId303" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/rVtWh/calculating-probabilities" xr:uid="{32BFA16D-0F05-4638-8AD6-66E90F5EADDB}"/>
+    <hyperlink ref="D112" r:id="rId304" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/rVtWh/calculating-probabilities" xr:uid="{7197FEA3-66AF-4E2F-A405-08DB960FDFE5}"/>
+    <hyperlink ref="D113" r:id="rId305" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/5bKHs/populating-the-transition-matrix" xr:uid="{10DD2E96-973F-410F-AD7D-B7CDEE0E1BF4}"/>
+    <hyperlink ref="D114" r:id="rId306" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/5bKHs/populating-the-transition-matrix" xr:uid="{1C332B4C-C5D4-4947-A65E-822C0B5ABA12}"/>
+    <hyperlink ref="D115" r:id="rId307" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/VaIUw/populating-the-transition-matrix" xr:uid="{0AA89E69-7601-4B5F-A655-FED9BC3CE104}"/>
+    <hyperlink ref="D116" r:id="rId308" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/VaIUw/populating-the-transition-matrix" xr:uid="{675333BD-3763-478E-823E-648561946967}"/>
+    <hyperlink ref="D117" r:id="rId309" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/S7MlE/populating-the-emission-matrix" xr:uid="{672593C0-FBC3-45D1-800C-3EB44E627CF7}"/>
+    <hyperlink ref="D118" r:id="rId310" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/S7MlE/populating-the-emission-matrix" xr:uid="{5C906E1E-C11A-4564-9EAA-DFC75C24F52B}"/>
+    <hyperlink ref="D119" r:id="rId311" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/FGcFu/populating-the-emission-matrix" xr:uid="{5180DC95-F267-4E3C-9DEA-154B8F59598B}"/>
+    <hyperlink ref="D120" r:id="rId312" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/FGcFu/populating-the-emission-matrix" xr:uid="{8AF5928B-791D-4D59-ADF5-2133F94E3791}"/>
+    <hyperlink ref="D121" r:id="rId313" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/ungradedLab/jB1cr/lecture-notebook-working-with-tags-and-numpy" xr:uid="{D2B75C96-A7FA-4AB3-91D1-5C922EBC00E7}"/>
+    <hyperlink ref="D122" r:id="rId314" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/ungradedLab/jB1cr/lecture-notebook-working-with-tags-and-numpy" xr:uid="{7DEC2454-8279-4448-A157-E98236440A3E}"/>
+    <hyperlink ref="D123" r:id="rId315" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/A5wSY/the-viterbi-algorithm" xr:uid="{B777F9E2-6D37-4EBD-B11B-7074953751F4}"/>
+    <hyperlink ref="D124" r:id="rId316" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/A5wSY/the-viterbi-algorithm" xr:uid="{1A7A892B-5805-47F2-BDA5-F0FEE0639CD3}"/>
+    <hyperlink ref="D125" r:id="rId317" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/7efbd/the-viterbi-algorithm" xr:uid="{400F1357-BDB5-4134-8E2A-E7E50DDBCC62}"/>
+    <hyperlink ref="D126" r:id="rId318" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/7efbd/the-viterbi-algorithm" xr:uid="{51AA2BBD-B754-4E66-8FF1-B5A640EBDBCA}"/>
+    <hyperlink ref="D127" r:id="rId319" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/Q1Wuu/viterbi-initialization" xr:uid="{8E049BC6-03F5-465E-8388-6EAE6C9E2C8B}"/>
+    <hyperlink ref="D128" r:id="rId320" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/Q1Wuu/viterbi-initialization" xr:uid="{CFBFC51A-3BAF-4C5A-A19E-4F17ADD9FA20}"/>
+    <hyperlink ref="D129" r:id="rId321" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/0H6KQ/viterbi-initialization" xr:uid="{274D4596-6712-4BA4-9155-770CD3FE41B5}"/>
+    <hyperlink ref="D130" r:id="rId322" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/0H6KQ/viterbi-initialization" xr:uid="{759F485D-AD70-4890-895F-0C26A81FB8C4}"/>
+    <hyperlink ref="D131" r:id="rId323" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/c6m8s/viterbi-forward-pass" xr:uid="{C1E179FE-01CB-44D8-A904-A27874AF8B7E}"/>
+    <hyperlink ref="D132" r:id="rId324" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/c6m8s/viterbi-forward-pass" xr:uid="{7CD2742B-6C1A-4ADA-9E99-F6B6AC62CE94}"/>
+    <hyperlink ref="D133" r:id="rId325" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/9BigR/viterbi-forward-pass" xr:uid="{A59209D7-BEE0-41AB-B7ED-CFCBD10AFEE8}"/>
+    <hyperlink ref="D134" r:id="rId326" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/9BigR/viterbi-forward-pass" xr:uid="{9F5125B2-71F4-49F9-B1BE-7199ABF3356C}"/>
+    <hyperlink ref="D135" r:id="rId327" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/YqWsL/viterbi-backward-pass" xr:uid="{993676DC-6E60-4698-8491-39B0D2AEE2F0}"/>
+    <hyperlink ref="D136" r:id="rId328" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/YqWsL/viterbi-backward-pass" xr:uid="{2ECEE84F-F895-4214-948F-0E9246866548}"/>
+    <hyperlink ref="D137" r:id="rId329" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/4OAHP/viterbi-backward-pass" xr:uid="{067CA1A4-5710-473C-9054-F6617E4123F8}"/>
+    <hyperlink ref="D138" r:id="rId330" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/4OAHP/viterbi-backward-pass" xr:uid="{4583192E-03D3-4A16-AE8C-B95E6B419163}"/>
+    <hyperlink ref="D139" r:id="rId331" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/vQBDe/week-conclusion" xr:uid="{818AF34F-CC36-4262-938D-0E77561364F1}"/>
+    <hyperlink ref="D140" r:id="rId332" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/vQBDe/week-conclusion" xr:uid="{D491A736-92D4-458B-8001-804C07258F9D}"/>
+    <hyperlink ref="D143" r:id="rId333" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/02ea5/lecture-notes-w2" xr:uid="{B8F0C23B-D329-4CAD-A978-1D02BC1B217B}"/>
+    <hyperlink ref="D144" r:id="rId334" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/02ea5/lecture-notes-w2" xr:uid="{2688F0CE-0031-4D60-B5BF-2B32BD4574D0}"/>
+    <hyperlink ref="D147" r:id="rId335" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/assignment-submission/s2raG/part-of-speech-tagging" xr:uid="{0C064817-C5AD-4B0E-8420-FE2C228DB093}"/>
+    <hyperlink ref="D148" r:id="rId336" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/assignment-submission/s2raG/part-of-speech-tagging" xr:uid="{33CA99FB-351F-46A7-8ECC-366BD4CAB76A}"/>
+    <hyperlink ref="D151" r:id="rId337" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/programming/8POp8/part-of-speech-tagging" xr:uid="{775F2963-8460-48BA-8B3B-6E2D6FAEF9B1}"/>
+    <hyperlink ref="D152" r:id="rId338" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/programming/8POp8/part-of-speech-tagging" xr:uid="{F7F4B0C2-3BEC-4BFC-9F3D-90748E0BCFA6}"/>
+    <hyperlink ref="F88" r:id="rId339" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/rOjVO/week-introduction" xr:uid="{65C38098-9A70-447A-B834-75F518BAD6C2}"/>
+    <hyperlink ref="F89" r:id="rId340" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/rOjVO/week-introduction" xr:uid="{2801B3DE-1B7C-43C6-9232-A1D51788F2F1}"/>
+    <hyperlink ref="F90" r:id="rId341" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/4k0An/overview" xr:uid="{EB8EC43C-E651-498C-991A-E504301EB269}"/>
+    <hyperlink ref="F91" r:id="rId342" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/4k0An/overview" xr:uid="{2C993BF9-AC1C-4591-84DF-FEFE7276F4DD}"/>
+    <hyperlink ref="F92" r:id="rId343" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/Zij4F/overview" xr:uid="{07E84E27-2D13-40EA-BC54-629BCF3C00A2}"/>
+    <hyperlink ref="F93" r:id="rId344" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/Lkuce/basic-word-representations" xr:uid="{3DD588F7-CC21-4EAA-AE12-70F1B7BBB3A1}"/>
+    <hyperlink ref="F94" r:id="rId345" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/Lkuce/basic-word-representations" xr:uid="{7691C384-CC9F-4D65-9D83-BDE049130200}"/>
+    <hyperlink ref="F95" r:id="rId346" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/YY3Fl/basic-word-representations" xr:uid="{2E936F3F-BBC0-4AF3-815D-5EB06453654B}"/>
+    <hyperlink ref="F96" r:id="rId347" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/YY3Fl/basic-word-representations" xr:uid="{3091E09C-42EA-4780-986D-853ACA7A7119}"/>
+    <hyperlink ref="F97" r:id="rId348" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/YC0Un/word-embeddings" xr:uid="{C70F321E-7A77-4207-843F-084BAA13C769}"/>
+    <hyperlink ref="F98" r:id="rId349" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/YC0Un/word-embeddings" xr:uid="{951AAB28-3E4E-4BF0-8F3D-1685012F5081}"/>
+    <hyperlink ref="F99" r:id="rId350" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/VJeEP/word-embeddings" xr:uid="{95EBF46A-6542-47FF-920F-7AA5BE6ECF98}"/>
+    <hyperlink ref="F100" r:id="rId351" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/VJeEP/word-embeddings" xr:uid="{DE87D4D7-88DC-4C34-A61F-B7C75978D4BA}"/>
+    <hyperlink ref="F101" r:id="rId352" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/a6J0B/how-to-create-word-embeddings" xr:uid="{8C95656A-28F0-4A71-BB64-B9D79FB0349E}"/>
+    <hyperlink ref="F102" r:id="rId353" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/a6J0B/how-to-create-word-embeddings" xr:uid="{BAD4DA4A-30C1-4400-85CD-B3FF591D1D89}"/>
+    <hyperlink ref="F103" r:id="rId354" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/d57hd/how-to-create-word-embeddings" xr:uid="{1F1857D6-5B63-4B55-9E53-454F9CF903AA}"/>
+    <hyperlink ref="F104" r:id="rId355" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/d57hd/how-to-create-word-embeddings" xr:uid="{A0E03095-CEB8-48C7-B1B8-4D9AB5AC9ABE}"/>
+    <hyperlink ref="F105" r:id="rId356" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/wxlIv/word-embedding-methods" xr:uid="{CEF8ED9D-974E-4995-9FE3-F42B04AF5EF1}"/>
+    <hyperlink ref="F106" r:id="rId357" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/wxlIv/word-embedding-methods" xr:uid="{E2B1D59B-CDBB-48A7-96BB-170D81F0A280}"/>
+    <hyperlink ref="F107" r:id="rId358" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/tI0jL/word-embedding-methods" xr:uid="{47FBC312-729A-40B0-A2F6-43CCF716097E}"/>
+    <hyperlink ref="F108" r:id="rId359" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/tI0jL/word-embedding-methods" xr:uid="{188812D6-02DA-49C3-843E-895569FE3C04}"/>
+    <hyperlink ref="F109" r:id="rId360" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/hW72r/continuous-bag-of-words-model" xr:uid="{217F604D-BACD-4186-A837-93852BED3E97}"/>
+    <hyperlink ref="F110" r:id="rId361" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/hW72r/continuous-bag-of-words-model" xr:uid="{6E4C5F11-C211-48AD-ABC6-3350C2FBD5C8}"/>
+    <hyperlink ref="F111" r:id="rId362" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/FD4DO/continuous-bag-of-words-model" xr:uid="{58F6A90C-BF52-40BA-B58F-D452E26320E3}"/>
+    <hyperlink ref="F112" r:id="rId363" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/FD4DO/continuous-bag-of-words-model" xr:uid="{BE41BFB5-911D-46E5-BA90-1496B4518791}"/>
+    <hyperlink ref="F113" r:id="rId364" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/LnHR0/cleaning-and-tokenization" xr:uid="{505B4EED-7AA0-4762-B559-DD82A4B46B9C}"/>
+    <hyperlink ref="F114" r:id="rId365" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/LnHR0/cleaning-and-tokenization" xr:uid="{2295946E-C73C-4228-B1EA-564546D132BA}"/>
+    <hyperlink ref="F115" r:id="rId366" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/2gS0p/cleaning-and-tokenization" xr:uid="{848CC65D-712D-423C-BE1E-0814FA594F66}"/>
+    <hyperlink ref="F116" r:id="rId367" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/2gS0p/cleaning-and-tokenization" xr:uid="{4EC90371-4F63-4ECD-9A96-2453F9467C5D}"/>
+    <hyperlink ref="F117" r:id="rId368" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/GrY5v/sliding-window-of-words-in-python" xr:uid="{DDDF3F77-F546-4155-A3D1-7CF098A90F06}"/>
+    <hyperlink ref="F118" r:id="rId369" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/GrY5v/sliding-window-of-words-in-python" xr:uid="{E64BE3DC-291D-4193-ABE2-4D103405C655}"/>
+    <hyperlink ref="F119" r:id="rId370" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/nXUrW/sliding-window-of-words-in-python" xr:uid="{958795BD-66D1-41B8-B98F-E3FC7F9E111C}"/>
+    <hyperlink ref="F120" r:id="rId371" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/nXUrW/sliding-window-of-words-in-python" xr:uid="{1DD88B13-6C35-48DE-9B5C-E096D2FCD055}"/>
+    <hyperlink ref="F121" r:id="rId372" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/gCkdx/transforming-words-into-vectors" xr:uid="{4991A564-CF4B-4285-8651-D220F419B094}"/>
+    <hyperlink ref="F122" r:id="rId373" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/gCkdx/transforming-words-into-vectors" xr:uid="{9D07CDE9-44D0-4440-8093-F97E81381917}"/>
+    <hyperlink ref="F123" r:id="rId374" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/n2LS9/transforming-words-into-vectors" xr:uid="{B53E1952-47F3-4A14-82AB-2C9E6519C507}"/>
+    <hyperlink ref="F124" r:id="rId375" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/n2LS9/transforming-words-into-vectors" xr:uid="{D140BFBA-8630-4ED1-909D-82FDE1F37DDD}"/>
+    <hyperlink ref="F125" r:id="rId376" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/ungradedLab/YHCrt/lecture-notebook-data-preparation" xr:uid="{0D48AE1A-A6F7-4D10-B1E0-6C9F01819642}"/>
+    <hyperlink ref="F126" r:id="rId377" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/ungradedLab/YHCrt/lecture-notebook-data-preparation" xr:uid="{0AE59D13-0DA0-481A-B450-23C698447639}"/>
+    <hyperlink ref="F127" r:id="rId378" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/UiH4B/architecture-of-the-cbow-model" xr:uid="{F1881D72-46CE-416E-BF28-C2C3585A4A4C}"/>
+    <hyperlink ref="F128" r:id="rId379" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/UiH4B/architecture-of-the-cbow-model" xr:uid="{7C816C9C-3D5D-4520-9A3E-21F12BC0BF26}"/>
+    <hyperlink ref="F129" r:id="rId380" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/GTYeE/architecture-for-the-cbow-model" xr:uid="{A6DE649D-348B-43CE-84B2-FFB526C51805}"/>
+    <hyperlink ref="F130" r:id="rId381" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/GTYeE/architecture-for-the-cbow-model" xr:uid="{B6EC97BD-C49A-4277-BA86-DA27CD473580}"/>
+    <hyperlink ref="F131" r:id="rId382" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/2iBbs/architecture-of-the-cbow-model-dimensions" xr:uid="{071FE44D-69AE-4787-A4FC-6428F8AD4233}"/>
+    <hyperlink ref="F132" r:id="rId383" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/2iBbs/architecture-of-the-cbow-model-dimensions" xr:uid="{02436D32-4313-4080-8514-AC94F7AB4EEC}"/>
+    <hyperlink ref="F133" r:id="rId384" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/l1ucn/architecture-of-the-cbow-model-dimensions" xr:uid="{886C5F08-737F-4448-8CFF-267A041CBEDD}"/>
+    <hyperlink ref="F134" r:id="rId385" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/l1ucn/architecture-of-the-cbow-model-dimensions" xr:uid="{00B57142-70C4-4152-AF74-7F9DE3B6D3FE}"/>
+    <hyperlink ref="F135" r:id="rId386" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/bUzQu/architecture-of-the-cbow-model-dimensions-2" xr:uid="{9F23F2EB-7042-45C2-9429-4FE161D134CA}"/>
+    <hyperlink ref="F136" r:id="rId387" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/bUzQu/architecture-of-the-cbow-model-dimensions-2" xr:uid="{B1EB4298-0C97-43DA-9F12-7CC3143D9E38}"/>
+    <hyperlink ref="F137" r:id="rId388" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/0kvxU/architecture-of-the-cbow-model-dimensions" xr:uid="{72762C68-13BD-4302-B900-0D425FAAF6FA}"/>
+    <hyperlink ref="F138" r:id="rId389" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/0kvxU/architecture-of-the-cbow-model-dimensions" xr:uid="{F9B29D6A-3B7A-4A63-84CB-B5677F2B49FB}"/>
+    <hyperlink ref="F139" r:id="rId390" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/DLyPe/architecture-of-the-cbow-model-activation-functions" xr:uid="{B3A30311-F958-44B8-B73C-4A23D115858F}"/>
+    <hyperlink ref="F140" r:id="rId391" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/DLyPe/architecture-of-the-cbow-model-activation-functions" xr:uid="{7BB453E5-8227-4510-B325-6AC92CA51B75}"/>
+    <hyperlink ref="F141" r:id="rId392" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/WqIgG/architecture-of-the-cbow-model-activation-functions" xr:uid="{4444074A-0AA3-4004-BFC2-FB5D8F177EDB}"/>
+    <hyperlink ref="F142" r:id="rId393" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/WqIgG/architecture-of-the-cbow-model-activation-functions" xr:uid="{042D8DBF-BD85-4F44-86E2-D9B987B668FF}"/>
+    <hyperlink ref="F143" r:id="rId394" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/ungradedLab/40CB2/lecture-notebook-intro-to-cbow-model" xr:uid="{2C7663F8-A383-428A-AD39-38080F6689DE}"/>
+    <hyperlink ref="F144" r:id="rId395" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/ungradedLab/40CB2/lecture-notebook-intro-to-cbow-model" xr:uid="{6BBD290D-25C7-4E8B-AA4E-0CCD0FC2BFF8}"/>
+    <hyperlink ref="F145" r:id="rId396" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/N1pEX/training-a-cbow-model-cost-function" xr:uid="{16D0C14E-010B-47A3-BFB9-AF6EF038D608}"/>
+    <hyperlink ref="F146" r:id="rId397" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/N1pEX/training-a-cbow-model-cost-function" xr:uid="{D9D09A4B-D0B8-40D7-94F3-AD0EE47A7458}"/>
+    <hyperlink ref="F147" r:id="rId398" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/sfiuP/training-a-cbow-model-cost-function" xr:uid="{B329CC6F-7D3D-4963-98F5-53A333BE570F}"/>
+    <hyperlink ref="F148" r:id="rId399" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/sfiuP/training-a-cbow-model-cost-function" xr:uid="{16CD6131-21F6-4FAE-8FFD-67658B7DFDD9}"/>
+    <hyperlink ref="F149" r:id="rId400" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/Vphwi/training-a-cbow-model-forward-propagation" xr:uid="{036371BF-F4A7-40E8-857C-F1880FC0D930}"/>
+    <hyperlink ref="F150" r:id="rId401" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/Vphwi/training-a-cbow-model-forward-propagation" xr:uid="{9E2D341B-AFD9-40AF-B1A4-5324B95BB259}"/>
+    <hyperlink ref="F151" r:id="rId402" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/sD7Jz/training-a-cbow-model-forward-propagation" xr:uid="{7B33521D-91FA-4886-8882-E12CC4B902FF}"/>
+    <hyperlink ref="F152" r:id="rId403" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/sD7Jz/training-a-cbow-model-forward-propagation" xr:uid="{BFA697BB-E81B-41E5-993D-251EB525C976}"/>
+    <hyperlink ref="F153" r:id="rId404" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/mPJwt/training-a-cbow-model-backpropagation-and-gradient-descent" xr:uid="{FAE457E8-3A37-4EEA-815E-D7178C3EC51D}"/>
+    <hyperlink ref="F154" r:id="rId405" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/mPJwt/training-a-cbow-model-backpropagation-and-gradient-descent" xr:uid="{A65E2AE5-F8A5-4E2C-9717-EE3EB93511FE}"/>
+    <hyperlink ref="F155" r:id="rId406" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/EEbAq/training-a-cbow-model-backpropagation-and-gradient-descent" xr:uid="{D80CD540-EC5F-4E6F-9AE6-4AED8447FCE1}"/>
+    <hyperlink ref="F156" r:id="rId407" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/EEbAq/training-a-cbow-model-backpropagation-and-gradient-descent" xr:uid="{8A2B24AB-D50B-4B29-95B9-1BD9DDEC5A92}"/>
+    <hyperlink ref="F157" r:id="rId408" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/ungradedLab/EDfC4/lecture-notebook-training-the-cbow-model" xr:uid="{D3150177-2AFC-4DB2-B09C-9C4512ACE509}"/>
+    <hyperlink ref="F158" r:id="rId409" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/ungradedLab/EDfC4/lecture-notebook-training-the-cbow-model" xr:uid="{D0CCFAE1-398B-4928-9C07-B308F47D02CB}"/>
+    <hyperlink ref="F159" r:id="rId410" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/Py1VW/extracting-word-embedding-vectors" xr:uid="{168B3A53-7EFA-40B1-9DE1-F2DE691B99CE}"/>
+    <hyperlink ref="F160" r:id="rId411" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/Py1VW/extracting-word-embedding-vectors" xr:uid="{9F05FE8F-1E9B-4EDA-B894-1135CA1E4CE5}"/>
+    <hyperlink ref="F161" r:id="rId412" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/effZO/extracting-word-embedding-vectors" xr:uid="{E4F36529-C7EB-4CD2-A97D-34A4F56F3505}"/>
+    <hyperlink ref="F162" r:id="rId413" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/effZO/extracting-word-embedding-vectors" xr:uid="{36AE6C95-2F31-49E2-A66C-9A909A120283}"/>
+    <hyperlink ref="F163" r:id="rId414" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/ungradedLab/b8cUI/lecture-notebook-word-embeddings" xr:uid="{ABC95ACD-0477-414D-93D1-B9E10EA249BB}"/>
+    <hyperlink ref="F164" r:id="rId415" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/ungradedLab/b8cUI/lecture-notebook-word-embeddings" xr:uid="{5AFF01BF-8519-4FB0-818C-F7F278D76307}"/>
+    <hyperlink ref="F165" r:id="rId416" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/BELqR/evaluating-word-embeddings-intrinsic-evaluation" xr:uid="{2632C792-8CF3-463C-A113-31B2DE435ACD}"/>
+    <hyperlink ref="F166" r:id="rId417" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/BELqR/evaluating-word-embeddings-intrinsic-evaluation" xr:uid="{3DD125C4-9E28-4B6E-85FE-8870804189FB}"/>
+    <hyperlink ref="F167" r:id="rId418" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/b26Xq/evaluating-word-embeddings-intrinsic-evaluation" xr:uid="{279B5CBA-E35E-49C1-982D-02212EBDB52B}"/>
+    <hyperlink ref="F168" r:id="rId419" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/b26Xq/evaluating-word-embeddings-intrinsic-evaluation" xr:uid="{E5D60FA6-0D29-4481-9A47-AA761E84E367}"/>
+    <hyperlink ref="F169" r:id="rId420" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/SEJkb/evaluating-word-embeddings-extrinsic-evaluation" xr:uid="{344D5FFF-163E-4925-A8CB-B539268A8491}"/>
+    <hyperlink ref="F170" r:id="rId421" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/SEJkb/evaluating-word-embeddings-extrinsic-evaluation" xr:uid="{F1595379-BB2F-4E13-AF87-E4255B8834C2}"/>
+    <hyperlink ref="F171" r:id="rId422" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/np9nb/evaluating-word-embeddings-extrinsic-evaluation" xr:uid="{44295235-D911-4379-A0AD-4D9AC5CA3E60}"/>
+    <hyperlink ref="F172" r:id="rId423" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/np9nb/evaluating-word-embeddings-extrinsic-evaluation" xr:uid="{1B45A8EC-0A48-4C1C-BEA3-94D8CE7EBBD9}"/>
+    <hyperlink ref="F173" r:id="rId424" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/ungradedLab/FYCIF/lecture-notebook-word-embeddings-step-by-step" xr:uid="{229BD5C5-1AB0-4544-BD2E-E29FAA330D0C}"/>
+    <hyperlink ref="F174" r:id="rId425" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/ungradedLab/FYCIF/lecture-notebook-word-embeddings-step-by-step" xr:uid="{FF68D02F-F078-401A-9369-5B7F7295BECD}"/>
+    <hyperlink ref="F175" r:id="rId426" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/r7XXs/conclusion" xr:uid="{160CB33C-A2C7-479E-8DAC-9BD23B88F350}"/>
+    <hyperlink ref="F176" r:id="rId427" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/r7XXs/conclusion" xr:uid="{8D6CAFEB-32C8-4BFD-99D0-8C0DA5FBA233}"/>
+    <hyperlink ref="F177" r:id="rId428" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/aIneD/conclusion" xr:uid="{EAE3592D-F3C1-4FD1-9738-B5E0A8347707}"/>
+    <hyperlink ref="F178" r:id="rId429" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/aIneD/conclusion" xr:uid="{2637596C-60B0-4EF7-BED3-80A5EEFCA93D}"/>
+    <hyperlink ref="F180" r:id="rId430" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/FRqTy/week-conclusion" xr:uid="{2730152F-A295-44DD-9DFD-5789BC8FFFBA}"/>
+    <hyperlink ref="F181" r:id="rId431" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/lecture/FRqTy/week-conclusion" xr:uid="{601641A1-BD93-4F1A-9162-5A90AF8B20B3}"/>
+    <hyperlink ref="F183" r:id="rId432" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/Gkg2X/lecture-notes-w4" xr:uid="{C684DE88-7149-4667-B977-131DCA45EDA0}"/>
+    <hyperlink ref="F184" r:id="rId433" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/Gkg2X/lecture-notes-w4" xr:uid="{26E5DD49-8B06-407F-BA3C-33C1721C28D1}"/>
+    <hyperlink ref="F186" r:id="rId434" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/assignment-submission/YV9RE/word-embeddings" xr:uid="{E4450883-4EEA-440C-8DE1-DBD9AFF3FB27}"/>
+    <hyperlink ref="F187" r:id="rId435" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/assignment-submission/YV9RE/word-embeddings" xr:uid="{B5A171DF-8B73-484B-80A9-E11CC3A8DA16}"/>
+    <hyperlink ref="F189" r:id="rId436" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/dHRZs/important-reminder-about-end-of-access-to-lab-notebooks" xr:uid="{0B5BD05A-3B44-495C-A531-95EA232780D3}"/>
+    <hyperlink ref="F190" r:id="rId437" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/dHRZs/important-reminder-about-end-of-access-to-lab-notebooks" xr:uid="{46152C39-6A3C-4E7E-8FD6-F6BF953E24D1}"/>
+    <hyperlink ref="F192" r:id="rId438" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/programming/OrMrl/word-embeddings" xr:uid="{46714CB5-FE89-40C4-B2E5-A90BFF9C9976}"/>
+    <hyperlink ref="F193" r:id="rId439" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/programming/OrMrl/word-embeddings" xr:uid="{A74E87C7-7714-490F-8438-288F1CFFE9F5}"/>
+    <hyperlink ref="F195" r:id="rId440" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/DBect/acknowledgments" xr:uid="{8BC01ACB-F9F6-41DF-8CE7-F05AE5688AC3}"/>
+    <hyperlink ref="F196" r:id="rId441" display="https://www.coursera.org/learn/probabilistic-models-in-nlp/supplement/DBect/acknowledgments" xr:uid="{BCBE1F22-A91F-4663-A0EB-937EB592C8B4}"/>
+    <hyperlink ref="B205" r:id="rId442" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/rz8aj/course-3-introduction" xr:uid="{2581191F-0C03-4D50-B06D-B043F0195BCC}"/>
+    <hyperlink ref="B206" r:id="rId443" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/rz8aj/course-3-introduction" xr:uid="{391E3CAF-037B-4E30-8547-52CE918E4756}"/>
+    <hyperlink ref="B207" r:id="rId444" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/Sf4g4/lesson-introduction" xr:uid="{F75CFDC6-6B7F-4E02-A30E-35009448D905}"/>
+    <hyperlink ref="B208" r:id="rId445" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/Sf4g4/lesson-introduction" xr:uid="{FFD41BF5-EA5E-4093-9228-F063D8D499D5}"/>
+    <hyperlink ref="B209" r:id="rId446" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/qV6Eb/lesson-introduction-clarification" xr:uid="{D3E21FAB-C2F9-46C5-9B9E-84DEAF3EA98C}"/>
+    <hyperlink ref="B210" r:id="rId447" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/qV6Eb/lesson-introduction-clarification" xr:uid="{71E7F49C-C9F0-4622-BD26-B7953F4354D1}"/>
+    <hyperlink ref="B211" r:id="rId448" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/E3opc/neural-networks-for-sentiment-analysis" xr:uid="{36B0DB81-FE31-405B-852E-DF5828BB27A7}"/>
+    <hyperlink ref="B212" r:id="rId449" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/E3opc/neural-networks-for-sentiment-analysis" xr:uid="{4F271D72-3A9E-48B2-A45D-3000097D757C}"/>
+    <hyperlink ref="B213" r:id="rId450" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/cLSLo/neural-networks-for-sentiment-analysis" xr:uid="{DF6F78C8-0A3C-4D9C-8902-0AD40E602188}"/>
+    <hyperlink ref="B214" r:id="rId451" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/cLSLo/neural-networks-for-sentiment-analysis" xr:uid="{95FAECF9-5052-4D41-9B30-E6A604376644}"/>
+    <hyperlink ref="B215" r:id="rId452" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/AGDYm/dense-layers-and-relu" xr:uid="{ECA127AC-3F01-4085-B9B1-BEF9A2CD3CAF}"/>
+    <hyperlink ref="B216" r:id="rId453" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/AGDYm/dense-layers-and-relu" xr:uid="{0503F4C6-9C63-45BC-9E25-AA8168D540AD}"/>
+    <hyperlink ref="B217" r:id="rId454" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/9G7vx/dense-layers-and-relu" xr:uid="{5DC46EFD-CA1A-4477-8FF4-69E382C9EF46}"/>
+    <hyperlink ref="B218" r:id="rId455" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/9G7vx/dense-layers-and-relu" xr:uid="{81D19AD5-699D-4690-A114-65C71A30F9FB}"/>
+    <hyperlink ref="B219" r:id="rId456" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/CT6YH/embedding-and-mean-layers" xr:uid="{6164F6B6-4307-4952-B315-26C348673E4D}"/>
+    <hyperlink ref="B220" r:id="rId457" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/CT6YH/embedding-and-mean-layers" xr:uid="{960EE783-8E96-41E9-B429-C1F644BDF793}"/>
+    <hyperlink ref="B221" r:id="rId458" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/wfa54/embedding-and-mean-layers" xr:uid="{6D64FD6D-3154-4E82-9E17-08904DFC88C5}"/>
+    <hyperlink ref="B222" r:id="rId459" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/wfa54/embedding-and-mean-layers" xr:uid="{E0F9B32D-798E-4987-AAF2-B49167EAB429}"/>
+    <hyperlink ref="B223" r:id="rId460" display="https://www.coursera.org/learn/sequence-models-in-nlp/ungradedLab/eR5eM/introduction-to-tensorflow" xr:uid="{4E7901A2-15E1-4F79-8557-C440683558A0}"/>
+    <hyperlink ref="B224" r:id="rId461" display="https://www.coursera.org/learn/sequence-models-in-nlp/ungradedLab/eR5eM/introduction-to-tensorflow" xr:uid="{5D106E32-526E-40BF-8C28-3945AF0024BD}"/>
+    <hyperlink ref="B226" r:id="rId462" display="https://www.coursera.org/learn/sequence-models-in-nlp/ungradedLti/kfnFS/important-have-questions-issues-or-ideas-join-our-community-on-discourse" xr:uid="{EE925A5E-FDAF-4866-BFEE-4389A73A8B97}"/>
+    <hyperlink ref="B227" r:id="rId463" display="https://www.coursera.org/learn/sequence-models-in-nlp/ungradedLti/kfnFS/important-have-questions-issues-or-ideas-join-our-community-on-discourse" xr:uid="{D0A1B0E3-7128-4D30-8A20-93ECB89A250D}"/>
+    <hyperlink ref="B229" r:id="rId464" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/01fNq/optional-downloading-your-notebook-downloading-your-workspace-and-refreshing" xr:uid="{A582FAFB-20CF-4F05-9C76-A0FCD93C22E8}"/>
+    <hyperlink ref="B230" r:id="rId465" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/01fNq/optional-downloading-your-notebook-downloading-your-workspace-and-refreshing" xr:uid="{2F1762F8-5EFC-4175-9894-C1B1A4E9395F}"/>
+    <hyperlink ref="B232" r:id="rId466" display="https://www.coursera.org/learn/sequence-models-in-nlp/programming/DyPCv/sentiment-with-deep-neural-networks" xr:uid="{5BF534A7-FDC3-414B-8BBC-EB810C7549BA}"/>
+    <hyperlink ref="B233" r:id="rId467" display="https://www.coursera.org/learn/sequence-models-in-nlp/programming/DyPCv/sentiment-with-deep-neural-networks" xr:uid="{42BF9A5B-ED8B-4A82-91A0-1B6E2B96BA8D}"/>
+    <hyperlink ref="B235" r:id="rId468" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/XAIyJ/lesson-introduction" xr:uid="{D8C50161-C13A-43CB-AF44-E67A8248541F}"/>
+    <hyperlink ref="B236" r:id="rId469" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/XAIyJ/lesson-introduction" xr:uid="{6AFDD1F7-298C-4D63-A26A-DA99D6981E0A}"/>
+    <hyperlink ref="B237" r:id="rId470" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/adQKz/traditional-language-models" xr:uid="{51CEB157-51B7-4888-9681-F0B7A04276AB}"/>
+    <hyperlink ref="B238" r:id="rId471" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/adQKz/traditional-language-models" xr:uid="{CC709072-DA35-47BB-97FB-5E3413F6504D}"/>
+    <hyperlink ref="B239" r:id="rId472" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/jDg7N/traditional-language-models" xr:uid="{5B496145-B7A6-4FCF-A7E4-3F878887EF60}"/>
+    <hyperlink ref="B240" r:id="rId473" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/jDg7N/traditional-language-models" xr:uid="{9B2B444A-C13F-4E04-9683-45F19528A38E}"/>
+    <hyperlink ref="B241" r:id="rId474" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/SgnFd/recurrent-neural-networks" xr:uid="{8F382127-D7A3-41CF-83EC-3883D6CD12BF}"/>
+    <hyperlink ref="B242" r:id="rId475" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/SgnFd/recurrent-neural-networks" xr:uid="{F786056F-1E99-4CC2-A654-1833B4BDD912}"/>
+    <hyperlink ref="B243" r:id="rId476" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/TyJuk/recurrent-neural-networks" xr:uid="{2C44B8F1-C8BC-4BD9-ABCC-D838218D212D}"/>
+    <hyperlink ref="B244" r:id="rId477" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/TyJuk/recurrent-neural-networks" xr:uid="{DB1D2249-1722-4755-9374-C6064955BBC3}"/>
+    <hyperlink ref="B245" r:id="rId478" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/VLEGc/applications-of-rnns" xr:uid="{58C19EC6-CF88-4C18-9B06-73A780DCDD97}"/>
+    <hyperlink ref="B246" r:id="rId479" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/VLEGc/applications-of-rnns" xr:uid="{72AEBAD9-A17B-4183-ACB0-26A51DCFBBAD}"/>
+    <hyperlink ref="B247" r:id="rId480" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/1iglC/application-of-rnns" xr:uid="{A851B293-07AC-4C08-AA63-14EA52E1EBAC}"/>
+    <hyperlink ref="B248" r:id="rId481" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/1iglC/application-of-rnns" xr:uid="{62EA0929-A9F1-46BB-B2B5-0936296E22C7}"/>
+    <hyperlink ref="B249" r:id="rId482" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/q9vfy/math-in-simple-rnns" xr:uid="{EDAD29C6-4B70-4927-BD64-99CDB56BFABA}"/>
+    <hyperlink ref="B250" r:id="rId483" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/q9vfy/math-in-simple-rnns" xr:uid="{F4551910-3A0D-4E57-8D02-4357ADB3768F}"/>
+    <hyperlink ref="B251" r:id="rId484" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/eaLt6/math-in-simple-rnns" xr:uid="{7EF49D5A-0253-47C2-ADCA-12E3E429F11B}"/>
+    <hyperlink ref="B252" r:id="rId485" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/eaLt6/math-in-simple-rnns" xr:uid="{2C9FFF1B-9E07-4766-B390-1AA2F50673DC}"/>
+    <hyperlink ref="B253" r:id="rId486" display="https://www.coursera.org/learn/sequence-models-in-nlp/ungradedLab/qgDUb/hidden-state-activation" xr:uid="{44BB4FAC-ED20-479A-B9ED-3473F6DE92B9}"/>
+    <hyperlink ref="B254" r:id="rId487" display="https://www.coursera.org/learn/sequence-models-in-nlp/ungradedLab/qgDUb/hidden-state-activation" xr:uid="{92E4DB67-0EED-40DB-9ADD-239699848E33}"/>
+    <hyperlink ref="B255" r:id="rId488" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/v14dP/cost-function-for-rnns" xr:uid="{F7F7CF3C-A564-423F-B3B1-C3B9CE93A6E7}"/>
+    <hyperlink ref="B256" r:id="rId489" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/v14dP/cost-function-for-rnns" xr:uid="{04D5A59D-9D41-4E72-8821-A5A8A9BAD8C2}"/>
+    <hyperlink ref="B257" r:id="rId490" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/KBmVE/cost-function-for-rnns" xr:uid="{3E82E4FF-DA3E-4692-8894-2518ED258E67}"/>
+    <hyperlink ref="B258" r:id="rId491" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/KBmVE/cost-function-for-rnns" xr:uid="{E8DE0EB3-7D3F-487A-8B27-203B614B093A}"/>
+    <hyperlink ref="B259" r:id="rId492" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/402Mt/implementation-note" xr:uid="{995A9679-A923-4D38-8BDD-4898B7C0194A}"/>
+    <hyperlink ref="B260" r:id="rId493" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/402Mt/implementation-note" xr:uid="{FF9BDF65-558E-41ED-BE74-4D48E6A3A3D9}"/>
+    <hyperlink ref="B261" r:id="rId494" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/rhso8/implementation-note" xr:uid="{5C4DFCFB-B0E1-4183-94CF-FDD74F671C1E}"/>
+    <hyperlink ref="B262" r:id="rId495" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/rhso8/implementation-note" xr:uid="{BAF28965-110E-4DEB-92EA-7803AD75C3A0}"/>
+    <hyperlink ref="B263" r:id="rId496" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/U2BcV/gated-recurrent-units" xr:uid="{2060C7B9-F5A2-446D-910F-8AD5B0871F18}"/>
+    <hyperlink ref="B264" r:id="rId497" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/U2BcV/gated-recurrent-units" xr:uid="{E4D170FF-E39E-4CBC-8D41-0480A6B842F8}"/>
+    <hyperlink ref="B265" r:id="rId498" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/t5L3H/gated-recurrent-units" xr:uid="{53DD8F81-34A3-49D1-9AE6-A17C1DF2CA2A}"/>
+    <hyperlink ref="B266" r:id="rId499" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/t5L3H/gated-recurrent-units" xr:uid="{64D02C57-6427-4CD8-A91C-3C1B46F5676C}"/>
+    <hyperlink ref="B267" r:id="rId500" display="https://www.coursera.org/learn/sequence-models-in-nlp/ungradedLab/jJn3o/vanilla-rnns-grus-and-the-scan-function" xr:uid="{9AB03BB5-E9C3-4F3D-B598-2EC88950CC48}"/>
+    <hyperlink ref="B268" r:id="rId501" display="https://www.coursera.org/learn/sequence-models-in-nlp/ungradedLab/jJn3o/vanilla-rnns-grus-and-the-scan-function" xr:uid="{F88CBCDB-42CE-4A2A-9B71-E5394DAFA76E}"/>
+    <hyperlink ref="B269" r:id="rId502" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/xHrTe/deep-and-bi-directional-rnns" xr:uid="{FD0FBF6A-6B07-4535-9262-2A7131AB70F6}"/>
+    <hyperlink ref="B270" r:id="rId503" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/xHrTe/deep-and-bi-directional-rnns" xr:uid="{87BE5BE3-026F-4570-8E0A-B8F4BD16F8A4}"/>
+    <hyperlink ref="B271" r:id="rId504" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/TBXN7/deep-and-bi-directional-rnns" xr:uid="{DDA795DF-B305-4E9D-977B-702ACA555417}"/>
+    <hyperlink ref="B272" r:id="rId505" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/TBXN7/deep-and-bi-directional-rnns" xr:uid="{0F19F703-F2D2-4B29-86D7-6BDC2B1D318C}"/>
+    <hyperlink ref="B273" r:id="rId506" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/dYHmL/calculating-perplexity" xr:uid="{7FA94CF7-B649-4AC3-BE19-E313106A23F6}"/>
+    <hyperlink ref="B274" r:id="rId507" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/dYHmL/calculating-perplexity" xr:uid="{791BE7A6-0F77-4701-B093-9621644321AD}"/>
+    <hyperlink ref="B275" r:id="rId508" display="https://www.coursera.org/learn/sequence-models-in-nlp/ungradedLab/FfL0u/calculating-perplexity" xr:uid="{16594942-D6E5-4190-8155-B4AF44353CF2}"/>
+    <hyperlink ref="B276" r:id="rId509" display="https://www.coursera.org/learn/sequence-models-in-nlp/ungradedLab/FfL0u/calculating-perplexity" xr:uid="{6B0A1874-CB5F-4C4A-9900-8190EF252DED}"/>
+    <hyperlink ref="B278" r:id="rId510" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/cfAvr/week-conclusion" xr:uid="{153AD828-A98E-4E67-9209-F392564CE051}"/>
+    <hyperlink ref="B279" r:id="rId511" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/cfAvr/week-conclusion" xr:uid="{F529107D-CBFC-468C-924E-C95E26032C69}"/>
+    <hyperlink ref="B281" r:id="rId512" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/k8zPO/lecture-notes-w1" xr:uid="{DB6A0D7E-DF0D-436D-85B7-DED56D6A5B85}"/>
+    <hyperlink ref="B282" r:id="rId513" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/k8zPO/lecture-notes-w1" xr:uid="{AC6FAE49-5A27-4E35-9F36-B9FE38BDD48E}"/>
+    <hyperlink ref="B284" r:id="rId514" display="https://www.coursera.org/learn/sequence-models-in-nlp/assignment-submission/PAg58/rnns-for-language-modelling" xr:uid="{9869B348-CBCC-4304-BE9B-DEE6B3B3BC33}"/>
+    <hyperlink ref="B285" r:id="rId515" display="https://www.coursera.org/learn/sequence-models-in-nlp/assignment-submission/PAg58/rnns-for-language-modelling" xr:uid="{41D20CB0-AC89-4D70-96F7-FA76B4975A01}"/>
+    <hyperlink ref="B288" r:id="rId516" display="https://www.coursera.org/learn/sequence-models-in-nlp/programming/RWKwg/deep-n-grams" xr:uid="{C5F4E63D-07F6-42EE-88E5-8D1135080966}"/>
+    <hyperlink ref="B289" r:id="rId517" display="https://www.coursera.org/learn/sequence-models-in-nlp/programming/RWKwg/deep-n-grams" xr:uid="{DB664CE6-F16F-42F1-92BA-7B7EE435F809}"/>
+    <hyperlink ref="B291" r:id="rId518" display="https://www.coursera.org/learn/sequence-models-in-nlp/home/welcome" xr:uid="{0E2A46B5-15ED-440A-9235-E4662A3827FF}"/>
+    <hyperlink ref="B293" r:id="rId519" display="https://www.coursera.org/learn/sequence-models-in-nlp/home/week/1" xr:uid="{A9250B9D-5D47-4AEA-996B-5DFCB2E634F8}"/>
+    <hyperlink ref="B295" r:id="rId520" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/rz8aj/course-3-introduction" xr:uid="{5E255313-1D62-4C62-B827-DBA25AFD4CEB}"/>
+    <hyperlink ref="D206" r:id="rId521" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/VzGce/week-introduction" xr:uid="{34C9EF82-B65F-483A-9ED4-C73499B91E7A}"/>
+    <hyperlink ref="D207" r:id="rId522" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/VzGce/week-introduction" xr:uid="{CDD79533-452E-48A2-94B3-DFA81872EA95}"/>
+    <hyperlink ref="D208" r:id="rId523" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/bIio4/rnns-and-vanishing-gradients" xr:uid="{63F5C3BC-4D1A-43BC-9147-0A6AE06C257D}"/>
+    <hyperlink ref="D209" r:id="rId524" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/bIio4/rnns-and-vanishing-gradients" xr:uid="{118EEA3A-45FC-4A9C-871C-E862CCDB7007}"/>
+    <hyperlink ref="D210" r:id="rId525" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/OIXEN/rnns-and-vanishing-gradients" xr:uid="{D283B87F-B1CF-4E26-97AC-680B93376C1D}"/>
+    <hyperlink ref="D211" r:id="rId526" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/OIXEN/rnns-and-vanishing-gradients" xr:uid="{12AB24A2-38FA-41A3-B868-3AD114668E66}"/>
+    <hyperlink ref="D212" r:id="rId527" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/zMoax/optional-intro-to-optimization-in-deep-learning-gradient-descent" xr:uid="{08A7A19D-7C4B-42BA-9CDA-EC07D6DB6E11}"/>
+    <hyperlink ref="D213" r:id="rId528" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/zMoax/optional-intro-to-optimization-in-deep-learning-gradient-descent" xr:uid="{9B5D731C-F4DA-4A29-853E-05FFFBB51943}"/>
+    <hyperlink ref="D214" r:id="rId529" display="https://www.coursera.org/learn/sequence-models-in-nlp/ungradedLab/XuaHb/vanishing-gradients" xr:uid="{BAF318DB-1618-43F4-835D-855BC50110A2}"/>
+    <hyperlink ref="D215" r:id="rId530" display="https://www.coursera.org/learn/sequence-models-in-nlp/ungradedLab/XuaHb/vanishing-gradients" xr:uid="{A7B466EE-0E8B-40CA-996D-05BF8005727E}"/>
+    <hyperlink ref="D216" r:id="rId531" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/eJalx/introduction-to-lstms" xr:uid="{79FBB3FB-9133-49DD-B3DC-895B492B9CC6}"/>
+    <hyperlink ref="D217" r:id="rId532" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/eJalx/introduction-to-lstms" xr:uid="{E2766588-8FA5-440E-A1A5-C3EAB5A4DEE8}"/>
+    <hyperlink ref="D218" r:id="rId533" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/mXkvE/introduction-to-lstms" xr:uid="{18D2E50E-A95B-4805-99BF-B0C86FF889C3}"/>
+    <hyperlink ref="D219" r:id="rId534" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/mXkvE/introduction-to-lstms" xr:uid="{7215E5A6-9965-482E-AAFA-A4A10D2BB090}"/>
+    <hyperlink ref="D220" r:id="rId535" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/f1Sqa/lstm-architecture" xr:uid="{A75C6DEF-F4E6-4B51-8F90-FF53043C8FF4}"/>
+    <hyperlink ref="D221" r:id="rId536" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/f1Sqa/lstm-architecture" xr:uid="{5CC046AD-F921-4E22-8BF8-C88A279545B9}"/>
+    <hyperlink ref="D222" r:id="rId537" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/RHssB/lstm-architecture" xr:uid="{F08F30D5-5E26-43C4-A75A-75552003005A}"/>
+    <hyperlink ref="D223" r:id="rId538" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/RHssB/lstm-architecture" xr:uid="{EDAF7388-6214-4827-925A-BE1501A9681E}"/>
+    <hyperlink ref="D224" r:id="rId539" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/mSUuG/introduction-to-named-entity-recognition" xr:uid="{CEA6F46A-E35B-44A0-A175-6AF08AA0DB5B}"/>
+    <hyperlink ref="D225" r:id="rId540" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/mSUuG/introduction-to-named-entity-recognition" xr:uid="{28EB3D33-7BA8-4F5A-8C10-F716D1DB1FF8}"/>
+    <hyperlink ref="D226" r:id="rId541" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/Rn4uP/introduction-to-named-entity-recognition" xr:uid="{16B6BA54-6694-49FC-A3AC-F5E819517A63}"/>
+    <hyperlink ref="D227" r:id="rId542" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/Rn4uP/introduction-to-named-entity-recognition" xr:uid="{E1242980-4D90-43F7-BAC7-35A5C539E3B3}"/>
+    <hyperlink ref="D228" r:id="rId543" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/vUAlY/training-ners-data-processing" xr:uid="{3032F620-99D1-432A-8770-F5269EBFFC1F}"/>
+    <hyperlink ref="D229" r:id="rId544" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/vUAlY/training-ners-data-processing" xr:uid="{FCE8FD46-B88E-4A52-908D-94A39A1F1D0D}"/>
+    <hyperlink ref="D230" r:id="rId545" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/eDGae/training-ners-data-processing" xr:uid="{4FC57E6E-8BE7-4B31-8487-70F929472771}"/>
+    <hyperlink ref="D231" r:id="rId546" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/eDGae/training-ners-data-processing" xr:uid="{19273534-9C34-4803-9F70-C6EEF347A77A}"/>
+    <hyperlink ref="D232" r:id="rId547" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/UKvIA/long-short-term-memory-deep-learning-specialization-c5" xr:uid="{F93D06B6-4B13-4E9C-AB67-B678371E5357}"/>
+    <hyperlink ref="D233" r:id="rId548" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/UKvIA/long-short-term-memory-deep-learning-specialization-c5" xr:uid="{F93312B4-5769-4EDF-98DF-0BC11BFEE2CC}"/>
+    <hyperlink ref="D234" r:id="rId549" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/odcLM/computing-accuracy" xr:uid="{6537DF3A-B8E8-4C35-AC26-53D2E437A045}"/>
+    <hyperlink ref="D235" r:id="rId550" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/odcLM/computing-accuracy" xr:uid="{6173D312-6404-4909-9A23-C31CACBD9796}"/>
+    <hyperlink ref="D236" r:id="rId551" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/Nh7o2/computing-accuracy" xr:uid="{0F060C2D-8437-420A-ACF1-F1DA879C0BC4}"/>
+    <hyperlink ref="D237" r:id="rId552" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/Nh7o2/computing-accuracy" xr:uid="{B5E6C14D-1537-4AFD-9E88-CF17BA1A06FF}"/>
+    <hyperlink ref="D238" r:id="rId553" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/utwd1/week-conclusion" xr:uid="{41DBD324-7E93-477B-BCBC-29882459AF64}"/>
+    <hyperlink ref="D239" r:id="rId554" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/utwd1/week-conclusion" xr:uid="{E1CBC566-CAB8-4CE6-B888-AC3671219E15}"/>
+    <hyperlink ref="D242" r:id="rId555" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/y5nIG/lecture-notes-w2" xr:uid="{A1AC98B1-A876-4776-8A83-73104DAE596B}"/>
+    <hyperlink ref="D243" r:id="rId556" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/y5nIG/lecture-notes-w2" xr:uid="{6A14EE69-1131-4151-8DEC-DEF79EABDB97}"/>
+    <hyperlink ref="D246" r:id="rId557" display="https://www.coursera.org/learn/sequence-models-in-nlp/assignment-submission/iwL7k/lstms-and-named-entity-recognition" xr:uid="{2C4C7D36-7761-44CD-9C66-1831AD7783AD}"/>
+    <hyperlink ref="D247" r:id="rId558" display="https://www.coursera.org/learn/sequence-models-in-nlp/assignment-submission/iwL7k/lstms-and-named-entity-recognition" xr:uid="{10AE1065-11DA-43DE-A481-F5CF3BE4331E}"/>
+    <hyperlink ref="D250" r:id="rId559" display="https://www.coursera.org/learn/sequence-models-in-nlp/programming/hDP4K/named-entity-recognition-ner" xr:uid="{315DDC98-5674-4049-9CC0-D995F60A9AD3}"/>
+    <hyperlink ref="D251" r:id="rId560" display="https://www.coursera.org/learn/sequence-models-in-nlp/programming/hDP4K/named-entity-recognition-ner" xr:uid="{9555AB1F-7ADA-4390-B7D7-1EC0A76002C4}"/>
+    <hyperlink ref="F206" r:id="rId561" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/DNjwu/week-introduction" xr:uid="{4ABFAA15-48C0-4B32-B4A5-820CCD882EF5}"/>
+    <hyperlink ref="F207" r:id="rId562" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/DNjwu/week-introduction" xr:uid="{0750DDE9-4FE3-45E2-94D0-80BC27EAD3B6}"/>
+    <hyperlink ref="F208" r:id="rId563" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/C0TdU/siamese-networks" xr:uid="{488C5279-47DA-4B6E-A11A-66539EA01ED7}"/>
+    <hyperlink ref="F209" r:id="rId564" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/C0TdU/siamese-networks" xr:uid="{9B12FE2D-4F18-4CF7-94CE-213979B543A5}"/>
+    <hyperlink ref="F210" r:id="rId565" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/Ar2T2/siamese-network" xr:uid="{448A45B3-A610-46B3-8600-84C048F7A135}"/>
+    <hyperlink ref="F211" r:id="rId566" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/Ar2T2/siamese-network" xr:uid="{A76EAC59-42D8-45F1-99C9-98A654549B97}"/>
+    <hyperlink ref="F212" r:id="rId567" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/t2Zft/architecture" xr:uid="{D4CE2DE2-1922-4554-8C45-CD021390B376}"/>
+    <hyperlink ref="F213" r:id="rId568" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/t2Zft/architecture" xr:uid="{BAB7DD1D-B625-4A0A-920D-2A553C5C21D0}"/>
+    <hyperlink ref="F214" r:id="rId569" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/oUdcN/architecture" xr:uid="{37B2DB03-02DF-4E0C-B66B-A781468E90EF}"/>
+    <hyperlink ref="F215" r:id="rId570" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/oUdcN/architecture" xr:uid="{868A3A2D-16DE-43F7-BBA9-CF21092FF0D0}"/>
+    <hyperlink ref="F216" r:id="rId571" display="https://www.coursera.org/learn/sequence-models-in-nlp/ungradedLab/ppr8A/creating-a-siamese-model" xr:uid="{CE51564D-460A-4013-898E-BAD8BDE0D89B}"/>
+    <hyperlink ref="F217" r:id="rId572" display="https://www.coursera.org/learn/sequence-models-in-nlp/ungradedLab/ppr8A/creating-a-siamese-model" xr:uid="{540A6979-00E5-40F1-B1DD-44E4DF3ACE10}"/>
+    <hyperlink ref="F218" r:id="rId573" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/qiwjv/cost-function" xr:uid="{0A8E4329-2B2F-4047-BDCC-DD24D74CB094}"/>
+    <hyperlink ref="F219" r:id="rId574" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/qiwjv/cost-function" xr:uid="{6AFEC925-5CAE-4D6D-A86E-6DB5131B33F0}"/>
+    <hyperlink ref="F220" r:id="rId575" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/Dts95/cost-function" xr:uid="{FF997B36-627E-4F2F-8EB1-361725605137}"/>
+    <hyperlink ref="F221" r:id="rId576" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/Dts95/cost-function" xr:uid="{F1290A88-13D8-4F92-BF6E-CFD9AD8F6760}"/>
+    <hyperlink ref="F222" r:id="rId577" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/L88EY/triplets" xr:uid="{BE2D689A-7E8B-4518-853A-80FA7370D9E6}"/>
+    <hyperlink ref="F223" r:id="rId578" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/L88EY/triplets" xr:uid="{6CA17F5C-13D0-4D56-BA1D-309F513144F6}"/>
+    <hyperlink ref="F224" r:id="rId579" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/Xm3vv/triplets" xr:uid="{A9E47AEE-5363-48B6-A343-2E7C19C3EDF8}"/>
+    <hyperlink ref="F225" r:id="rId580" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/Xm3vv/triplets" xr:uid="{A4E9E521-F825-4D87-B0A2-152B53836C02}"/>
+    <hyperlink ref="F226" r:id="rId581" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/T4Ylj/computing-the-cost-i" xr:uid="{25CC0463-4992-42FF-9200-1015913DF134}"/>
+    <hyperlink ref="F227" r:id="rId582" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/T4Ylj/computing-the-cost-i" xr:uid="{50FC9ED1-3012-4A9B-A956-1A8E6FE3526C}"/>
+    <hyperlink ref="F228" r:id="rId583" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/g0yAF/computing-the-cost-i" xr:uid="{89285367-9D60-43B6-A57B-A8F7ADDD217A}"/>
+    <hyperlink ref="F229" r:id="rId584" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/g0yAF/computing-the-cost-i" xr:uid="{A18456FD-D1E5-40B2-9C76-0BC4945603A9}"/>
+    <hyperlink ref="F230" r:id="rId585" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/qXOjN/computing-the-cost-ii" xr:uid="{5FC992DE-C307-4BCC-99A1-D8A43BC01EA5}"/>
+    <hyperlink ref="F231" r:id="rId586" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/qXOjN/computing-the-cost-ii" xr:uid="{F5D73598-45DD-452E-814E-1EB5A4217E75}"/>
+    <hyperlink ref="F232" r:id="rId587" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/I3DUX/computing-the-cost-ii" xr:uid="{08E2727A-B76D-4175-ABAB-D65745A96CFE}"/>
+    <hyperlink ref="F233" r:id="rId588" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/I3DUX/computing-the-cost-ii" xr:uid="{D1FCA6A0-5C81-4919-AA04-E14F5EC78607}"/>
+    <hyperlink ref="F234" r:id="rId589" display="https://www.coursera.org/learn/sequence-models-in-nlp/ungradedLab/PjdpZ/implementing-the-modified-triplet-loss-in-tensorflow" xr:uid="{E3FACA77-3EBB-423D-8ED6-172E7F17CF37}"/>
+    <hyperlink ref="F235" r:id="rId590" display="https://www.coursera.org/learn/sequence-models-in-nlp/ungradedLab/PjdpZ/implementing-the-modified-triplet-loss-in-tensorflow" xr:uid="{BC3B0B91-C36F-4B0E-BE90-264F3F6A9000}"/>
+    <hyperlink ref="F236" r:id="rId591" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/MyJfA/one-shot-learning" xr:uid="{55506B25-3601-4678-BA63-9CA52421AFA8}"/>
+    <hyperlink ref="F237" r:id="rId592" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/MyJfA/one-shot-learning" xr:uid="{BDA9495D-EE56-4E56-A1A2-9965F1E91D1E}"/>
+    <hyperlink ref="F238" r:id="rId593" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/2UWi3/one-shot-learning" xr:uid="{B8F5710E-EB96-40FF-A48A-C5D98493E162}"/>
+    <hyperlink ref="F239" r:id="rId594" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/2UWi3/one-shot-learning" xr:uid="{759A38BB-FAEC-477F-BA37-198AF49A986F}"/>
+    <hyperlink ref="F240" r:id="rId595" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/KDqML/training-testing" xr:uid="{8AECDE44-CFB2-49C1-8DFB-620EBB8FB304}"/>
+    <hyperlink ref="F241" r:id="rId596" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/KDqML/training-testing" xr:uid="{CF12EF20-39B7-4897-8268-CA1EF245596F}"/>
+    <hyperlink ref="F242" r:id="rId597" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/ucnWB/training-testing" xr:uid="{D3A19EF4-6232-496A-A3EB-7A2F29BD8F96}"/>
+    <hyperlink ref="F243" r:id="rId598" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/ucnWB/training-testing" xr:uid="{48478B04-897B-432B-948B-D187096DB7D2}"/>
+    <hyperlink ref="F244" r:id="rId599" display="https://www.coursera.org/learn/sequence-models-in-nlp/ungradedLab/R0s1B/evaluate-a-siamese-model" xr:uid="{AE9720D3-8BFB-4BA2-8998-96599BBE4F96}"/>
+    <hyperlink ref="F245" r:id="rId600" display="https://www.coursera.org/learn/sequence-models-in-nlp/ungradedLab/R0s1B/evaluate-a-siamese-model" xr:uid="{72CD844A-7315-4F50-8F95-A22945AD7D07}"/>
+    <hyperlink ref="F246" r:id="rId601" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/VaeWQ/week-conclusion" xr:uid="{229C5489-5DA4-4ED2-86C7-B00B778BD657}"/>
+    <hyperlink ref="F247" r:id="rId602" display="https://www.coursera.org/learn/sequence-models-in-nlp/lecture/VaeWQ/week-conclusion" xr:uid="{3B16F1D3-6DCE-4D08-9330-66423742DD5D}"/>
+    <hyperlink ref="F250" r:id="rId603" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/tqJ0w/lecture-notes-w3" xr:uid="{D721C6F0-18CA-4355-AD5E-5B7DF97B6FFD}"/>
+    <hyperlink ref="F251" r:id="rId604" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/tqJ0w/lecture-notes-w3" xr:uid="{355D9021-7BC2-4EC8-8580-DF83447066C2}"/>
+    <hyperlink ref="F254" r:id="rId605" display="https://www.coursera.org/learn/sequence-models-in-nlp/assignment-submission/Jx8Ye/siamese-networks" xr:uid="{BE5C8FB1-D2D3-41F4-A2F0-43C2D5BE60E7}"/>
+    <hyperlink ref="F255" r:id="rId606" display="https://www.coursera.org/learn/sequence-models-in-nlp/assignment-submission/Jx8Ye/siamese-networks" xr:uid="{C7BB557E-ECBE-4B21-A2A6-F0ED6B893462}"/>
+    <hyperlink ref="F258" r:id="rId607" display="https://www.coursera.org/learn/sequence-models-in-nlp/programming/jjKpq/question-duplicates" xr:uid="{FC195C34-0D0E-4C63-BD69-00B2DD99A42E}"/>
+    <hyperlink ref="F259" r:id="rId608" display="https://www.coursera.org/learn/sequence-models-in-nlp/programming/jjKpq/question-duplicates" xr:uid="{784BC69A-9450-4A49-B1EA-83E8D1C3089C}"/>
+    <hyperlink ref="F262" r:id="rId609" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/2MrqP/acknowledgments" xr:uid="{8FB6E6C1-2E06-44B8-82E7-94DBF63EFBC3}"/>
+    <hyperlink ref="F263" r:id="rId610" display="https://www.coursera.org/learn/sequence-models-in-nlp/supplement/2MrqP/acknowledgments" xr:uid="{101CED6B-D938-4F88-800B-CC5423CB90A0}"/>
+    <hyperlink ref="B402" r:id="rId611" display="https://www.coursera.org/learn/attention-models-in-nlp/lecture/EXHcS/course-4-introduction" xr:uid="{52537C2F-68BD-49BC-83D7-7F7F3B063B96}"/>
+    <hyperlink ref="B403" r:id="rId612" display="https://www.coursera.org/learn/attention-models-in-nlp/lecture/EXHcS/course-4-introduction" xr:uid="{B4C886EE-3C25-4260-B239-EE164DDFBF17}"/>
+    <hyperlink ref="B404" r:id="rId613" display="https://www.coursera.org/learn/attention-models-in-nlp/lecture/GHweQ/week-introduction" xr:uid="{269F18EE-1199-4CF2-87BB-3D57CE1E5F7D}"/>
+    <hyperlink ref="B405" r:id="rId614" display="https://www.coursera.org/learn/attention-models-in-nlp/lecture/GHweQ/week-introduction" xr:uid="{6ED142DC-CFCE-4AEA-8664-4369FDE514C6}"/>
+    <hyperlink ref="B406" r:id="rId615" display="https://www.coursera.org/learn/attention-models-in-nlp/lecture/VhWLB/seq2seq" xr:uid="{CD831473-933A-4760-A6BD-184169CAE3AD}"/>
+    <hyperlink ref="B407" r:id="rId616" display="https://www.coursera.org/learn/attention-models-in-nlp/lecture/VhWLB/seq2seq" xr:uid="{4A6683D4-1CD3-49C2-8126-526EA8D3506A}"/>
+    <hyperlink ref="B408" r:id="rId617" display="https://www.coursera.org/learn/attention-models-in-nlp/lecture/LLvlj/seq2seq-model-with-attention" xr:uid="{362E6E40-FF5A-44A8-8B88-E0CA6F39876D}"/>
+    <hyperlink ref="B409" r:id="rId618" display="https://www.coursera.org/learn/attention-models-in-nlp/lecture/LLvlj/seq2seq-model-with-attention" xr:uid="{93DAB6C1-FA8A-42C4-9F65-4BC46625C4C1}"/>
+    <hyperlink ref="B410" r:id="rId619" display="https://www.coursera.org/learn/attention-models-in-nlp/ungradedLab/yTiQN/ungraded-lab-basic-attention" xr:uid="{52F89AA1-F0E9-4835-9605-AF2A54BBB015}"/>
+    <hyperlink ref="B411" r:id="rId620" display="https://www.coursera.org/learn/attention-models-in-nlp/ungradedLab/yTiQN/ungraded-lab-basic-attention" xr:uid="{DB30C8F6-4A97-4908-B140-9F85E184C8AD}"/>
+    <hyperlink ref="B412" r:id="rId621" display="https://www.coursera.org/learn/attention-models-in-nlp/supplement/HJ84q/background-on-seq2seq" xr:uid="{0E43672A-F372-43C0-8CA3-C645A45C6198}"/>
+    <hyperlink ref="B413" r:id="rId622" display="https://www.coursera.org/learn/attention-models-in-nlp/supplement/HJ84q/background-on-seq2seq" xr:uid="{CEDE7204-AF4F-4F72-9FC4-F3C0D61362DB}"/>
+    <hyperlink ref="B414" r:id="rId623" display="https://www.coursera.org/learn/attention-models-in-nlp/lecture/hPxD1/queries-keys-values-and-attention" xr:uid="{17DB785C-9647-4F71-B687-0C209BACEF92}"/>
+    <hyperlink ref="B415" r:id="rId624" display="https://www.coursera.org/learn/attention-models-in-nlp/lecture/hPxD1/queries-keys-values-and-attention" xr:uid="{67FA933B-6BAC-49EA-9507-ADF8208B434B}"/>
+    <hyperlink ref="B416" r:id="rId625" display="https://www.coursera.org/learn/attention-models-in-nlp/ungradedLab/pqgnf/ungraded-lab-scaled-dot-product-attention" xr:uid="{0C63B3E7-9106-4051-85E5-916A6DB9AD7F}"/>
+    <hyperlink ref="B417" r:id="rId626" display="https://www.coursera.org/learn/attention-models-in-nlp/ungradedLab/pqgnf/ungraded-lab-scaled-dot-product-attention" xr:uid="{AEE3F787-1CB2-4C89-8C96-555CB515EEC3}"/>
+    <hyperlink ref="B418" r:id="rId627" display="https://www.coursera.org/learn/attention-models-in-nlp/lecture/87aPC/setup-for-machine-translation" xr:uid="{9859FA9F-BA52-4214-8465-759B103413AE}"/>
+    <hyperlink ref="B419" r:id="rId628" display="https://www.coursera.org/learn/attention-models-in-nlp/lecture/87aPC/setup-for-machine-translation" xr:uid="{6C120C13-7318-4FD2-94AF-86BF6D39BAA6}"/>
+    <hyperlink ref="B420" r:id="rId629" display="https://www.coursera.org/learn/attention-models-in-nlp/lecture/noMUB/teacher-forcing" xr:uid="{64E1BF47-D292-47B9-8066-A400DFA33F16}"/>
+    <hyperlink ref="B421" r:id="rId630" display="https://www.coursera.org/learn/attention-models-in-nlp/lecture/noMUB/teacher-forcing" xr:uid="{0A98D348-E062-4690-B2D4-CE7415F71171}"/>
+    <hyperlink ref="B422" r:id="rId631" display="https://www.coursera.org/learn/attention-models-in-nlp/lecture/CieMg/nmt-model-with-attention" xr:uid="{E9BAFDA3-5DDC-4703-9DEF-EFF22C187181}"/>
+    <hyperlink ref="B423" r:id="rId632" display="https://www.coursera.org/learn/attention-models-in-nlp/lecture/CieMg/nmt-model-with-attention" xr:uid="{24709112-80BD-4F39-A6A4-83C8353DEE29}"/>
+    <hyperlink ref="B424" r:id="rId633" display="https://www.coursera.org/learn/attention-models-in-nlp/lecture/4ZdLf/bleu-score" xr:uid="{001E6CF1-D7E2-41D5-A53A-FC5180D77620}"/>
+    <hyperlink ref="B425" r:id="rId634" display="https://www.coursera.org/learn/attention-models-in-nlp/lecture/4ZdLf/bleu-score" xr:uid="{12F5DE52-1B31-4CF4-A7CD-D73D7907ACAE}"/>
+    <hyperlink ref="B426" r:id="rId635" display="https://www.coursera.org/learn/attention-models-in-nlp/ungradedLab/67bz7/ungraded-lab-bleu-score" xr:uid="{228DF3FB-B868-4C62-807D-BA476F1E5D97}"/>
+    <hyperlink ref="B427" r:id="rId636" display="https://www.coursera.org/learn/attention-models-in-nlp/ungradedLab/67bz7/ungraded-lab-bleu-score" xr:uid="{D1E9CAED-8ADC-4296-A103-C01B4B062F3A}"/>
+    <hyperlink ref="B428" r:id="rId637" display="https://www.coursera.org/learn/attention-models-in-nlp/lecture/CtY2v/rouge-n-score" xr:uid="{332BC8FF-4D01-4B51-8867-C733849BB342}"/>
+    <hyperlink ref="B429" r:id="rId638" display="https://www.coursera.org/learn/attention-models-in-nlp/lecture/CtY2v/rouge-n-score" xr:uid="{089C2827-0EBB-4963-AF89-47A83E39FBCF}"/>
+    <hyperlink ref="B430" r:id="rId639" display="https://www.coursera.org/learn/attention-models-in-nlp/lecture/5OVYd/sampling-and-decoding" xr:uid="{F9EB870A-43A7-49CE-93EF-21BF885DDAF2}"/>
+    <hyperlink ref="B431" r:id="rId640" display="https://www.coursera.org/learn/attention-models-in-nlp/lecture/5OVYd/sampling-and-decoding" xr:uid="{C67EEC24-0EE4-4CE9-8D61-A1F88A64EA35}"/>
+    <hyperlink ref="B432" r:id="rId641" display="https://www.coursera.org/learn/attention-models-in-nlp/lecture/Ukk3c/beam-search" xr:uid="{CEE3846B-E156-4DF3-9A55-B1DBDACBFBBE}"/>
+    <hyperlink ref="B433" r:id="rId642" display="https://www.coursera.org/learn/attention-models-in-nlp/lecture/Ukk3c/beam-search" xr:uid="{3D930EA7-1666-44E8-BF68-0495B7A466ED}"/>
+    <hyperlink ref="B434" r:id="rId643" display="https://www.coursera.org/learn/attention-models-in-nlp/lecture/2UOc2/minimum-bayes-risk" xr:uid="{2418C149-ABB0-4EC8-A903-74BCDB05859E}"/>
+    <hyperlink ref="B435" r:id="rId644" display="https://www.coursera.org/learn/attention-models-in-nlp/lecture/2UOc2/minimum-bayes-risk" xr:uid="{64E6697A-95D1-4382-89E8-D4604910FDA3}"/>
+    <hyperlink ref="B436" r:id="rId645" display="https://www.coursera.org/learn/attention-models-in-nlp/lecture/ggQCj/week-conclusion" xr:uid="{66D3F231-EFD3-4AE1-ADB6-C896119EC5A2}"/>
+    <hyperlink ref="B437" r:id="rId646" display="https://www.coursera.org/learn/attention-models-in-nlp/lecture/ggQCj/week-conclusion" xr:uid="{B1DDDA08-A18D-4C14-8875-1CA89EC0381F}"/>
+    <hyperlink ref="B438" r:id="rId647" display="https://www.coursera.org/learn/attention-models-in-nlp/supplement/Cvrzm/content-resource" xr:uid="{A34C1CF0-1709-4ED6-9EE4-F3F1BEBB9AA3}"/>
+    <hyperlink ref="B439" r:id="rId648" display="https://www.coursera.org/learn/attention-models-in-nlp/supplement/Cvrzm/content-resource" xr:uid="{EE58E3BD-1E6F-489C-BD7B-B037B7A79D46}"/>
+    <hyperlink ref="B440" r:id="rId649" display="https://www.coursera.org/learn/attention-models-in-nlp/ungradedLti/yuY7z/important-have-questions-issues-or-ideas-join-our-community" xr:uid="{6559468B-4B81-46E5-B1AC-273B16282FC4}"/>
+    <hyperlink ref="B441" r:id="rId650" display="https://www.coursera.org/learn/attention-models-in-nlp/ungradedLti/yuY7z/important-have-questions-issues-or-ideas-join-our-community" xr:uid="{A629CFE1-75F5-49D8-A9E5-E5D8BE6F83AF}"/>
+    <hyperlink ref="B444" r:id="rId651" display="https://www.coursera.org/learn/attention-models-in-nlp/supplement/wt3sP/lecture-notes-w1" xr:uid="{33D9C4E9-2B02-4F0B-B0FF-1EC915781417}"/>
+    <hyperlink ref="B445" r:id="rId652" display="https://www.coursera.org/learn/attention-models-in-nlp/supplement/wt3sP/lecture-notes-w1" xr:uid="{C4EB2D1F-851C-42ED-8CB5-00FD42189108}"/>
+    <hyperlink ref="B448" r:id="rId653" display="https://www.coursera.org/learn/attention-models-in-nlp/assignment-submission/5E7sq/neural-machine-translation" xr:uid="{050810A3-5F60-4981-A683-8C97EE3B70AE}"/>
+    <hyperlink ref="B449" r:id="rId654" display="https://www.coursera.org/learn/attention-models-in-nlp/assignment-submission/5E7sq/neural-machine-translation" xr:uid="{08B0AED7-D5F8-42DA-B68F-4CB24CC35507}"/>
+    <hyperlink ref="B452" r:id="rId655" display="https://www.coursera.org/learn/attention-models-in-nlp/supplement/gIOWC/optional-downloading-your-notebook-downloading-your-workspace-and-refreshing" xr:uid="{6742B172-B958-4D32-8EE2-F03D39148AEB}"/>
+    <hyperlink ref="B453" r:id="rId656" display="https://www.coursera.org/learn/attention-models-in-nlp/supplement/gIOWC/optional-downloading-your-notebook-downloading-your-workspace-and-refreshing" xr:uid="{7972CF5A-D2CF-4846-A00F-41205DBF5ED2}"/>
+    <hyperlink ref="B454" r:id="rId657" display="https://www.coursera.org/learn/attention-models-in-nlp/programming/bGQXT/nmt-with-attention-tensorflow" xr:uid="{8DBA0C0E-286B-4A18-962A-698FAE4650CC}"/>
+    <hyperlink ref="B455" r:id="rId658" display="https://www.coursera.org/learn/attention-models-in-nlp/programming/bGQXT/nmt-with-attention-tensorflow" xr:uid="{E77A6CF9-84AA-4992-BFD6-EBF0FE21BA63}"/>
+    <hyperlink ref="B458" r:id="rId659" display="https://www.coursera.org/learn/attention-models-in-nlp/lecture/n9npP/andrew-ng-with-oren-etzioni" xr:uid="{5723C1BA-8989-437B-9395-BC797CEA5903}"/>
+    <hyperlink ref="B459" r:id="rId660" display="https://www.coursera.org/learn/attention-models-in-nlp/lecture/n9npP/andrew-ng-with-oren-etzioni" xr:uid="{F3A2BBC1-A50C-419F-B64B-0F60CB45879C}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId661"/>
+  <drawing r:id="rId662"/>
+  <legacyDrawing r:id="rId663"/>
+  <controls>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1025" r:id="rId664" name="Control 1">
+          <controlPr defaultSize="0" r:id="rId665">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>390</xdr:row>
+                <xdr:rowOff>28575</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>1190625</xdr:colOff>
+                <xdr:row>391</xdr:row>
+                <xdr:rowOff>133350</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1025" r:id="rId664" name="Control 1"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+  </controls>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D09824E0-4EC5-409A-A3E6-1EE94EDCE3F4}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="63.28515625" customWidth="1"/>
+    <col min="4" max="4" width="53.28515625" customWidth="1"/>
+    <col min="6" max="6" width="62.28515625" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
+  </cols>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46D6608B-DC5A-4280-A295-F2A4332D692B}">
   <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2387,7 +8936,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15B0C420-D9D0-4B0E-94EE-D3DE5E37BFD7}">
   <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2569,7 +9118,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DDD8583-6A72-4B85-A719-4247344EDA9F}">
   <dimension ref="B1:H143"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4697,7 +11246,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{403B1D1B-819A-4168-9798-982D9103325B}">
   <dimension ref="B1:H98"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5645,440 +12194,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED28FC12-FCE5-4FD3-B40B-D96785393966}">
-  <dimension ref="A1:I74"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="12.7109375" style="18" customWidth="1"/>
-    <col min="2" max="2" width="8.140625" style="21" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" style="19" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" style="19" customWidth="1"/>
-    <col min="5" max="5" width="69.7109375" style="19" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" style="18" customWidth="1"/>
-    <col min="7" max="7" width="35" style="19" customWidth="1"/>
-    <col min="8" max="8" width="3.5703125" style="19" customWidth="1"/>
-    <col min="9" max="9" width="46.5703125" style="19" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="19"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" s="15" customFormat="1" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="16" t="s">
-        <v>386</v>
-      </c>
-      <c r="B1" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="22" t="s">
-        <v>387</v>
-      </c>
-      <c r="E1" s="22" t="s">
-        <v>394</v>
-      </c>
-      <c r="F1" s="16" t="s">
-        <v>386</v>
-      </c>
-      <c r="G1" s="15" t="s">
-        <v>388</v>
-      </c>
-      <c r="I1" s="15" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="18">
-        <v>45650</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="18">
-        <v>45650</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B7" s="21">
-        <v>2</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>397</v>
-      </c>
-      <c r="I7" s="19" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E8" s="19" t="s">
-        <v>395</v>
-      </c>
-      <c r="I8" s="23" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E9" s="19" t="s">
-        <v>396</v>
-      </c>
-      <c r="I9" s="23" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="18">
-        <v>45650</v>
-      </c>
-      <c r="B12" s="21">
-        <v>3</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D13" s="19" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E14" s="19" t="s">
-        <v>400</v>
-      </c>
-      <c r="I14" s="19" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E15" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="I15" s="19" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E16" s="19" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="18">
-        <v>45650</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B20" s="21">
-        <v>2</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E21" s="19" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E22" s="19" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E23" s="19" t="s">
-        <v>409</v>
-      </c>
-      <c r="I23" s="19" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="18">
-        <v>45650</v>
-      </c>
-      <c r="B26" s="21">
-        <v>3</v>
-      </c>
-      <c r="C26" s="17" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D27" s="19" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E28" s="19" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E29" s="19" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E30" s="19" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E31" s="19" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="18">
-        <v>45651</v>
-      </c>
-      <c r="C34" s="17" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B35" s="21">
-        <v>2</v>
-      </c>
-      <c r="D35" s="19" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E36" s="19" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E37" s="19" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E38" s="19" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="18">
-        <v>45652</v>
-      </c>
-      <c r="C43" s="17" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B44" s="21">
-        <v>1</v>
-      </c>
-      <c r="D44" s="19" t="s">
-        <v>446</v>
-      </c>
-      <c r="F44" s="18">
-        <v>45652</v>
-      </c>
-      <c r="G44" s="19" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E45" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="G45" s="19" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E46" s="19" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E47" s="19" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E48" s="19" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="18">
-        <v>45653</v>
-      </c>
-      <c r="B49" s="21">
-        <v>2</v>
-      </c>
-      <c r="D49" s="19" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E50" s="19" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E51" s="19" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E52" s="19" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E53" s="19" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E54" s="19" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E55" s="19" t="s">
-        <v>458</v>
-      </c>
-      <c r="F55" s="18">
-        <v>45653</v>
-      </c>
-      <c r="G55" s="19" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E56" s="19" t="s">
-        <v>457</v>
-      </c>
-      <c r="F56" s="18">
-        <v>45653</v>
-      </c>
-      <c r="G56" s="19" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="18">
-        <v>45654</v>
-      </c>
-      <c r="B59" s="21">
-        <v>3</v>
-      </c>
-      <c r="D59" s="19" t="s">
-        <v>305</v>
-      </c>
-      <c r="F59" s="18">
-        <v>45656</v>
-      </c>
-      <c r="G59" s="19" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E60" s="19" t="s">
-        <v>461</v>
-      </c>
-      <c r="G60" s="19" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E61" s="19" t="s">
-        <v>462</v>
-      </c>
-      <c r="G61" s="19" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E62" s="19" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E63" s="19" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E64" s="19" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" s="18">
-        <v>45657</v>
-      </c>
-      <c r="B67" s="21">
-        <v>4</v>
-      </c>
-      <c r="D67" s="19" t="s">
-        <v>347</v>
-      </c>
-      <c r="F67" s="18">
-        <v>45658</v>
-      </c>
-      <c r="G67" s="19" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E68" s="19" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E69" s="19" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E70" s="19" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E71" s="19" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E72" s="19" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E73" s="19" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E74" s="19" t="s">
-        <v>476</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="I8" r:id="rId1" display="https://www.coursera.org/learn/convolutional-neural-networks/lecture/4THzO/transfer-learning" xr:uid="{B9121CC7-7813-4873-864A-8369867402F8}"/>
-    <hyperlink ref="I9" r:id="rId2" display="https://www.coursera.org/learn/convolutional-neural-networks/lecture/AYzbX/data-augmentation" xr:uid="{2B7168BD-CD28-4234-9D63-C3228459BEC1}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16CAD99E-6B46-4DB4-B669-4ADC4A8FF44C}">
   <dimension ref="B1:B64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
